--- a/employees.xlsx
+++ b/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,6 +752,51 @@
       </c>
       <c r="K7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3030</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>vvvvv</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9874563211</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vvvvv@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>vvvv</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hjvg</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3030</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,318 +484,6 @@
           <t>route</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>123456</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>bhartesh</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>7620096199</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>bharteshsavale2112@gmail.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>123456</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>12344</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>abcc</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>7620096198</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>bajajautopune1@gmail.com</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>moshi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>cccc</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1234</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>9876</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>abcd</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>9874563210</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>abcd@gmail.com</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Survey No. 669, Pune-Nashik Highway
-Moshi Alandi Road</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>98765</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7410</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sakshi</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>9156396198</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sakshi@gmail.com</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>chakan</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chakan </t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>7410</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9090</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>9921531890</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>vishal@gmail.com</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>aaaa</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>9090</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>7575</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sachin</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>7788639090</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sachin@gmail.com</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>avc</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>7575</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>3030</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>vvvvv</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>9874563211</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>vvvvv@gmail.com</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1st Shift</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>vvvv</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>hjvg</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>3030</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,318 @@
           <t>route</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>123456</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bhartesh</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7620096199</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bharteshsavale2112@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>123456</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>12344</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>abcc</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7620096198</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>bajajautopune1@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>moshi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cccc</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9876</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>abcd</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9874563210</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>abcd@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Survey No. 669, Pune-Nashik Highway
+Moshi Alandi Road</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>98765</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sakshi</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9156396198</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sakshi@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>chakan</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chakan </t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9090</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9921531890</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vishal@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>aaaa</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>9090</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7575</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sachin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7788639090</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sachin@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>avc</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>7575</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3030</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>vvvvv</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9874563211</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vvvvv@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1st Shift</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>vvvv</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hjvg</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3030</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -523,10 +523,16 @@
           <t>moshi</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>123456</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$FyM9X9SjvJoTK8hx$7dce7abafaebd423902245a50d80f8606219abc18b39df118778496d286161c4f38a1c3180549a2cd61ef7d5d3e3cafdd367b4bc5502e44cf43e99f7fc945321</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>alandi</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -608,7 +614,8 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Survey No. 669, Pune-Nashik Highway
+          <t>Survey No. 669, Pune-Nashik Highway_x000d_
+_x000d_
 Moshi Alandi Road</t>
         </is>
       </c>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641E5CEF-CCED-4FA0-8D34-8BD5974EB7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E72A63-85C0-43C3-A211-13F7364D767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9060" uniqueCount="2466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9059" uniqueCount="2466">
   <si>
     <t>employeeCode</t>
   </si>
@@ -55632,7 +55632,7 @@
         <v>9938097309</v>
       </c>
       <c r="D1412" s="3" t="s">
-        <v>1746</v>
+        <v>1807</v>
       </c>
       <c r="E1412" s="5" t="str">
         <f t="shared" ref="E1412:E1475" si="22">LOWER(SUBSTITUTE(B1412," ",""))&amp;"@gmail.com"</f>
@@ -55642,17 +55642,17 @@
         <v>15</v>
       </c>
       <c r="G1412" s="4" t="s">
-        <v>1169</v>
+        <v>1245</v>
       </c>
       <c r="H1412" s="6">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I1412" s="6"/>
       <c r="J1412" s="2">
         <v>229085</v>
       </c>
-      <c r="K1412" s="4" t="s">
-        <v>433</v>
+      <c r="K1412" s="4">
+        <v>22</v>
       </c>
     </row>
     <row r="1413" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E72A63-85C0-43C3-A211-13F7364D767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52B8BDF-0303-4806-8D06-CCCD13EF56B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9059" uniqueCount="2466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9061" uniqueCount="2466">
   <si>
     <t>employeeCode</t>
   </si>
@@ -7928,7 +7928,7 @@
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="49.6640625" bestFit="1" customWidth="1"/>
@@ -68913,13 +68913,18 @@
       <c r="F1808" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G1808" s="4"/>
-      <c r="H1808" s="6"/>
-      <c r="I1808" s="6"/>
+      <c r="G1808" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H1808" s="6">
+        <v>33</v>
+      </c>
       <c r="J1808" s="8">
         <v>232678</v>
       </c>
-      <c r="K1808" s="4"/>
+      <c r="K1808" t="s">
+        <v>2212</v>
+      </c>
     </row>
     <row r="1809" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1809" s="8">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52B8BDF-0303-4806-8D06-CCCD13EF56B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E72A63-85C0-43C3-A211-13F7364D767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9061" uniqueCount="2466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9059" uniqueCount="2466">
   <si>
     <t>employeeCode</t>
   </si>
@@ -7928,7 +7928,7 @@
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="49.6640625" bestFit="1" customWidth="1"/>
@@ -68913,18 +68913,13 @@
       <c r="F1808" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G1808" s="4" t="s">
-        <v>1125</v>
-      </c>
-      <c r="H1808" s="6">
-        <v>33</v>
-      </c>
+      <c r="G1808" s="4"/>
+      <c r="H1808" s="6"/>
+      <c r="I1808" s="6"/>
       <c r="J1808" s="8">
         <v>232678</v>
       </c>
-      <c r="K1808" t="s">
-        <v>2212</v>
-      </c>
+      <c r="K1808" s="4"/>
     </row>
     <row r="1809" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1809" s="8">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E72A63-85C0-43C3-A211-13F7364D767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1140B7F-8C0E-4658-981D-2DC7EF0B7443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9059" uniqueCount="2466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9061" uniqueCount="2467">
   <si>
     <t>employeeCode</t>
   </si>
@@ -7429,6 +7429,9 @@
   </si>
   <si>
     <t>Prem Arun Shinde</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -35231,7 +35234,9 @@
       <c r="H805" s="6">
         <v>11</v>
       </c>
-      <c r="I805" s="6"/>
+      <c r="I805" s="6" t="s">
+        <v>2466</v>
+      </c>
       <c r="J805" s="2">
         <v>129792</v>
       </c>
@@ -35634,17 +35639,17 @@
         <v>15</v>
       </c>
       <c r="G817" s="4" t="s">
-        <v>872</v>
+        <v>1314</v>
       </c>
       <c r="H817" s="6">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I817" s="6"/>
       <c r="J817" s="2">
         <v>129902</v>
       </c>
       <c r="K817" s="4" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
     </row>
     <row r="818" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -41066,12 +41071,16 @@
         <v>15</v>
       </c>
       <c r="G978" s="4"/>
-      <c r="H978" s="6"/>
+      <c r="H978" s="6">
+        <v>19</v>
+      </c>
       <c r="I978" s="6"/>
       <c r="J978" s="2">
         <v>134694</v>
       </c>
-      <c r="K978" s="4"/>
+      <c r="K978" s="4" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="979" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A979" s="2">

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10895" uniqueCount="4296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10897" uniqueCount="4297">
   <si>
     <t>employeeCode</t>
   </si>
@@ -12178,6 +12178,9 @@
     <t>Nageshvr vidyalay chikhali</t>
   </si>
   <si>
+    <t>TALWADE CHOWK</t>
+  </si>
+  <si>
     <t>CHAKAN  CHOWK</t>
   </si>
   <si>
@@ -12253,9 +12256,6 @@
     <t>TAWADE CHOWK</t>
   </si>
   <si>
-    <t>TALWADE CHOWK</t>
-  </si>
-  <si>
     <t>CHAKANCHOWK</t>
   </si>
   <si>
@@ -12689,6 +12689,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>SHAHUNAGAR</t>
@@ -13457,7 +13460,7 @@
         <v>48092</v>
       </c>
       <c r="K7" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -13547,7 +13550,7 @@
         <v>48198</v>
       </c>
       <c r="K10" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -13579,7 +13582,7 @@
         <v>48199</v>
       </c>
       <c r="K11" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -13611,7 +13614,7 @@
         <v>48202</v>
       </c>
       <c r="K12" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -13736,7 +13739,7 @@
         <v>53533</v>
       </c>
       <c r="K16" t="s">
-        <v>4227</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -13768,7 +13771,7 @@
         <v>55968</v>
       </c>
       <c r="K17" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -13832,7 +13835,7 @@
         <v>60026</v>
       </c>
       <c r="K19" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -13928,7 +13931,7 @@
         <v>60033</v>
       </c>
       <c r="K22" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -13960,7 +13963,7 @@
         <v>60039</v>
       </c>
       <c r="K23" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -14056,7 +14059,7 @@
         <v>60044</v>
       </c>
       <c r="K26" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -14088,7 +14091,7 @@
         <v>60046</v>
       </c>
       <c r="K27" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -14120,7 +14123,7 @@
         <v>60051</v>
       </c>
       <c r="K28" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -14184,7 +14187,7 @@
         <v>60137</v>
       </c>
       <c r="K30" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -14245,7 +14248,7 @@
         <v>60166</v>
       </c>
       <c r="K32" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -14277,7 +14280,7 @@
         <v>60175</v>
       </c>
       <c r="K33" t="s">
-        <v>4227</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -14309,7 +14312,7 @@
         <v>60176</v>
       </c>
       <c r="K34" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -14405,7 +14408,7 @@
         <v>60210</v>
       </c>
       <c r="K37" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -14501,7 +14504,7 @@
         <v>60215</v>
       </c>
       <c r="K40" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -14533,7 +14536,7 @@
         <v>60216</v>
       </c>
       <c r="K41" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -14591,7 +14594,7 @@
         <v>60218</v>
       </c>
       <c r="K43" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -14719,7 +14722,7 @@
         <v>60230</v>
       </c>
       <c r="K47" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -14751,7 +14754,7 @@
         <v>60232</v>
       </c>
       <c r="K48" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -14783,7 +14786,7 @@
         <v>60233</v>
       </c>
       <c r="K49" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -14844,7 +14847,7 @@
         <v>60240</v>
       </c>
       <c r="K51" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -14876,7 +14879,7 @@
         <v>60242</v>
       </c>
       <c r="K52" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -14908,7 +14911,7 @@
         <v>60247</v>
       </c>
       <c r="K53" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -15004,7 +15007,7 @@
         <v>60256</v>
       </c>
       <c r="K56" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -15036,7 +15039,7 @@
         <v>60258</v>
       </c>
       <c r="K57" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -15068,7 +15071,7 @@
         <v>60259</v>
       </c>
       <c r="K58" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -15257,7 +15260,7 @@
         <v>60355</v>
       </c>
       <c r="K64" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -15353,7 +15356,7 @@
         <v>60359</v>
       </c>
       <c r="K67" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -15417,7 +15420,7 @@
         <v>60361</v>
       </c>
       <c r="K69" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -15478,7 +15481,7 @@
         <v>60363</v>
       </c>
       <c r="K71" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -15542,7 +15545,7 @@
         <v>60367</v>
       </c>
       <c r="K73" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -15574,7 +15577,7 @@
         <v>60369</v>
       </c>
       <c r="K74" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -15606,7 +15609,7 @@
         <v>60370</v>
       </c>
       <c r="K75" t="s">
-        <v>4237</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -15734,7 +15737,7 @@
         <v>60376</v>
       </c>
       <c r="K79" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -15798,7 +15801,7 @@
         <v>60378</v>
       </c>
       <c r="K81" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -15830,7 +15833,7 @@
         <v>60379</v>
       </c>
       <c r="K82" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -15862,7 +15865,7 @@
         <v>60380</v>
       </c>
       <c r="K83" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -15926,7 +15929,7 @@
         <v>60382</v>
       </c>
       <c r="K85" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -15958,7 +15961,7 @@
         <v>60384</v>
       </c>
       <c r="K86" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -15990,7 +15993,7 @@
         <v>60386</v>
       </c>
       <c r="K87" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -16054,7 +16057,7 @@
         <v>60388</v>
       </c>
       <c r="K89" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -16086,7 +16089,7 @@
         <v>60389</v>
       </c>
       <c r="K90" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -16118,7 +16121,7 @@
         <v>60390</v>
       </c>
       <c r="K91" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -16150,7 +16153,7 @@
         <v>60391</v>
       </c>
       <c r="K92" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -16214,7 +16217,7 @@
         <v>60397</v>
       </c>
       <c r="K94" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -16246,7 +16249,7 @@
         <v>60398</v>
       </c>
       <c r="K95" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -16310,7 +16313,7 @@
         <v>60400</v>
       </c>
       <c r="K97" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -16342,7 +16345,7 @@
         <v>60401</v>
       </c>
       <c r="K98" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -16406,7 +16409,7 @@
         <v>60403</v>
       </c>
       <c r="K100" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -16438,7 +16441,7 @@
         <v>60404</v>
       </c>
       <c r="K101" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -16470,7 +16473,7 @@
         <v>60406</v>
       </c>
       <c r="K102" t="s">
-        <v>4242</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -16534,7 +16537,7 @@
         <v>60409</v>
       </c>
       <c r="K104" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -16566,7 +16569,7 @@
         <v>60410</v>
       </c>
       <c r="K105" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -16598,7 +16601,7 @@
         <v>60424</v>
       </c>
       <c r="K106" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -16630,7 +16633,7 @@
         <v>60455</v>
       </c>
       <c r="K107" t="s">
-        <v>4243</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -16662,7 +16665,7 @@
         <v>60463</v>
       </c>
       <c r="K108" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -16694,7 +16697,7 @@
         <v>60465</v>
       </c>
       <c r="K109" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -16758,7 +16761,7 @@
         <v>60473</v>
       </c>
       <c r="K111" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -16822,7 +16825,7 @@
         <v>60479</v>
       </c>
       <c r="K113" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -16918,7 +16921,7 @@
         <v>60483</v>
       </c>
       <c r="K116" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -17075,7 +17078,7 @@
         <v>60490</v>
       </c>
       <c r="K121" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -17203,7 +17206,7 @@
         <v>60495</v>
       </c>
       <c r="K125" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -17267,7 +17270,7 @@
         <v>60499</v>
       </c>
       <c r="K127" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -17299,7 +17302,7 @@
         <v>60501</v>
       </c>
       <c r="K128" t="s">
-        <v>4242</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -17331,7 +17334,7 @@
         <v>60502</v>
       </c>
       <c r="K129" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -17395,7 +17398,7 @@
         <v>60505</v>
       </c>
       <c r="K131" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -17491,7 +17494,7 @@
         <v>60508</v>
       </c>
       <c r="K134" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -17523,7 +17526,7 @@
         <v>60509</v>
       </c>
       <c r="K135" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -17587,7 +17590,7 @@
         <v>60512</v>
       </c>
       <c r="K137" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -17683,7 +17686,7 @@
         <v>60516</v>
       </c>
       <c r="K140" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -17715,7 +17718,7 @@
         <v>60517</v>
       </c>
       <c r="K141" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -17843,7 +17846,7 @@
         <v>60522</v>
       </c>
       <c r="K145" t="s">
-        <v>4237</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -17907,7 +17910,7 @@
         <v>60528</v>
       </c>
       <c r="K147" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -17939,7 +17942,7 @@
         <v>60531</v>
       </c>
       <c r="K148" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -17971,7 +17974,7 @@
         <v>60532</v>
       </c>
       <c r="K149" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -18003,7 +18006,7 @@
         <v>60539</v>
       </c>
       <c r="K150" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -18035,7 +18038,7 @@
         <v>60540</v>
       </c>
       <c r="K151" t="s">
-        <v>4245</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -18131,7 +18134,7 @@
         <v>60563</v>
       </c>
       <c r="K154" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -18163,7 +18166,7 @@
         <v>60568</v>
       </c>
       <c r="K155" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -18195,7 +18198,7 @@
         <v>60612</v>
       </c>
       <c r="K156" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -18227,7 +18230,7 @@
         <v>60613</v>
       </c>
       <c r="K157" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -18320,7 +18323,7 @@
         <v>60646</v>
       </c>
       <c r="K160" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -18352,7 +18355,7 @@
         <v>60658</v>
       </c>
       <c r="K161" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -18384,7 +18387,7 @@
         <v>60661</v>
       </c>
       <c r="K162" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -18544,7 +18547,7 @@
         <v>60712</v>
       </c>
       <c r="K167" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -18576,7 +18579,7 @@
         <v>60714</v>
       </c>
       <c r="K168" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -18608,7 +18611,7 @@
         <v>60729</v>
       </c>
       <c r="K169" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -18736,7 +18739,7 @@
         <v>60777</v>
       </c>
       <c r="K173" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -18768,7 +18771,7 @@
         <v>60778</v>
       </c>
       <c r="K174" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -18832,7 +18835,7 @@
         <v>60780</v>
       </c>
       <c r="K176" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -18864,7 +18867,7 @@
         <v>60781</v>
       </c>
       <c r="K177" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -18928,7 +18931,7 @@
         <v>60783</v>
       </c>
       <c r="K179" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -18960,7 +18963,7 @@
         <v>60784</v>
       </c>
       <c r="K180" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -18992,7 +18995,7 @@
         <v>60785</v>
       </c>
       <c r="K181" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -19024,7 +19027,7 @@
         <v>60787</v>
       </c>
       <c r="K182" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -19120,7 +19123,7 @@
         <v>60791</v>
       </c>
       <c r="K185" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -19152,7 +19155,7 @@
         <v>60792</v>
       </c>
       <c r="K186" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -19184,7 +19187,7 @@
         <v>60793</v>
       </c>
       <c r="K187" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -19248,7 +19251,7 @@
         <v>60795</v>
       </c>
       <c r="K189" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -19312,7 +19315,7 @@
         <v>60798</v>
       </c>
       <c r="K191" t="s">
-        <v>4243</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -19344,7 +19347,7 @@
         <v>60800</v>
       </c>
       <c r="K192" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -19504,7 +19507,7 @@
         <v>60807</v>
       </c>
       <c r="K197" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -19536,7 +19539,7 @@
         <v>60808</v>
       </c>
       <c r="K198" t="s">
-        <v>4246</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -19696,7 +19699,7 @@
         <v>60815</v>
       </c>
       <c r="K203" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -19760,7 +19763,7 @@
         <v>60857</v>
       </c>
       <c r="K205" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -19792,7 +19795,7 @@
         <v>60858</v>
       </c>
       <c r="K206" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -19824,7 +19827,7 @@
         <v>60859</v>
       </c>
       <c r="K207" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -19856,7 +19859,7 @@
         <v>60860</v>
       </c>
       <c r="K208" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -19888,7 +19891,7 @@
         <v>60870</v>
       </c>
       <c r="K209" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -19952,7 +19955,7 @@
         <v>60974</v>
       </c>
       <c r="K211" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -20016,7 +20019,7 @@
         <v>60981</v>
       </c>
       <c r="K213" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -20080,7 +20083,7 @@
         <v>61017</v>
       </c>
       <c r="K215" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -20112,7 +20115,7 @@
         <v>61020</v>
       </c>
       <c r="K216" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -20208,7 +20211,7 @@
         <v>61023</v>
       </c>
       <c r="K219" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -20272,7 +20275,7 @@
         <v>61025</v>
       </c>
       <c r="K221" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -20400,7 +20403,7 @@
         <v>61029</v>
       </c>
       <c r="K225" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -20432,7 +20435,7 @@
         <v>61030</v>
       </c>
       <c r="K226" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -20496,7 +20499,7 @@
         <v>61032</v>
       </c>
       <c r="K228" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -20592,7 +20595,7 @@
         <v>61037</v>
       </c>
       <c r="K231" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -20656,7 +20659,7 @@
         <v>61039</v>
       </c>
       <c r="K233" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -20816,7 +20819,7 @@
         <v>61045</v>
       </c>
       <c r="K238" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -20976,7 +20979,7 @@
         <v>61050</v>
       </c>
       <c r="K243" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -21008,7 +21011,7 @@
         <v>61051</v>
       </c>
       <c r="K244" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -21072,7 +21075,7 @@
         <v>61070</v>
       </c>
       <c r="K246" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -21136,7 +21139,7 @@
         <v>61073</v>
       </c>
       <c r="K248" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -21168,7 +21171,7 @@
         <v>61074</v>
       </c>
       <c r="K249" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -21264,7 +21267,7 @@
         <v>61077</v>
       </c>
       <c r="K252" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -21392,7 +21395,7 @@
         <v>61087</v>
       </c>
       <c r="K256" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -21424,7 +21427,7 @@
         <v>61088</v>
       </c>
       <c r="K257" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -21456,7 +21459,7 @@
         <v>61089</v>
       </c>
       <c r="K258" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -21488,7 +21491,7 @@
         <v>61090</v>
       </c>
       <c r="K259" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -21552,7 +21555,7 @@
         <v>61092</v>
       </c>
       <c r="K261" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -21584,7 +21587,7 @@
         <v>61093</v>
       </c>
       <c r="K262" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -21648,7 +21651,7 @@
         <v>61095</v>
       </c>
       <c r="K264" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -21744,7 +21747,7 @@
         <v>61099</v>
       </c>
       <c r="K267" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -21776,7 +21779,7 @@
         <v>61102</v>
       </c>
       <c r="K268" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -21808,7 +21811,7 @@
         <v>61124</v>
       </c>
       <c r="K269" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -21840,7 +21843,7 @@
         <v>61126</v>
       </c>
       <c r="K270" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -21872,7 +21875,7 @@
         <v>61137</v>
       </c>
       <c r="K271" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -21904,7 +21907,7 @@
         <v>61150</v>
       </c>
       <c r="K272" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -21936,7 +21939,7 @@
         <v>61154</v>
       </c>
       <c r="K273" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -21968,7 +21971,7 @@
         <v>61160</v>
       </c>
       <c r="K274" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -22000,7 +22003,7 @@
         <v>61168</v>
       </c>
       <c r="K275" t="s">
-        <v>4248</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -22032,7 +22035,7 @@
         <v>61177</v>
       </c>
       <c r="K276" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="277" spans="1:11">
@@ -22096,7 +22099,7 @@
         <v>61189</v>
       </c>
       <c r="K278" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -22128,7 +22131,7 @@
         <v>61191</v>
       </c>
       <c r="K279" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -22192,7 +22195,7 @@
         <v>61193</v>
       </c>
       <c r="K281" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -22224,7 +22227,7 @@
         <v>61214</v>
       </c>
       <c r="K282" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -22288,7 +22291,7 @@
         <v>61227</v>
       </c>
       <c r="K284" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -22320,7 +22323,7 @@
         <v>61249</v>
       </c>
       <c r="K285" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -22384,7 +22387,7 @@
         <v>61255</v>
       </c>
       <c r="K287" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -22512,7 +22515,7 @@
         <v>61260</v>
       </c>
       <c r="K291" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -22544,7 +22547,7 @@
         <v>61263</v>
       </c>
       <c r="K292" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -22672,7 +22675,7 @@
         <v>61273</v>
       </c>
       <c r="K296" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="297" spans="1:11">
@@ -22736,7 +22739,7 @@
         <v>61275</v>
       </c>
       <c r="K298" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="299" spans="1:11">
@@ -22768,7 +22771,7 @@
         <v>61278</v>
       </c>
       <c r="K299" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="300" spans="1:11">
@@ -22800,7 +22803,7 @@
         <v>61279</v>
       </c>
       <c r="K300" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="301" spans="1:11">
@@ -22864,7 +22867,7 @@
         <v>61281</v>
       </c>
       <c r="K302" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="303" spans="1:11">
@@ -22896,7 +22899,7 @@
         <v>61282</v>
       </c>
       <c r="K303" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="304" spans="1:11">
@@ -22928,7 +22931,7 @@
         <v>61283</v>
       </c>
       <c r="K304" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="305" spans="1:11">
@@ -22992,7 +22995,7 @@
         <v>61285</v>
       </c>
       <c r="K306" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="307" spans="1:11">
@@ -23024,7 +23027,7 @@
         <v>61287</v>
       </c>
       <c r="K307" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="308" spans="1:11">
@@ -23056,7 +23059,7 @@
         <v>61288</v>
       </c>
       <c r="K308" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="309" spans="1:11">
@@ -23120,7 +23123,7 @@
         <v>61291</v>
       </c>
       <c r="K310" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="311" spans="1:11">
@@ -23184,7 +23187,7 @@
         <v>61308</v>
       </c>
       <c r="K312" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="313" spans="1:11">
@@ -23216,7 +23219,7 @@
         <v>61311</v>
       </c>
       <c r="K313" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="314" spans="1:11">
@@ -23376,7 +23379,7 @@
         <v>61366</v>
       </c>
       <c r="K318" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="319" spans="1:11">
@@ -23408,7 +23411,7 @@
         <v>61373</v>
       </c>
       <c r="K319" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="320" spans="1:11">
@@ -23440,7 +23443,7 @@
         <v>61467</v>
       </c>
       <c r="K320" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="321" spans="1:11">
@@ -23472,7 +23475,7 @@
         <v>61469</v>
       </c>
       <c r="K321" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="322" spans="1:11">
@@ -23504,7 +23507,7 @@
         <v>61471</v>
       </c>
       <c r="K322" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="323" spans="1:11">
@@ -23536,7 +23539,7 @@
         <v>61473</v>
       </c>
       <c r="K323" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="324" spans="1:11">
@@ -23568,7 +23571,7 @@
         <v>61474</v>
       </c>
       <c r="K324" t="s">
-        <v>4242</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="325" spans="1:11">
@@ -23600,7 +23603,7 @@
         <v>61475</v>
       </c>
       <c r="K325" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="326" spans="1:11">
@@ -23632,7 +23635,7 @@
         <v>61481</v>
       </c>
       <c r="K326" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="327" spans="1:11">
@@ -23664,7 +23667,7 @@
         <v>61484</v>
       </c>
       <c r="K327" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="328" spans="1:11">
@@ -23728,7 +23731,7 @@
         <v>61491</v>
       </c>
       <c r="K329" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="330" spans="1:11">
@@ -23792,7 +23795,7 @@
         <v>61493</v>
       </c>
       <c r="K331" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="332" spans="1:11">
@@ -23824,7 +23827,7 @@
         <v>61494</v>
       </c>
       <c r="K332" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="333" spans="1:11">
@@ -23856,7 +23859,7 @@
         <v>61510</v>
       </c>
       <c r="K333" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="334" spans="1:11">
@@ -23888,7 +23891,7 @@
         <v>61527</v>
       </c>
       <c r="K334" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="335" spans="1:11">
@@ -23984,7 +23987,7 @@
         <v>61568</v>
       </c>
       <c r="K337" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="338" spans="1:11">
@@ -24048,7 +24051,7 @@
         <v>61591</v>
       </c>
       <c r="K339" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="340" spans="1:11">
@@ -24080,7 +24083,7 @@
         <v>61749</v>
       </c>
       <c r="K340" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="341" spans="1:11">
@@ -24112,7 +24115,7 @@
         <v>61750</v>
       </c>
       <c r="K341" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="342" spans="1:11">
@@ -24208,7 +24211,7 @@
         <v>61772</v>
       </c>
       <c r="K344" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="345" spans="1:11">
@@ -24272,7 +24275,7 @@
         <v>61775</v>
       </c>
       <c r="K346" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="347" spans="1:11">
@@ -24304,7 +24307,7 @@
         <v>61776</v>
       </c>
       <c r="K347" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="348" spans="1:11">
@@ -24336,7 +24339,7 @@
         <v>61782</v>
       </c>
       <c r="K348" t="s">
-        <v>4227</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="349" spans="1:11">
@@ -24368,7 +24371,7 @@
         <v>61783</v>
       </c>
       <c r="K349" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="350" spans="1:11">
@@ -24432,7 +24435,7 @@
         <v>61785</v>
       </c>
       <c r="K351" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="352" spans="1:11">
@@ -24464,7 +24467,7 @@
         <v>61786</v>
       </c>
       <c r="K352" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="353" spans="1:11">
@@ -24496,7 +24499,7 @@
         <v>61787</v>
       </c>
       <c r="K353" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="354" spans="1:11">
@@ -24560,7 +24563,7 @@
         <v>61789</v>
       </c>
       <c r="K355" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="356" spans="1:11">
@@ -24624,7 +24627,7 @@
         <v>61791</v>
       </c>
       <c r="K357" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="358" spans="1:11">
@@ -24656,7 +24659,7 @@
         <v>61792</v>
       </c>
       <c r="K358" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="359" spans="1:11">
@@ -24784,7 +24787,7 @@
         <v>61796</v>
       </c>
       <c r="K362" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="363" spans="1:11">
@@ -24880,7 +24883,7 @@
         <v>61819</v>
       </c>
       <c r="K365" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="366" spans="1:11">
@@ -24912,7 +24915,7 @@
         <v>61820</v>
       </c>
       <c r="K366" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="367" spans="1:11">
@@ -24976,7 +24979,7 @@
         <v>61822</v>
       </c>
       <c r="K368" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="369" spans="1:11">
@@ -25040,7 +25043,7 @@
         <v>61828</v>
       </c>
       <c r="K370" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="371" spans="1:11">
@@ -25136,7 +25139,7 @@
         <v>61883</v>
       </c>
       <c r="K373" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="374" spans="1:11">
@@ -25168,7 +25171,7 @@
         <v>61886</v>
       </c>
       <c r="K374" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="375" spans="1:11">
@@ -25200,7 +25203,7 @@
         <v>61887</v>
       </c>
       <c r="K375" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="376" spans="1:11">
@@ -25264,7 +25267,7 @@
         <v>61890</v>
       </c>
       <c r="K377" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="378" spans="1:11">
@@ -25296,7 +25299,7 @@
         <v>61893</v>
       </c>
       <c r="K378" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="379" spans="1:11">
@@ -25392,7 +25395,7 @@
         <v>61912</v>
       </c>
       <c r="K381" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="382" spans="1:11">
@@ -25424,7 +25427,7 @@
         <v>61915</v>
       </c>
       <c r="K382" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="383" spans="1:11">
@@ -25456,7 +25459,7 @@
         <v>61919</v>
       </c>
       <c r="K383" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="384" spans="1:11">
@@ -25520,7 +25523,7 @@
         <v>61922</v>
       </c>
       <c r="K385" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="386" spans="1:11">
@@ -25584,7 +25587,7 @@
         <v>61931</v>
       </c>
       <c r="K387" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="388" spans="1:11">
@@ -25616,7 +25619,7 @@
         <v>61933</v>
       </c>
       <c r="K388" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="389" spans="1:11">
@@ -25648,7 +25651,7 @@
         <v>61945</v>
       </c>
       <c r="K389" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="390" spans="1:11">
@@ -25680,7 +25683,7 @@
         <v>61948</v>
       </c>
       <c r="K390" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="391" spans="1:11">
@@ -25744,7 +25747,7 @@
         <v>61960</v>
       </c>
       <c r="K392" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="393" spans="1:11">
@@ -25808,7 +25811,7 @@
         <v>61964</v>
       </c>
       <c r="K394" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="395" spans="1:11">
@@ -25840,7 +25843,7 @@
         <v>61965</v>
       </c>
       <c r="K395" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="396" spans="1:11">
@@ -25904,7 +25907,7 @@
         <v>61970</v>
       </c>
       <c r="K397" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="398" spans="1:11">
@@ -25936,7 +25939,7 @@
         <v>62031</v>
       </c>
       <c r="K398" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="399" spans="1:11">
@@ -25968,7 +25971,7 @@
         <v>62067</v>
       </c>
       <c r="K399" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="400" spans="1:11">
@@ -26000,7 +26003,7 @@
         <v>62074</v>
       </c>
       <c r="K400" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="401" spans="1:11">
@@ -26096,7 +26099,7 @@
         <v>62117</v>
       </c>
       <c r="K403" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="404" spans="1:11">
@@ -26128,7 +26131,7 @@
         <v>62121</v>
       </c>
       <c r="K404" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="405" spans="1:11">
@@ -26160,7 +26163,7 @@
         <v>62140</v>
       </c>
       <c r="K405" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="406" spans="1:11">
@@ -26192,7 +26195,7 @@
         <v>62141</v>
       </c>
       <c r="K406" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="407" spans="1:11">
@@ -26256,7 +26259,7 @@
         <v>62144</v>
       </c>
       <c r="K408" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="409" spans="1:11">
@@ -26288,7 +26291,7 @@
         <v>62146</v>
       </c>
       <c r="K409" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="410" spans="1:11">
@@ -26320,7 +26323,7 @@
         <v>62147</v>
       </c>
       <c r="K410" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="411" spans="1:11">
@@ -26352,7 +26355,7 @@
         <v>62148</v>
       </c>
       <c r="K411" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="412" spans="1:11">
@@ -26384,7 +26387,7 @@
         <v>62149</v>
       </c>
       <c r="K412" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="413" spans="1:11">
@@ -26416,7 +26419,7 @@
         <v>62150</v>
       </c>
       <c r="K413" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="414" spans="1:11">
@@ -26448,7 +26451,7 @@
         <v>62178</v>
       </c>
       <c r="K414" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="415" spans="1:11">
@@ -26480,7 +26483,7 @@
         <v>62181</v>
       </c>
       <c r="K415" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="416" spans="1:11">
@@ -26512,7 +26515,7 @@
         <v>62183</v>
       </c>
       <c r="K416" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="417" spans="1:11">
@@ -26544,7 +26547,7 @@
         <v>62186</v>
       </c>
       <c r="K417" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="418" spans="1:11">
@@ -26576,7 +26579,7 @@
         <v>62191</v>
       </c>
       <c r="K418" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="419" spans="1:11">
@@ -26608,7 +26611,7 @@
         <v>62193</v>
       </c>
       <c r="K419" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="420" spans="1:11">
@@ -26672,7 +26675,7 @@
         <v>62195</v>
       </c>
       <c r="K421" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="422" spans="1:11">
@@ -26800,7 +26803,7 @@
         <v>62225</v>
       </c>
       <c r="K425" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="426" spans="1:11">
@@ -26832,7 +26835,7 @@
         <v>62233</v>
       </c>
       <c r="K426" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="427" spans="1:11">
@@ -26864,7 +26867,7 @@
         <v>62242</v>
       </c>
       <c r="K427" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="428" spans="1:11">
@@ -26896,7 +26899,7 @@
         <v>62256</v>
       </c>
       <c r="K428" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="429" spans="1:11">
@@ -26925,7 +26928,7 @@
         <v>62257</v>
       </c>
       <c r="K429" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="430" spans="1:11">
@@ -26957,7 +26960,7 @@
         <v>62259</v>
       </c>
       <c r="K430" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="431" spans="1:11">
@@ -27018,7 +27021,7 @@
         <v>62266</v>
       </c>
       <c r="K432" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="433" spans="1:11">
@@ -27050,7 +27053,7 @@
         <v>62334</v>
       </c>
       <c r="K433" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="434" spans="1:11">
@@ -27114,7 +27117,7 @@
         <v>62517</v>
       </c>
       <c r="K435" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="436" spans="1:11">
@@ -27146,7 +27149,7 @@
         <v>62529</v>
       </c>
       <c r="K436" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="437" spans="1:11">
@@ -27178,7 +27181,7 @@
         <v>62531</v>
       </c>
       <c r="K437" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="438" spans="1:11">
@@ -27210,7 +27213,7 @@
         <v>62532</v>
       </c>
       <c r="K438" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="439" spans="1:11">
@@ -27242,7 +27245,7 @@
         <v>62592</v>
       </c>
       <c r="K439" t="s">
-        <v>4249</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="440" spans="1:11">
@@ -27274,7 +27277,7 @@
         <v>62593</v>
       </c>
       <c r="K440" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="441" spans="1:11">
@@ -27530,7 +27533,7 @@
         <v>62633</v>
       </c>
       <c r="K448" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="449" spans="1:11">
@@ -27626,7 +27629,7 @@
         <v>62680</v>
       </c>
       <c r="K451" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="452" spans="1:11">
@@ -27722,7 +27725,7 @@
         <v>62683</v>
       </c>
       <c r="K454" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="455" spans="1:11">
@@ -27754,7 +27757,7 @@
         <v>62684</v>
       </c>
       <c r="K455" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="456" spans="1:11">
@@ -27818,7 +27821,7 @@
         <v>62724</v>
       </c>
       <c r="K457" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="458" spans="1:11">
@@ -27914,7 +27917,7 @@
         <v>62727</v>
       </c>
       <c r="K460" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="461" spans="1:11">
@@ -28042,7 +28045,7 @@
         <v>62762</v>
       </c>
       <c r="K464" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="465" spans="1:11">
@@ -28074,7 +28077,7 @@
         <v>62763</v>
       </c>
       <c r="K465" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="466" spans="1:11">
@@ -28234,7 +28237,7 @@
         <v>62794</v>
       </c>
       <c r="K470" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="471" spans="1:11">
@@ -28330,7 +28333,7 @@
         <v>62805</v>
       </c>
       <c r="K473" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="474" spans="1:11">
@@ -28362,7 +28365,7 @@
         <v>62812</v>
       </c>
       <c r="K474" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="475" spans="1:11">
@@ -28426,7 +28429,7 @@
         <v>62818</v>
       </c>
       <c r="K476" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="477" spans="1:11">
@@ -28458,7 +28461,7 @@
         <v>62835</v>
       </c>
       <c r="K477" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="478" spans="1:11">
@@ -28522,7 +28525,7 @@
         <v>62853</v>
       </c>
       <c r="K479" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="480" spans="1:11">
@@ -28554,7 +28557,7 @@
         <v>62855</v>
       </c>
       <c r="K480" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="481" spans="1:11">
@@ -28586,7 +28589,7 @@
         <v>62857</v>
       </c>
       <c r="K481" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="482" spans="1:11">
@@ -28618,7 +28621,7 @@
         <v>62858</v>
       </c>
       <c r="K482" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="483" spans="1:11">
@@ -28650,7 +28653,7 @@
         <v>62859</v>
       </c>
       <c r="K483" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="484" spans="1:11">
@@ -28714,7 +28717,7 @@
         <v>62862</v>
       </c>
       <c r="K485" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="486" spans="1:11">
@@ -28938,7 +28941,7 @@
         <v>62879</v>
       </c>
       <c r="K492" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="493" spans="1:11">
@@ -28970,7 +28973,7 @@
         <v>62880</v>
       </c>
       <c r="K493" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="494" spans="1:11">
@@ -29002,7 +29005,7 @@
         <v>62881</v>
       </c>
       <c r="K494" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="495" spans="1:11">
@@ -29034,7 +29037,7 @@
         <v>62882</v>
       </c>
       <c r="K495" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="496" spans="1:11">
@@ -29386,7 +29389,7 @@
         <v>62921</v>
       </c>
       <c r="K506" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="507" spans="1:11">
@@ -29450,7 +29453,7 @@
         <v>62923</v>
       </c>
       <c r="K508" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="509" spans="1:11">
@@ -29642,7 +29645,7 @@
         <v>62941</v>
       </c>
       <c r="K514" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="515" spans="1:11">
@@ -29738,7 +29741,7 @@
         <v>62959</v>
       </c>
       <c r="K517" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="518" spans="1:11">
@@ -29866,7 +29869,7 @@
         <v>62977</v>
       </c>
       <c r="K521" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="522" spans="1:11">
@@ -29898,7 +29901,7 @@
         <v>62979</v>
       </c>
       <c r="K522" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="523" spans="1:11">
@@ -29930,7 +29933,7 @@
         <v>62980</v>
       </c>
       <c r="K523" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="524" spans="1:11">
@@ -29962,7 +29965,7 @@
         <v>62983</v>
       </c>
       <c r="K524" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="525" spans="1:11">
@@ -30058,7 +30061,7 @@
         <v>62996</v>
       </c>
       <c r="K527" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="528" spans="1:11">
@@ -30090,7 +30093,7 @@
         <v>62997</v>
       </c>
       <c r="K528" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="529" spans="1:11">
@@ -30154,7 +30157,7 @@
         <v>63005</v>
       </c>
       <c r="K530" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="531" spans="1:11">
@@ -30186,7 +30189,7 @@
         <v>63006</v>
       </c>
       <c r="K531" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="532" spans="1:11">
@@ -30250,7 +30253,7 @@
         <v>63010</v>
       </c>
       <c r="K533" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="534" spans="1:11">
@@ -30442,7 +30445,7 @@
         <v>63018</v>
       </c>
       <c r="K539" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="540" spans="1:11">
@@ -30474,7 +30477,7 @@
         <v>63020</v>
       </c>
       <c r="K540" t="s">
-        <v>4250</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="541" spans="1:11">
@@ -30506,7 +30509,7 @@
         <v>63021</v>
       </c>
       <c r="K541" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="542" spans="1:11">
@@ -30538,7 +30541,7 @@
         <v>63022</v>
       </c>
       <c r="K542" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="543" spans="1:11">
@@ -30570,7 +30573,7 @@
         <v>63023</v>
       </c>
       <c r="K543" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="544" spans="1:11">
@@ -30602,7 +30605,7 @@
         <v>63025</v>
       </c>
       <c r="K544" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="545" spans="1:11">
@@ -30634,7 +30637,7 @@
         <v>63026</v>
       </c>
       <c r="K545" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="546" spans="1:11">
@@ -30666,7 +30669,7 @@
         <v>63028</v>
       </c>
       <c r="K546" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="547" spans="1:11">
@@ -30698,7 +30701,7 @@
         <v>63029</v>
       </c>
       <c r="K547" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="548" spans="1:11">
@@ -30762,7 +30765,7 @@
         <v>63031</v>
       </c>
       <c r="K549" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="550" spans="1:11">
@@ -30890,7 +30893,7 @@
         <v>63051</v>
       </c>
       <c r="K553" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="554" spans="1:11">
@@ -30922,7 +30925,7 @@
         <v>63052</v>
       </c>
       <c r="K554" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="555" spans="1:11">
@@ -30954,7 +30957,7 @@
         <v>63082</v>
       </c>
       <c r="K555" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="556" spans="1:11">
@@ -30986,7 +30989,7 @@
         <v>63085</v>
       </c>
       <c r="K556" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="557" spans="1:11">
@@ -31018,7 +31021,7 @@
         <v>63086</v>
       </c>
       <c r="K557" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="558" spans="1:11">
@@ -31050,7 +31053,7 @@
         <v>63091</v>
       </c>
       <c r="K558" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="559" spans="1:11">
@@ -31146,7 +31149,7 @@
         <v>63108</v>
       </c>
       <c r="K561" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="562" spans="1:11">
@@ -31242,7 +31245,7 @@
         <v>63130</v>
       </c>
       <c r="K564" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="565" spans="1:11">
@@ -31402,7 +31405,7 @@
         <v>63227</v>
       </c>
       <c r="K569" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="570" spans="1:11">
@@ -31530,7 +31533,7 @@
         <v>63338</v>
       </c>
       <c r="K573" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="574" spans="1:11">
@@ -31658,7 +31661,7 @@
         <v>63364</v>
       </c>
       <c r="K577" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="578" spans="1:11">
@@ -31690,7 +31693,7 @@
         <v>63372</v>
       </c>
       <c r="K578" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="579" spans="1:11">
@@ -31751,7 +31754,7 @@
         <v>63389</v>
       </c>
       <c r="K580" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="581" spans="1:11">
@@ -31783,7 +31786,7 @@
         <v>63391</v>
       </c>
       <c r="K581" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="582" spans="1:11">
@@ -31815,7 +31818,7 @@
         <v>63395</v>
       </c>
       <c r="K582" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="583" spans="1:11">
@@ -31879,7 +31882,7 @@
         <v>63398</v>
       </c>
       <c r="K584" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="585" spans="1:11">
@@ -31911,7 +31914,7 @@
         <v>63403</v>
       </c>
       <c r="K585" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="586" spans="1:11">
@@ -31943,7 +31946,7 @@
         <v>63405</v>
       </c>
       <c r="K586" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="587" spans="1:11">
@@ -31975,7 +31978,7 @@
         <v>63413</v>
       </c>
       <c r="K587" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="588" spans="1:11">
@@ -32071,7 +32074,7 @@
         <v>63479</v>
       </c>
       <c r="K590" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="591" spans="1:11">
@@ -32231,7 +32234,7 @@
         <v>63534</v>
       </c>
       <c r="K595" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="596" spans="1:11">
@@ -32263,7 +32266,7 @@
         <v>63536</v>
       </c>
       <c r="K596" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="597" spans="1:11">
@@ -32295,7 +32298,7 @@
         <v>63537</v>
       </c>
       <c r="K597" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="598" spans="1:11">
@@ -32359,7 +32362,7 @@
         <v>63539</v>
       </c>
       <c r="K599" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="600" spans="1:11">
@@ -32423,7 +32426,7 @@
         <v>63550</v>
       </c>
       <c r="K601" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="602" spans="1:11">
@@ -32519,7 +32522,7 @@
         <v>63613</v>
       </c>
       <c r="K604" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="605" spans="1:11">
@@ -32551,7 +32554,7 @@
         <v>63614</v>
       </c>
       <c r="K605" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="606" spans="1:11">
@@ -32615,7 +32618,7 @@
         <v>63617</v>
       </c>
       <c r="K607" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="608" spans="1:11">
@@ -32647,7 +32650,7 @@
         <v>63618</v>
       </c>
       <c r="K608" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="609" spans="1:11">
@@ -32711,7 +32714,7 @@
         <v>63684</v>
       </c>
       <c r="K610" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="611" spans="1:11">
@@ -32743,7 +32746,7 @@
         <v>63693</v>
       </c>
       <c r="K611" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="612" spans="1:11">
@@ -32775,7 +32778,7 @@
         <v>63797</v>
       </c>
       <c r="K612" t="s">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="613" spans="1:11">
@@ -32807,7 +32810,7 @@
         <v>63819</v>
       </c>
       <c r="K613" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="614" spans="1:11">
@@ -32871,7 +32874,7 @@
         <v>63842</v>
       </c>
       <c r="K615" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="616" spans="1:11">
@@ -32903,7 +32906,7 @@
         <v>63846</v>
       </c>
       <c r="K616" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="617" spans="1:11">
@@ -32935,7 +32938,7 @@
         <v>63850</v>
       </c>
       <c r="K617" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="618" spans="1:11">
@@ -32967,7 +32970,7 @@
         <v>63851</v>
       </c>
       <c r="K618" t="s">
-        <v>4242</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="619" spans="1:11">
@@ -32999,7 +33002,7 @@
         <v>63853</v>
       </c>
       <c r="K619" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="620" spans="1:11">
@@ -33063,7 +33066,7 @@
         <v>63873</v>
       </c>
       <c r="K621" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="622" spans="1:11">
@@ -33095,7 +33098,7 @@
         <v>63893</v>
       </c>
       <c r="K622" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="623" spans="1:11">
@@ -33127,7 +33130,7 @@
         <v>63894</v>
       </c>
       <c r="K623" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="624" spans="1:11">
@@ -33191,7 +33194,7 @@
         <v>63900</v>
       </c>
       <c r="K625" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="626" spans="1:11">
@@ -33223,7 +33226,7 @@
         <v>63954</v>
       </c>
       <c r="K626" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="627" spans="1:11">
@@ -33255,7 +33258,7 @@
         <v>63955</v>
       </c>
       <c r="K627" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="628" spans="1:11">
@@ -33287,7 +33290,7 @@
         <v>63959</v>
       </c>
       <c r="K628" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="629" spans="1:11">
@@ -33319,7 +33322,7 @@
         <v>63985</v>
       </c>
       <c r="K629" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="630" spans="1:11">
@@ -33351,7 +33354,7 @@
         <v>64060</v>
       </c>
       <c r="K630" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="631" spans="1:11">
@@ -33383,7 +33386,7 @@
         <v>64073</v>
       </c>
       <c r="K631" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="632" spans="1:11">
@@ -33415,7 +33418,7 @@
         <v>64077</v>
       </c>
       <c r="K632" t="s">
-        <v>4245</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="633" spans="1:11">
@@ -33479,7 +33482,7 @@
         <v>64109</v>
       </c>
       <c r="K634" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="635" spans="1:11">
@@ -33511,7 +33514,7 @@
         <v>64121</v>
       </c>
       <c r="K635" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="636" spans="1:11">
@@ -33543,7 +33546,7 @@
         <v>64122</v>
       </c>
       <c r="K636" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="637" spans="1:11">
@@ -33575,7 +33578,7 @@
         <v>64123</v>
       </c>
       <c r="K637" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="638" spans="1:11">
@@ -33607,7 +33610,7 @@
         <v>64124</v>
       </c>
       <c r="K638" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="639" spans="1:11">
@@ -33639,7 +33642,7 @@
         <v>64152</v>
       </c>
       <c r="K639" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="640" spans="1:11">
@@ -33703,7 +33706,7 @@
         <v>64197</v>
       </c>
       <c r="K641" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="642" spans="1:11">
@@ -33799,7 +33802,7 @@
         <v>64249</v>
       </c>
       <c r="K644" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="645" spans="1:11">
@@ -33895,7 +33898,7 @@
         <v>64397</v>
       </c>
       <c r="K647" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="648" spans="1:11">
@@ -33927,7 +33930,7 @@
         <v>64408</v>
       </c>
       <c r="K648" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="649" spans="1:11">
@@ -33991,7 +33994,7 @@
         <v>64410</v>
       </c>
       <c r="K650" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="651" spans="1:11">
@@ -34023,7 +34026,7 @@
         <v>64438</v>
       </c>
       <c r="K651" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="652" spans="1:11">
@@ -34055,7 +34058,7 @@
         <v>64449</v>
       </c>
       <c r="K652" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="653" spans="1:11">
@@ -34151,7 +34154,7 @@
         <v>64516</v>
       </c>
       <c r="K655" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="656" spans="1:11">
@@ -34247,7 +34250,7 @@
         <v>64548</v>
       </c>
       <c r="K658" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="659" spans="1:11">
@@ -34279,7 +34282,7 @@
         <v>64560</v>
       </c>
       <c r="K659" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="660" spans="1:11">
@@ -34372,7 +34375,7 @@
         <v>64762</v>
       </c>
       <c r="K662" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="663" spans="1:11">
@@ -34404,7 +34407,7 @@
         <v>64763</v>
       </c>
       <c r="K663" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="664" spans="1:11">
@@ -34500,7 +34503,7 @@
         <v>64769</v>
       </c>
       <c r="K666" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="667" spans="1:11">
@@ -34532,7 +34535,7 @@
         <v>64770</v>
       </c>
       <c r="K667" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="668" spans="1:11">
@@ -34596,7 +34599,7 @@
         <v>64777</v>
       </c>
       <c r="K669" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="670" spans="1:11">
@@ -34971,7 +34974,7 @@
         <v>65994</v>
       </c>
       <c r="K681" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="682" spans="1:11">
@@ -35003,7 +35006,7 @@
         <v>66555</v>
       </c>
       <c r="K682" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="683" spans="1:11">
@@ -35212,7 +35215,7 @@
         <v>99309</v>
       </c>
       <c r="K689" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="690" spans="1:11">
@@ -35244,7 +35247,7 @@
         <v>99310</v>
       </c>
       <c r="K690" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="691" spans="1:11">
@@ -35276,7 +35279,7 @@
         <v>101166</v>
       </c>
       <c r="K691" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="692" spans="1:11">
@@ -35308,7 +35311,7 @@
         <v>101316</v>
       </c>
       <c r="K692" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="693" spans="1:11">
@@ -35369,7 +35372,7 @@
         <v>101374</v>
       </c>
       <c r="K694" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="695" spans="1:11">
@@ -35497,7 +35500,7 @@
         <v>103231</v>
       </c>
       <c r="K698" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="699" spans="1:11">
@@ -35593,7 +35596,7 @@
         <v>103805</v>
       </c>
       <c r="K701" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="702" spans="1:11">
@@ -35817,7 +35820,7 @@
         <v>104796</v>
       </c>
       <c r="K708" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="709" spans="1:11">
@@ -35849,7 +35852,7 @@
         <v>105309</v>
       </c>
       <c r="K709" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="710" spans="1:11">
@@ -35913,7 +35916,7 @@
         <v>106029</v>
       </c>
       <c r="K711" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="712" spans="1:11">
@@ -35945,7 +35948,7 @@
         <v>106034</v>
       </c>
       <c r="K712" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="713" spans="1:11">
@@ -36009,7 +36012,7 @@
         <v>107137</v>
       </c>
       <c r="K714" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="715" spans="1:11">
@@ -36073,7 +36076,7 @@
         <v>107488</v>
       </c>
       <c r="K716" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="717" spans="1:11">
@@ -36105,7 +36108,7 @@
         <v>109957</v>
       </c>
       <c r="K717" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="718" spans="1:11">
@@ -36201,7 +36204,7 @@
         <v>110221</v>
       </c>
       <c r="K720" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="721" spans="1:11">
@@ -36265,7 +36268,7 @@
         <v>110513</v>
       </c>
       <c r="K722" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="723" spans="1:11">
@@ -36332,7 +36335,7 @@
         <v>111560</v>
       </c>
       <c r="K724" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="725" spans="1:11">
@@ -36364,7 +36367,7 @@
         <v>111606</v>
       </c>
       <c r="K725" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="726" spans="1:11">
@@ -36460,7 +36463,7 @@
         <v>112015</v>
       </c>
       <c r="K728" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="729" spans="1:11">
@@ -36492,7 +36495,7 @@
         <v>112563</v>
       </c>
       <c r="K729" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="730" spans="1:11">
@@ -36524,7 +36527,7 @@
         <v>113827</v>
       </c>
       <c r="K730" t="s">
-        <v>4242</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="731" spans="1:11">
@@ -36713,7 +36716,7 @@
         <v>118860</v>
       </c>
       <c r="K736" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="737" spans="1:11">
@@ -36745,7 +36748,7 @@
         <v>120077</v>
       </c>
       <c r="K737" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="738" spans="1:11">
@@ -36777,7 +36780,7 @@
         <v>120305</v>
       </c>
       <c r="K738" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="739" spans="1:11">
@@ -36809,7 +36812,7 @@
         <v>120627</v>
       </c>
       <c r="K739" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="740" spans="1:11">
@@ -36870,7 +36873,7 @@
         <v>121959</v>
       </c>
       <c r="K741" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="742" spans="1:11">
@@ -36902,7 +36905,7 @@
         <v>122272</v>
       </c>
       <c r="K742" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="743" spans="1:11">
@@ -37021,7 +37024,7 @@
         <v>122882</v>
       </c>
       <c r="K746" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="747" spans="1:11">
@@ -37053,7 +37056,7 @@
         <v>123288</v>
       </c>
       <c r="K747" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="748" spans="1:11">
@@ -37204,7 +37207,7 @@
         <v>127235</v>
       </c>
       <c r="K752" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="753" spans="1:11">
@@ -37236,7 +37239,7 @@
         <v>127268</v>
       </c>
       <c r="K753" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="754" spans="1:11">
@@ -37268,7 +37271,7 @@
         <v>127289</v>
       </c>
       <c r="K754" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="755" spans="1:11">
@@ -37428,7 +37431,7 @@
         <v>129297</v>
       </c>
       <c r="K759" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="760" spans="1:11">
@@ -37457,7 +37460,7 @@
         <v>129313</v>
       </c>
       <c r="K760" t="s">
-        <v>4251</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="761" spans="1:11">
@@ -37489,7 +37492,7 @@
         <v>129400</v>
       </c>
       <c r="K761" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="762" spans="1:11">
@@ -37521,7 +37524,7 @@
         <v>129401</v>
       </c>
       <c r="K762" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="763" spans="1:11">
@@ -37553,7 +37556,7 @@
         <v>129421</v>
       </c>
       <c r="K763" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="764" spans="1:11">
@@ -37617,7 +37620,7 @@
         <v>129444</v>
       </c>
       <c r="K765" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="766" spans="1:11">
@@ -37681,7 +37684,7 @@
         <v>129452</v>
       </c>
       <c r="K767" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="768" spans="1:11">
@@ -37713,7 +37716,7 @@
         <v>129454</v>
       </c>
       <c r="K768" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="769" spans="1:11">
@@ -37745,7 +37748,7 @@
         <v>129456</v>
       </c>
       <c r="K769" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="770" spans="1:11">
@@ -37873,7 +37876,7 @@
         <v>129464</v>
       </c>
       <c r="K773" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="774" spans="1:11">
@@ -37905,7 +37908,7 @@
         <v>129510</v>
       </c>
       <c r="K774" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="775" spans="1:11">
@@ -37937,7 +37940,7 @@
         <v>129525</v>
       </c>
       <c r="K775" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="776" spans="1:11">
@@ -38001,7 +38004,7 @@
         <v>129536</v>
       </c>
       <c r="K777" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="778" spans="1:11">
@@ -38097,7 +38100,7 @@
         <v>129569</v>
       </c>
       <c r="K780" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="781" spans="1:11">
@@ -38161,7 +38164,7 @@
         <v>129586</v>
       </c>
       <c r="K782" t="s">
-        <v>4228</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="783" spans="1:11">
@@ -38193,7 +38196,7 @@
         <v>129588</v>
       </c>
       <c r="K783" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="784" spans="1:11">
@@ -38225,7 +38228,7 @@
         <v>129589</v>
       </c>
       <c r="K784" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="785" spans="1:11">
@@ -38257,7 +38260,7 @@
         <v>129592</v>
       </c>
       <c r="K785" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="786" spans="1:11">
@@ -38321,7 +38324,7 @@
         <v>129594</v>
       </c>
       <c r="K787" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="788" spans="1:11">
@@ -38417,7 +38420,7 @@
         <v>129603</v>
       </c>
       <c r="K790" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="791" spans="1:11">
@@ -38449,7 +38452,7 @@
         <v>129605</v>
       </c>
       <c r="K791" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="792" spans="1:11">
@@ -38481,7 +38484,7 @@
         <v>129656</v>
       </c>
       <c r="K792" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="793" spans="1:11">
@@ -38670,7 +38673,7 @@
         <v>129692</v>
       </c>
       <c r="K798" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="799" spans="1:11">
@@ -38702,7 +38705,7 @@
         <v>129706</v>
       </c>
       <c r="K799" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="800" spans="1:11">
@@ -38766,7 +38769,7 @@
         <v>129769</v>
       </c>
       <c r="K801" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="802" spans="1:11">
@@ -38890,6 +38893,9 @@
       <c r="H805">
         <v>11</v>
       </c>
+      <c r="I805" t="s">
+        <v>4225</v>
+      </c>
       <c r="J805">
         <v>129792</v>
       </c>
@@ -38926,7 +38932,7 @@
         <v>129794</v>
       </c>
       <c r="K806" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="807" spans="1:11">
@@ -38990,7 +38996,7 @@
         <v>129796</v>
       </c>
       <c r="K808" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="809" spans="1:11">
@@ -39022,7 +39028,7 @@
         <v>129797</v>
       </c>
       <c r="K809" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="810" spans="1:11">
@@ -39054,7 +39060,7 @@
         <v>129798</v>
       </c>
       <c r="K810" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="811" spans="1:11">
@@ -39086,7 +39092,7 @@
         <v>129801</v>
       </c>
       <c r="K811" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="812" spans="1:11">
@@ -39118,7 +39124,7 @@
         <v>129863</v>
       </c>
       <c r="K812" t="s">
-        <v>4252</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="813" spans="1:11">
@@ -39150,7 +39156,7 @@
         <v>129867</v>
       </c>
       <c r="K813" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="814" spans="1:11">
@@ -39182,7 +39188,7 @@
         <v>129869</v>
       </c>
       <c r="K814" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="815" spans="1:11">
@@ -39269,16 +39275,16 @@
         <v>3754</v>
       </c>
       <c r="G817" t="s">
-        <v>3982</v>
+        <v>4054</v>
       </c>
       <c r="H817">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J817">
         <v>129902</v>
       </c>
       <c r="K817" t="s">
-        <v>4239</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="818" spans="1:11">
@@ -39365,7 +39371,7 @@
         <v>3754</v>
       </c>
       <c r="G820" t="s">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="H820">
         <v>33</v>
@@ -39470,7 +39476,7 @@
         <v>130079</v>
       </c>
       <c r="K823" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="824" spans="1:11">
@@ -39502,7 +39508,7 @@
         <v>130080</v>
       </c>
       <c r="K824" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="825" spans="1:11">
@@ -39534,7 +39540,7 @@
         <v>130082</v>
       </c>
       <c r="K825" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="826" spans="1:11">
@@ -39566,7 +39572,7 @@
         <v>130083</v>
       </c>
       <c r="K826" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="827" spans="1:11">
@@ -39653,7 +39659,7 @@
         <v>3754</v>
       </c>
       <c r="G829" t="s">
-        <v>4055</v>
+        <v>4056</v>
       </c>
       <c r="H829">
         <v>33</v>
@@ -39662,7 +39668,7 @@
         <v>130162</v>
       </c>
       <c r="K829" t="s">
-        <v>4253</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="830" spans="1:11">
@@ -39685,7 +39691,7 @@
         <v>3754</v>
       </c>
       <c r="G830" t="s">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="H830">
         <v>33</v>
@@ -39694,7 +39700,7 @@
         <v>130163</v>
       </c>
       <c r="K830" t="s">
-        <v>4253</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="831" spans="1:11">
@@ -39717,7 +39723,7 @@
         <v>3754</v>
       </c>
       <c r="G831" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="H831">
         <v>35</v>
@@ -39749,7 +39755,7 @@
         <v>3754</v>
       </c>
       <c r="G832" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="H832">
         <v>35</v>
@@ -39813,7 +39819,7 @@
         <v>3754</v>
       </c>
       <c r="G834" t="s">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="H834">
         <v>18</v>
@@ -39822,7 +39828,7 @@
         <v>130217</v>
       </c>
       <c r="K834" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="835" spans="1:11">
@@ -39845,7 +39851,7 @@
         <v>3754</v>
       </c>
       <c r="G835" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="H835">
         <v>18</v>
@@ -39854,7 +39860,7 @@
         <v>130218</v>
       </c>
       <c r="K835" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="836" spans="1:11">
@@ -39886,7 +39892,7 @@
         <v>130224</v>
       </c>
       <c r="K836" t="s">
-        <v>4235</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="837" spans="1:11">
@@ -39918,7 +39924,7 @@
         <v>130229</v>
       </c>
       <c r="K837" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="838" spans="1:11">
@@ -39950,7 +39956,7 @@
         <v>130230</v>
       </c>
       <c r="K838" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="839" spans="1:11">
@@ -39973,7 +39979,7 @@
         <v>3754</v>
       </c>
       <c r="G839" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="H839">
         <v>14</v>
@@ -39982,7 +39988,7 @@
         <v>130293</v>
       </c>
       <c r="K839" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="840" spans="1:11">
@@ -40014,7 +40020,7 @@
         <v>130294</v>
       </c>
       <c r="K840" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="841" spans="1:11">
@@ -40069,7 +40075,7 @@
         <v>3754</v>
       </c>
       <c r="G842" t="s">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="H842">
         <v>15</v>
@@ -40078,7 +40084,7 @@
         <v>130512</v>
       </c>
       <c r="K842" t="s">
-        <v>4254</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="843" spans="1:11">
@@ -40110,7 +40116,7 @@
         <v>130675</v>
       </c>
       <c r="K843" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="844" spans="1:11">
@@ -40165,7 +40171,7 @@
         <v>3754</v>
       </c>
       <c r="G845" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H845">
         <v>28</v>
@@ -40174,7 +40180,7 @@
         <v>130816</v>
       </c>
       <c r="K845" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="846" spans="1:11">
@@ -40197,7 +40203,7 @@
         <v>3754</v>
       </c>
       <c r="G846" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="H846">
         <v>34</v>
@@ -40206,7 +40212,7 @@
         <v>130828</v>
       </c>
       <c r="K846" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="847" spans="1:11">
@@ -40238,7 +40244,7 @@
         <v>130843</v>
       </c>
       <c r="K847" t="s">
-        <v>4253</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="848" spans="1:11">
@@ -40270,7 +40276,7 @@
         <v>130844</v>
       </c>
       <c r="K848" t="s">
-        <v>4253</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="849" spans="1:11">
@@ -40293,7 +40299,7 @@
         <v>3754</v>
       </c>
       <c r="G849" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="H849">
         <v>35</v>
@@ -40334,7 +40340,7 @@
         <v>131086</v>
       </c>
       <c r="K850" t="s">
-        <v>4226</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="851" spans="1:11">
@@ -40357,7 +40363,7 @@
         <v>3754</v>
       </c>
       <c r="G851" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H851">
         <v>33</v>
@@ -40366,7 +40372,7 @@
         <v>131160</v>
       </c>
       <c r="K851" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="852" spans="1:11">
@@ -40389,7 +40395,7 @@
         <v>3754</v>
       </c>
       <c r="G852" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H852">
         <v>33</v>
@@ -40398,7 +40404,7 @@
         <v>131161</v>
       </c>
       <c r="K852" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="853" spans="1:11">
@@ -40462,7 +40468,7 @@
         <v>131180</v>
       </c>
       <c r="K854" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="855" spans="1:11">
@@ -40494,7 +40500,7 @@
         <v>131213</v>
       </c>
       <c r="K855" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="856" spans="1:11">
@@ -40549,7 +40555,7 @@
         <v>3754</v>
       </c>
       <c r="G857" t="s">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="H857">
         <v>17</v>
@@ -40558,7 +40564,7 @@
         <v>131286</v>
       </c>
       <c r="K857" t="s">
-        <v>4255</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="858" spans="1:11">
@@ -40581,7 +40587,7 @@
         <v>3754</v>
       </c>
       <c r="G858" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H858">
         <v>31</v>
@@ -40590,7 +40596,7 @@
         <v>131312</v>
       </c>
       <c r="K858" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="859" spans="1:11">
@@ -40613,7 +40619,7 @@
         <v>3754</v>
       </c>
       <c r="G859" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H859">
         <v>31</v>
@@ -40622,7 +40628,7 @@
         <v>131314</v>
       </c>
       <c r="K859" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="860" spans="1:11">
@@ -40654,7 +40660,7 @@
         <v>131374</v>
       </c>
       <c r="K860" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="861" spans="1:11">
@@ -40718,7 +40724,7 @@
         <v>131389</v>
       </c>
       <c r="K862" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="863" spans="1:11">
@@ -40750,7 +40756,7 @@
         <v>131390</v>
       </c>
       <c r="K863" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="864" spans="1:11">
@@ -40773,7 +40779,7 @@
         <v>3754</v>
       </c>
       <c r="G864" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="H864">
         <v>23</v>
@@ -40805,7 +40811,7 @@
         <v>3754</v>
       </c>
       <c r="G865" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
       <c r="H865">
         <v>22</v>
@@ -40846,7 +40852,7 @@
         <v>131562</v>
       </c>
       <c r="K866" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="867" spans="1:11">
@@ -40910,7 +40916,7 @@
         <v>131697</v>
       </c>
       <c r="K868" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="869" spans="1:11">
@@ -40933,7 +40939,7 @@
         <v>3754</v>
       </c>
       <c r="G869" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="H869">
         <v>35</v>
@@ -40997,7 +41003,7 @@
         <v>3754</v>
       </c>
       <c r="G871" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="H871">
         <v>33</v>
@@ -41006,7 +41012,7 @@
         <v>131810</v>
       </c>
       <c r="K871" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="872" spans="1:11">
@@ -41038,7 +41044,7 @@
         <v>131811</v>
       </c>
       <c r="K872" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="873" spans="1:11">
@@ -41061,7 +41067,7 @@
         <v>3754</v>
       </c>
       <c r="G873" t="s">
-        <v>4070</v>
+        <v>4071</v>
       </c>
       <c r="H873">
         <v>10</v>
@@ -41070,7 +41076,7 @@
         <v>131870</v>
       </c>
       <c r="K873" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="874" spans="1:11">
@@ -41093,7 +41099,7 @@
         <v>3754</v>
       </c>
       <c r="G874" t="s">
-        <v>4070</v>
+        <v>4071</v>
       </c>
       <c r="H874">
         <v>35</v>
@@ -41125,7 +41131,7 @@
         <v>3754</v>
       </c>
       <c r="G875" t="s">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="H875">
         <v>35</v>
@@ -41189,7 +41195,7 @@
         <v>3754</v>
       </c>
       <c r="G877" t="s">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="H877">
         <v>20</v>
@@ -41198,7 +41204,7 @@
         <v>131975</v>
       </c>
       <c r="K877" t="s">
-        <v>4256</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="878" spans="1:11">
@@ -41253,7 +41259,7 @@
         <v>3754</v>
       </c>
       <c r="G879" t="s">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="H879">
         <v>14</v>
@@ -41262,7 +41268,7 @@
         <v>132027</v>
       </c>
       <c r="K879" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="880" spans="1:11">
@@ -41326,7 +41332,7 @@
         <v>132029</v>
       </c>
       <c r="K881" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="882" spans="1:11">
@@ -41413,7 +41419,7 @@
         <v>3754</v>
       </c>
       <c r="G884" t="s">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="H884">
         <v>33</v>
@@ -41422,7 +41428,7 @@
         <v>132107</v>
       </c>
       <c r="K884" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="885" spans="1:11">
@@ -41445,7 +41451,7 @@
         <v>3754</v>
       </c>
       <c r="G885" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H885">
         <v>31</v>
@@ -41454,7 +41460,7 @@
         <v>132112</v>
       </c>
       <c r="K885" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="886" spans="1:11">
@@ -41477,7 +41483,7 @@
         <v>3754</v>
       </c>
       <c r="G886" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H886">
         <v>33</v>
@@ -41486,7 +41492,7 @@
         <v>132113</v>
       </c>
       <c r="K886" t="s">
-        <v>4257</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="887" spans="1:11">
@@ -41518,7 +41524,7 @@
         <v>132125</v>
       </c>
       <c r="K887" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="888" spans="1:11">
@@ -41541,7 +41547,7 @@
         <v>3754</v>
       </c>
       <c r="G888" t="s">
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="H888">
         <v>11</v>
@@ -41582,7 +41588,7 @@
         <v>132164</v>
       </c>
       <c r="K889" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="890" spans="1:11">
@@ -41605,7 +41611,7 @@
         <v>3754</v>
       </c>
       <c r="G890" t="s">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="H890">
         <v>35</v>
@@ -41637,7 +41643,7 @@
         <v>3754</v>
       </c>
       <c r="G891" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H891">
         <v>33</v>
@@ -41678,7 +41684,7 @@
         <v>132170</v>
       </c>
       <c r="K892" t="s">
-        <v>4258</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="893" spans="1:11">
@@ -41710,7 +41716,7 @@
         <v>132171</v>
       </c>
       <c r="K893" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="894" spans="1:11">
@@ -41733,7 +41739,7 @@
         <v>3754</v>
       </c>
       <c r="G894" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H894">
         <v>31</v>
@@ -41742,7 +41748,7 @@
         <v>132172</v>
       </c>
       <c r="K894" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="895" spans="1:11">
@@ -41829,7 +41835,7 @@
         <v>3754</v>
       </c>
       <c r="G897" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H897">
         <v>30</v>
@@ -41838,7 +41844,7 @@
         <v>132182</v>
       </c>
       <c r="K897" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="898" spans="1:11">
@@ -41861,7 +41867,7 @@
         <v>3754</v>
       </c>
       <c r="G898" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="H898">
         <v>14</v>
@@ -41870,7 +41876,7 @@
         <v>132183</v>
       </c>
       <c r="K898" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="899" spans="1:11">
@@ -41893,7 +41899,7 @@
         <v>3754</v>
       </c>
       <c r="G899" t="s">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="H899">
         <v>19</v>
@@ -41925,7 +41931,7 @@
         <v>3754</v>
       </c>
       <c r="G900" t="s">
-        <v>4079</v>
+        <v>4054</v>
       </c>
       <c r="H900">
         <v>19</v>
@@ -42140,7 +42146,7 @@
         <v>132270</v>
       </c>
       <c r="K907" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="908" spans="1:11">
@@ -42204,7 +42210,7 @@
         <v>132311</v>
       </c>
       <c r="K909" t="s">
-        <v>4259</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="910" spans="1:11">
@@ -42236,7 +42242,7 @@
         <v>132367</v>
       </c>
       <c r="K910" t="s">
-        <v>4253</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="911" spans="1:11">
@@ -42268,7 +42274,7 @@
         <v>132424</v>
       </c>
       <c r="K911" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="912" spans="1:11">
@@ -42300,7 +42306,7 @@
         <v>132425</v>
       </c>
       <c r="K912" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="913" spans="1:11">
@@ -42323,7 +42329,7 @@
         <v>3754</v>
       </c>
       <c r="G913" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="H913">
         <v>19</v>
@@ -42364,7 +42370,7 @@
         <v>132446</v>
       </c>
       <c r="K914" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="915" spans="1:11">
@@ -42419,7 +42425,7 @@
         <v>3754</v>
       </c>
       <c r="G916" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H916">
         <v>31</v>
@@ -42428,7 +42434,7 @@
         <v>132676</v>
       </c>
       <c r="K916" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="917" spans="1:11">
@@ -42451,7 +42457,7 @@
         <v>3754</v>
       </c>
       <c r="G917" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H917">
         <v>33</v>
@@ -42515,7 +42521,7 @@
         <v>3754</v>
       </c>
       <c r="G919" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H919">
         <v>33</v>
@@ -42556,7 +42562,7 @@
         <v>132872</v>
       </c>
       <c r="K920" t="s">
-        <v>4258</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="921" spans="1:11">
@@ -42588,7 +42594,7 @@
         <v>133129</v>
       </c>
       <c r="K921" t="s">
-        <v>4260</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="922" spans="1:11">
@@ -42620,7 +42626,7 @@
         <v>133130</v>
       </c>
       <c r="K922" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="923" spans="1:11">
@@ -42684,7 +42690,7 @@
         <v>133362</v>
       </c>
       <c r="K924" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="925" spans="1:11">
@@ -42716,7 +42722,7 @@
         <v>133467</v>
       </c>
       <c r="K925" t="s">
-        <v>4257</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="926" spans="1:11">
@@ -42748,7 +42754,7 @@
         <v>133468</v>
       </c>
       <c r="K926" t="s">
-        <v>4257</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="927" spans="1:11">
@@ -42780,7 +42786,7 @@
         <v>133469</v>
       </c>
       <c r="K927" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="928" spans="1:11">
@@ -42812,7 +42818,7 @@
         <v>133470</v>
       </c>
       <c r="K928" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="929" spans="1:11">
@@ -42844,7 +42850,7 @@
         <v>133479</v>
       </c>
       <c r="K929" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="930" spans="1:11">
@@ -42876,7 +42882,7 @@
         <v>133544</v>
       </c>
       <c r="K930" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="931" spans="1:11">
@@ -42908,7 +42914,7 @@
         <v>133545</v>
       </c>
       <c r="K931" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="932" spans="1:11">
@@ -42940,7 +42946,7 @@
         <v>133546</v>
       </c>
       <c r="K932" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="933" spans="1:11">
@@ -42972,7 +42978,7 @@
         <v>133607</v>
       </c>
       <c r="K933" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="934" spans="1:11">
@@ -43004,7 +43010,7 @@
         <v>133738</v>
       </c>
       <c r="K934" t="s">
-        <v>4261</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="935" spans="1:11">
@@ -43082,7 +43088,7 @@
         <v>3754</v>
       </c>
       <c r="G937" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H937">
         <v>33</v>
@@ -43123,7 +43129,7 @@
         <v>133780</v>
       </c>
       <c r="K938" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="939" spans="1:11">
@@ -43178,7 +43184,7 @@
         <v>133915</v>
       </c>
       <c r="K940" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="941" spans="1:11">
@@ -43210,7 +43216,7 @@
         <v>133979</v>
       </c>
       <c r="K941" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="942" spans="1:11">
@@ -43265,7 +43271,7 @@
         <v>134012</v>
       </c>
       <c r="K943" t="s">
-        <v>4258</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="944" spans="1:11">
@@ -43384,7 +43390,7 @@
         <v>134091</v>
       </c>
       <c r="K947" t="s">
-        <v>4262</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="948" spans="1:11">
@@ -43480,7 +43486,7 @@
         <v>134209</v>
       </c>
       <c r="K950" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="951" spans="1:11">
@@ -43512,7 +43518,7 @@
         <v>134211</v>
       </c>
       <c r="K951" t="s">
-        <v>4257</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="952" spans="1:11">
@@ -43576,7 +43582,7 @@
         <v>134218</v>
       </c>
       <c r="K953" t="s">
-        <v>4257</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="954" spans="1:11">
@@ -43622,7 +43628,7 @@
         <v>3754</v>
       </c>
       <c r="G955" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="H955">
         <v>34</v>
@@ -43631,7 +43637,7 @@
         <v>134229</v>
       </c>
       <c r="K955" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="956" spans="1:11">
@@ -43654,7 +43660,7 @@
         <v>3754</v>
       </c>
       <c r="G956" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H956">
         <v>10</v>
@@ -43663,7 +43669,7 @@
         <v>134231</v>
       </c>
       <c r="K956" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="957" spans="1:11">
@@ -43695,7 +43701,7 @@
         <v>134233</v>
       </c>
       <c r="K957" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="958" spans="1:11">
@@ -43759,7 +43765,7 @@
         <v>134330</v>
       </c>
       <c r="K959" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="960" spans="1:11">
@@ -43814,7 +43820,7 @@
         <v>3754</v>
       </c>
       <c r="G961" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="H961">
         <v>34</v>
@@ -43823,7 +43829,7 @@
         <v>134363</v>
       </c>
       <c r="K961" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="962" spans="1:11">
@@ -44047,7 +44053,7 @@
         <v>134679</v>
       </c>
       <c r="K968" t="s">
-        <v>4263</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="969" spans="1:11">
@@ -44111,7 +44117,7 @@
         <v>134681</v>
       </c>
       <c r="K970" t="s">
-        <v>4263</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="971" spans="1:11">
@@ -44357,8 +44363,14 @@
       <c r="F978" t="s">
         <v>3754</v>
       </c>
+      <c r="H978">
+        <v>19</v>
+      </c>
       <c r="J978">
         <v>134694</v>
+      </c>
+      <c r="K978" t="s">
+        <v>4088</v>
       </c>
     </row>
     <row r="979" spans="1:11">
@@ -44390,7 +44402,7 @@
         <v>134718</v>
       </c>
       <c r="K979" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="980" spans="1:11">
@@ -44710,7 +44722,7 @@
         <v>134731</v>
       </c>
       <c r="K989" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="990" spans="1:11">
@@ -44742,7 +44754,7 @@
         <v>134732</v>
       </c>
       <c r="K990" t="s">
-        <v>4257</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="991" spans="1:11">
@@ -44765,7 +44777,7 @@
         <v>3754</v>
       </c>
       <c r="G991" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="H991">
         <v>33</v>
@@ -44774,7 +44786,7 @@
         <v>134733</v>
       </c>
       <c r="K991" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="992" spans="1:11">
@@ -44829,7 +44841,7 @@
         <v>3754</v>
       </c>
       <c r="G993" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H993">
         <v>30</v>
@@ -44838,7 +44850,7 @@
         <v>134735</v>
       </c>
       <c r="K993" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="994" spans="1:11">
@@ -44861,7 +44873,7 @@
         <v>3754</v>
       </c>
       <c r="G994" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H994">
         <v>30</v>
@@ -44870,7 +44882,7 @@
         <v>134736</v>
       </c>
       <c r="K994" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="995" spans="1:11">
@@ -44989,7 +45001,7 @@
         <v>3754</v>
       </c>
       <c r="G998" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H998">
         <v>30</v>
@@ -44998,7 +45010,7 @@
         <v>134742</v>
       </c>
       <c r="K998" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="999" spans="1:11">
@@ -45094,7 +45106,7 @@
         <v>134746</v>
       </c>
       <c r="K1001" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1002" spans="1:11">
@@ -45158,7 +45170,7 @@
         <v>134748</v>
       </c>
       <c r="K1003" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1004" spans="1:11">
@@ -45181,7 +45193,7 @@
         <v>3754</v>
       </c>
       <c r="G1004" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1004">
         <v>31</v>
@@ -45190,7 +45202,7 @@
         <v>134749</v>
       </c>
       <c r="K1004" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1005" spans="1:11">
@@ -45245,7 +45257,7 @@
         <v>134751</v>
       </c>
       <c r="K1006" t="s">
-        <v>4253</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="1007" spans="1:11">
@@ -45277,7 +45289,7 @@
         <v>134752</v>
       </c>
       <c r="K1007" t="s">
-        <v>4253</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="1008" spans="1:11">
@@ -45309,7 +45321,7 @@
         <v>134753</v>
       </c>
       <c r="K1008" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1009" spans="1:11">
@@ -45341,7 +45353,7 @@
         <v>134754</v>
       </c>
       <c r="K1009" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1010" spans="1:11">
@@ -45373,7 +45385,7 @@
         <v>134755</v>
       </c>
       <c r="K1010" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1011" spans="1:11">
@@ -45405,7 +45417,7 @@
         <v>134757</v>
       </c>
       <c r="K1011" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1012" spans="1:11">
@@ -45437,7 +45449,7 @@
         <v>134758</v>
       </c>
       <c r="K1012" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1013" spans="1:11">
@@ -45469,7 +45481,7 @@
         <v>134759</v>
       </c>
       <c r="K1013" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1014" spans="1:11">
@@ -45501,7 +45513,7 @@
         <v>134760</v>
       </c>
       <c r="K1014" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1015" spans="1:11">
@@ -45533,7 +45545,7 @@
         <v>134761</v>
       </c>
       <c r="K1015" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1016" spans="1:11">
@@ -45556,7 +45568,7 @@
         <v>3754</v>
       </c>
       <c r="G1016" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1016">
         <v>30</v>
@@ -45565,7 +45577,7 @@
         <v>134762</v>
       </c>
       <c r="K1016" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1017" spans="1:11">
@@ -45588,7 +45600,7 @@
         <v>3754</v>
       </c>
       <c r="G1017" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1017">
         <v>31</v>
@@ -45597,7 +45609,7 @@
         <v>134763</v>
       </c>
       <c r="K1017" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1018" spans="1:11">
@@ -45629,7 +45641,7 @@
         <v>134764</v>
       </c>
       <c r="K1018" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1019" spans="1:11">
@@ -45661,7 +45673,7 @@
         <v>134765</v>
       </c>
       <c r="K1019" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1020" spans="1:11">
@@ -45684,7 +45696,7 @@
         <v>3754</v>
       </c>
       <c r="G1020" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1020">
         <v>31</v>
@@ -45693,7 +45705,7 @@
         <v>134766</v>
       </c>
       <c r="K1020" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1021" spans="1:11">
@@ -45757,7 +45769,7 @@
         <v>134768</v>
       </c>
       <c r="K1022" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1023" spans="1:11">
@@ -45789,7 +45801,7 @@
         <v>134769</v>
       </c>
       <c r="K1023" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1024" spans="1:11">
@@ -45821,7 +45833,7 @@
         <v>134770</v>
       </c>
       <c r="K1024" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1025" spans="1:11">
@@ -45844,7 +45856,7 @@
         <v>3754</v>
       </c>
       <c r="G1025" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H1025">
         <v>19</v>
@@ -45853,7 +45865,7 @@
         <v>134771</v>
       </c>
       <c r="K1025" t="s">
-        <v>4264</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1026" spans="1:11">
@@ -45876,7 +45888,7 @@
         <v>3754</v>
       </c>
       <c r="G1026" t="s">
-        <v>4079</v>
+        <v>4054</v>
       </c>
       <c r="H1026">
         <v>19</v>
@@ -45917,7 +45929,7 @@
         <v>134773</v>
       </c>
       <c r="K1027" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1028" spans="1:11">
@@ -45949,7 +45961,7 @@
         <v>134774</v>
       </c>
       <c r="K1028" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1029" spans="1:11">
@@ -45981,7 +45993,7 @@
         <v>134775</v>
       </c>
       <c r="K1029" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1030" spans="1:11">
@@ -46013,7 +46025,7 @@
         <v>134776</v>
       </c>
       <c r="K1030" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1031" spans="1:11">
@@ -46141,7 +46153,7 @@
         <v>134789</v>
       </c>
       <c r="K1034" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1035" spans="1:11">
@@ -46173,7 +46185,7 @@
         <v>134791</v>
       </c>
       <c r="K1035" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1036" spans="1:11">
@@ -46205,7 +46217,7 @@
         <v>134792</v>
       </c>
       <c r="K1036" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1037" spans="1:11">
@@ -46292,7 +46304,7 @@
         <v>134824</v>
       </c>
       <c r="K1039" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1040" spans="1:11">
@@ -46420,7 +46432,7 @@
         <v>134828</v>
       </c>
       <c r="K1043" t="s">
-        <v>4265</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1044" spans="1:11">
@@ -46484,7 +46496,7 @@
         <v>134830</v>
       </c>
       <c r="K1045" t="s">
-        <v>4266</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1046" spans="1:11">
@@ -46516,7 +46528,7 @@
         <v>134831</v>
       </c>
       <c r="K1046" t="s">
-        <v>4265</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1047" spans="1:11">
@@ -46609,7 +46621,7 @@
         <v>134836</v>
       </c>
       <c r="K1049" t="s">
-        <v>4265</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1050" spans="1:11">
@@ -46673,7 +46685,7 @@
         <v>134838</v>
       </c>
       <c r="K1051" t="s">
-        <v>4265</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1052" spans="1:11">
@@ -46769,7 +46781,7 @@
         <v>134842</v>
       </c>
       <c r="K1054" t="s">
-        <v>4265</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1055" spans="1:11">
@@ -46833,7 +46845,7 @@
         <v>134844</v>
       </c>
       <c r="K1056" t="s">
-        <v>4265</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1057" spans="1:11">
@@ -46865,7 +46877,7 @@
         <v>134845</v>
       </c>
       <c r="K1057" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1058" spans="1:11">
@@ -46993,7 +47005,7 @@
         <v>134860</v>
       </c>
       <c r="K1061" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1062" spans="1:11">
@@ -47039,7 +47051,7 @@
         <v>3754</v>
       </c>
       <c r="G1063" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1063">
         <v>33</v>
@@ -47080,7 +47092,7 @@
         <v>134865</v>
       </c>
       <c r="K1064" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1065" spans="1:11">
@@ -47112,7 +47124,7 @@
         <v>134866</v>
       </c>
       <c r="K1065" t="s">
-        <v>4265</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1066" spans="1:11">
@@ -47213,7 +47225,7 @@
         <v>3754</v>
       </c>
       <c r="G1069" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="H1069">
         <v>23</v>
@@ -47222,7 +47234,7 @@
         <v>134872</v>
       </c>
       <c r="K1069" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1070" spans="1:11">
@@ -47277,7 +47289,7 @@
         <v>3754</v>
       </c>
       <c r="G1071" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1071">
         <v>31</v>
@@ -47332,7 +47344,7 @@
         <v>3754</v>
       </c>
       <c r="G1073" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1073">
         <v>31</v>
@@ -47448,7 +47460,7 @@
         <v>134885</v>
       </c>
       <c r="K1077" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1078" spans="1:11">
@@ -47544,7 +47556,7 @@
         <v>134893</v>
       </c>
       <c r="K1080" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1081" spans="1:11">
@@ -47576,7 +47588,7 @@
         <v>134894</v>
       </c>
       <c r="K1081" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1082" spans="1:11">
@@ -47599,7 +47611,7 @@
         <v>3754</v>
       </c>
       <c r="G1082" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1082">
         <v>31</v>
@@ -47608,7 +47620,7 @@
         <v>134896</v>
       </c>
       <c r="K1082" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1083" spans="1:11">
@@ -47631,7 +47643,7 @@
         <v>3754</v>
       </c>
       <c r="G1083" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1083">
         <v>31</v>
@@ -47640,7 +47652,7 @@
         <v>134897</v>
       </c>
       <c r="K1083" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1084" spans="1:11">
@@ -47663,7 +47675,7 @@
         <v>3754</v>
       </c>
       <c r="G1084" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1084">
         <v>31</v>
@@ -47672,7 +47684,7 @@
         <v>134899</v>
       </c>
       <c r="K1084" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1085" spans="1:11">
@@ -47695,7 +47707,7 @@
         <v>3754</v>
       </c>
       <c r="G1085" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1085">
         <v>31</v>
@@ -47704,7 +47716,7 @@
         <v>134900</v>
       </c>
       <c r="K1085" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1086" spans="1:11">
@@ -47727,7 +47739,7 @@
         <v>3754</v>
       </c>
       <c r="G1086" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1086">
         <v>31</v>
@@ -47736,7 +47748,7 @@
         <v>134902</v>
       </c>
       <c r="K1086" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1087" spans="1:11">
@@ -47768,7 +47780,7 @@
         <v>134904</v>
       </c>
       <c r="K1087" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1088" spans="1:11">
@@ -47791,7 +47803,7 @@
         <v>3754</v>
       </c>
       <c r="G1088" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1088">
         <v>31</v>
@@ -47800,7 +47812,7 @@
         <v>134905</v>
       </c>
       <c r="K1088" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1089" spans="1:11">
@@ -47832,7 +47844,7 @@
         <v>134907</v>
       </c>
       <c r="K1089" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1090" spans="1:11">
@@ -47864,7 +47876,7 @@
         <v>134932</v>
       </c>
       <c r="K1090" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1091" spans="1:11">
@@ -47896,7 +47908,7 @@
         <v>134933</v>
       </c>
       <c r="K1091" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1092" spans="1:11">
@@ -47928,7 +47940,7 @@
         <v>134935</v>
       </c>
       <c r="K1092" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1093" spans="1:11">
@@ -47960,7 +47972,7 @@
         <v>134936</v>
       </c>
       <c r="K1093" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1094" spans="1:11">
@@ -47983,7 +47995,7 @@
         <v>3754</v>
       </c>
       <c r="G1094" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1094">
         <v>31</v>
@@ -47992,7 +48004,7 @@
         <v>134938</v>
       </c>
       <c r="K1094" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1095" spans="1:11">
@@ -48015,7 +48027,7 @@
         <v>3754</v>
       </c>
       <c r="G1095" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1095">
         <v>30</v>
@@ -48024,7 +48036,7 @@
         <v>134939</v>
       </c>
       <c r="K1095" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1096" spans="1:11">
@@ -48047,7 +48059,7 @@
         <v>3754</v>
       </c>
       <c r="G1096" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1096">
         <v>30</v>
@@ -48056,7 +48068,7 @@
         <v>134940</v>
       </c>
       <c r="K1096" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1097" spans="1:11">
@@ -48184,7 +48196,7 @@
         <v>135014</v>
       </c>
       <c r="K1100" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1101" spans="1:11">
@@ -48262,7 +48274,7 @@
         <v>3754</v>
       </c>
       <c r="G1103" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1103">
         <v>33</v>
@@ -48271,7 +48283,7 @@
         <v>135020</v>
       </c>
       <c r="K1103" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1104" spans="1:11">
@@ -48294,7 +48306,7 @@
         <v>3754</v>
       </c>
       <c r="G1104" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1104">
         <v>33</v>
@@ -48303,7 +48315,7 @@
         <v>135021</v>
       </c>
       <c r="K1104" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1105" spans="1:11">
@@ -48425,7 +48437,7 @@
         <v>135049</v>
       </c>
       <c r="K1108" t="s">
-        <v>4259</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="1109" spans="1:11">
@@ -48457,7 +48469,7 @@
         <v>135050</v>
       </c>
       <c r="K1109" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1110" spans="1:11">
@@ -48489,7 +48501,7 @@
         <v>135051</v>
       </c>
       <c r="K1110" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1111" spans="1:11">
@@ -48512,7 +48524,7 @@
         <v>3754</v>
       </c>
       <c r="G1111" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1111">
         <v>33</v>
@@ -48521,7 +48533,7 @@
         <v>135053</v>
       </c>
       <c r="K1111" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1112" spans="1:11">
@@ -48544,7 +48556,7 @@
         <v>3754</v>
       </c>
       <c r="G1112" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1112">
         <v>33</v>
@@ -48553,7 +48565,7 @@
         <v>135054</v>
       </c>
       <c r="K1112" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1113" spans="1:11">
@@ -48576,7 +48588,7 @@
         <v>3754</v>
       </c>
       <c r="G1113" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1113">
         <v>33</v>
@@ -48585,7 +48597,7 @@
         <v>135055</v>
       </c>
       <c r="K1113" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1114" spans="1:11">
@@ -48617,7 +48629,7 @@
         <v>135056</v>
       </c>
       <c r="K1114" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1115" spans="1:11">
@@ -48649,7 +48661,7 @@
         <v>135057</v>
       </c>
       <c r="K1115" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1116" spans="1:11">
@@ -48681,7 +48693,7 @@
         <v>135058</v>
       </c>
       <c r="K1116" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1117" spans="1:11">
@@ -48713,7 +48725,7 @@
         <v>135059</v>
       </c>
       <c r="K1117" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1118" spans="1:11">
@@ -48745,7 +48757,7 @@
         <v>135060</v>
       </c>
       <c r="K1118" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1119" spans="1:11">
@@ -48777,7 +48789,7 @@
         <v>135061</v>
       </c>
       <c r="K1119" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1120" spans="1:11">
@@ -48809,7 +48821,7 @@
         <v>135062</v>
       </c>
       <c r="K1120" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1121" spans="1:11">
@@ -48841,7 +48853,7 @@
         <v>135063</v>
       </c>
       <c r="K1121" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1122" spans="1:11">
@@ -48873,7 +48885,7 @@
         <v>135064</v>
       </c>
       <c r="K1122" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1123" spans="1:11">
@@ -48905,7 +48917,7 @@
         <v>135065</v>
       </c>
       <c r="K1123" t="s">
-        <v>4259</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="1124" spans="1:11">
@@ -48937,7 +48949,7 @@
         <v>135066</v>
       </c>
       <c r="K1124" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1125" spans="1:11">
@@ -48969,7 +48981,7 @@
         <v>135067</v>
       </c>
       <c r="K1125" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1126" spans="1:11">
@@ -49001,7 +49013,7 @@
         <v>135068</v>
       </c>
       <c r="K1126" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1127" spans="1:11">
@@ -49033,7 +49045,7 @@
         <v>135076</v>
       </c>
       <c r="K1127" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1128" spans="1:11">
@@ -49056,7 +49068,7 @@
         <v>3754</v>
       </c>
       <c r="G1128" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1128">
         <v>33</v>
@@ -49065,7 +49077,7 @@
         <v>135077</v>
       </c>
       <c r="K1128" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1129" spans="1:11">
@@ -49225,7 +49237,7 @@
         <v>135092</v>
       </c>
       <c r="K1133" t="s">
-        <v>4267</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1134" spans="1:11">
@@ -49257,7 +49269,7 @@
         <v>135093</v>
       </c>
       <c r="K1134" t="s">
-        <v>4267</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1135" spans="1:11">
@@ -49289,7 +49301,7 @@
         <v>135095</v>
       </c>
       <c r="K1135" t="s">
-        <v>4267</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1136" spans="1:11">
@@ -49321,7 +49333,7 @@
         <v>135096</v>
       </c>
       <c r="K1136" t="s">
-        <v>4267</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1137" spans="1:11">
@@ -49353,7 +49365,7 @@
         <v>135097</v>
       </c>
       <c r="K1137" t="s">
-        <v>4267</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1138" spans="1:11">
@@ -49385,7 +49397,7 @@
         <v>135098</v>
       </c>
       <c r="K1138" t="s">
-        <v>4267</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1139" spans="1:11">
@@ -49536,7 +49548,7 @@
         <v>135103</v>
       </c>
       <c r="K1143" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1144" spans="1:11">
@@ -49568,7 +49580,7 @@
         <v>135108</v>
       </c>
       <c r="K1144" t="s">
-        <v>4267</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1145" spans="1:11">
@@ -49632,7 +49644,7 @@
         <v>135110</v>
       </c>
       <c r="K1146" t="s">
-        <v>4268</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="1147" spans="1:11">
@@ -49696,7 +49708,7 @@
         <v>135113</v>
       </c>
       <c r="K1148" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1149" spans="1:11">
@@ -49728,7 +49740,7 @@
         <v>135117</v>
       </c>
       <c r="K1149" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1150" spans="1:11">
@@ -49760,7 +49772,7 @@
         <v>135118</v>
       </c>
       <c r="K1150" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1151" spans="1:11">
@@ -49792,7 +49804,7 @@
         <v>135119</v>
       </c>
       <c r="K1151" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1152" spans="1:11">
@@ -49888,7 +49900,7 @@
         <v>135125</v>
       </c>
       <c r="K1154" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1155" spans="1:11">
@@ -49920,7 +49932,7 @@
         <v>135126</v>
       </c>
       <c r="K1155" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1156" spans="1:11">
@@ -49966,7 +49978,7 @@
         <v>3754</v>
       </c>
       <c r="G1157" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1157">
         <v>31</v>
@@ -49975,7 +49987,7 @@
         <v>135129</v>
       </c>
       <c r="K1157" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1158" spans="1:11">
@@ -49998,7 +50010,7 @@
         <v>3754</v>
       </c>
       <c r="G1158" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1158">
         <v>31</v>
@@ -50007,7 +50019,7 @@
         <v>135130</v>
       </c>
       <c r="K1158" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1159" spans="1:11">
@@ -50030,7 +50042,7 @@
         <v>3754</v>
       </c>
       <c r="G1159" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1159">
         <v>31</v>
@@ -50039,7 +50051,7 @@
         <v>135131</v>
       </c>
       <c r="K1159" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1160" spans="1:11">
@@ -50062,7 +50074,7 @@
         <v>3754</v>
       </c>
       <c r="G1160" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1160">
         <v>31</v>
@@ -50071,7 +50083,7 @@
         <v>135132</v>
       </c>
       <c r="K1160" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1161" spans="1:11">
@@ -50094,7 +50106,7 @@
         <v>3754</v>
       </c>
       <c r="G1161" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1161">
         <v>31</v>
@@ -50103,7 +50115,7 @@
         <v>135133</v>
       </c>
       <c r="K1161" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1162" spans="1:11">
@@ -50149,7 +50161,7 @@
         <v>3754</v>
       </c>
       <c r="G1163" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1163">
         <v>31</v>
@@ -50158,7 +50170,7 @@
         <v>135178</v>
       </c>
       <c r="K1163" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1164" spans="1:11">
@@ -50181,7 +50193,7 @@
         <v>3754</v>
       </c>
       <c r="G1164" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1164">
         <v>31</v>
@@ -50190,7 +50202,7 @@
         <v>135180</v>
       </c>
       <c r="K1164" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1165" spans="1:11">
@@ -50286,7 +50298,7 @@
         <v>135262</v>
       </c>
       <c r="K1167" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1168" spans="1:11">
@@ -50318,7 +50330,7 @@
         <v>135266</v>
       </c>
       <c r="K1168" t="s">
-        <v>4269</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="1169" spans="1:11">
@@ -50350,7 +50362,7 @@
         <v>135267</v>
       </c>
       <c r="K1169" t="s">
-        <v>4270</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="1170" spans="1:11">
@@ -50373,7 +50385,7 @@
         <v>3754</v>
       </c>
       <c r="G1170" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1170">
         <v>30</v>
@@ -50382,7 +50394,7 @@
         <v>135268</v>
       </c>
       <c r="K1170" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1171" spans="1:11">
@@ -50446,7 +50458,7 @@
         <v>135335</v>
       </c>
       <c r="K1172" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1173" spans="1:11">
@@ -50606,7 +50618,7 @@
         <v>135343</v>
       </c>
       <c r="K1177" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1178" spans="1:11">
@@ -50757,7 +50769,7 @@
         <v>3754</v>
       </c>
       <c r="G1182" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1182">
         <v>31</v>
@@ -50766,7 +50778,7 @@
         <v>135426</v>
       </c>
       <c r="K1182" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1183" spans="1:11">
@@ -50789,7 +50801,7 @@
         <v>3754</v>
       </c>
       <c r="G1183" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1183">
         <v>31</v>
@@ -50798,7 +50810,7 @@
         <v>135427</v>
       </c>
       <c r="K1183" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1184" spans="1:11">
@@ -50821,7 +50833,7 @@
         <v>3754</v>
       </c>
       <c r="G1184" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1184">
         <v>31</v>
@@ -50830,7 +50842,7 @@
         <v>135429</v>
       </c>
       <c r="K1184" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1185" spans="1:11">
@@ -50853,7 +50865,7 @@
         <v>3754</v>
       </c>
       <c r="G1185" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1185">
         <v>31</v>
@@ -50862,7 +50874,7 @@
         <v>135430</v>
       </c>
       <c r="K1185" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1186" spans="1:11">
@@ -50894,7 +50906,7 @@
         <v>135431</v>
       </c>
       <c r="K1186" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1187" spans="1:11">
@@ -50917,7 +50929,7 @@
         <v>3754</v>
       </c>
       <c r="G1187" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1187">
         <v>31</v>
@@ -50926,7 +50938,7 @@
         <v>135432</v>
       </c>
       <c r="K1187" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1188" spans="1:11">
@@ -50949,7 +50961,7 @@
         <v>3754</v>
       </c>
       <c r="G1188" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1188">
         <v>31</v>
@@ -50958,7 +50970,7 @@
         <v>135433</v>
       </c>
       <c r="K1188" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1189" spans="1:11">
@@ -50981,7 +50993,7 @@
         <v>3754</v>
       </c>
       <c r="G1189" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1189">
         <v>31</v>
@@ -50990,7 +51002,7 @@
         <v>135435</v>
       </c>
       <c r="K1189" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1190" spans="1:11">
@@ -51022,7 +51034,7 @@
         <v>135436</v>
       </c>
       <c r="K1190" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1191" spans="1:11">
@@ -51118,7 +51130,7 @@
         <v>135439</v>
       </c>
       <c r="K1193" t="s">
-        <v>4264</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1194" spans="1:11">
@@ -51150,7 +51162,7 @@
         <v>135440</v>
       </c>
       <c r="K1194" t="s">
-        <v>4271</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="1195" spans="1:11">
@@ -51406,7 +51418,7 @@
         <v>135452</v>
       </c>
       <c r="K1202" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1203" spans="1:11">
@@ -51461,7 +51473,7 @@
         <v>3754</v>
       </c>
       <c r="G1204" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1204">
         <v>33</v>
@@ -51470,7 +51482,7 @@
         <v>135475</v>
       </c>
       <c r="K1204" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1205" spans="1:11">
@@ -51502,7 +51514,7 @@
         <v>135584</v>
       </c>
       <c r="K1205" t="s">
-        <v>4272</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="1206" spans="1:11">
@@ -51557,7 +51569,7 @@
         <v>135586</v>
       </c>
       <c r="K1207" t="s">
-        <v>4272</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="1208" spans="1:11">
@@ -51589,7 +51601,7 @@
         <v>135589</v>
       </c>
       <c r="K1208" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1209" spans="1:11">
@@ -51653,7 +51665,7 @@
         <v>135593</v>
       </c>
       <c r="K1210" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1211" spans="1:11">
@@ -51685,7 +51697,7 @@
         <v>135594</v>
       </c>
       <c r="K1211" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1212" spans="1:11">
@@ -51717,7 +51729,7 @@
         <v>135595</v>
       </c>
       <c r="K1212" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1213" spans="1:11">
@@ -51772,7 +51784,7 @@
         <v>3754</v>
       </c>
       <c r="G1214" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1214">
         <v>31</v>
@@ -51781,7 +51793,7 @@
         <v>135598</v>
       </c>
       <c r="K1214" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1215" spans="1:11">
@@ -51804,7 +51816,7 @@
         <v>3754</v>
       </c>
       <c r="G1215" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1215">
         <v>31</v>
@@ -51813,7 +51825,7 @@
         <v>135601</v>
       </c>
       <c r="K1215" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1216" spans="1:11">
@@ -51836,7 +51848,7 @@
         <v>3754</v>
       </c>
       <c r="G1216" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1216">
         <v>31</v>
@@ -51845,7 +51857,7 @@
         <v>135610</v>
       </c>
       <c r="K1216" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1217" spans="1:11">
@@ -51877,7 +51889,7 @@
         <v>135622</v>
       </c>
       <c r="K1217" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1218" spans="1:11">
@@ -51932,7 +51944,7 @@
         <v>3754</v>
       </c>
       <c r="G1219" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H1219">
         <v>19</v>
@@ -51941,7 +51953,7 @@
         <v>135672</v>
       </c>
       <c r="K1219" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="1220" spans="1:11">
@@ -52028,7 +52040,7 @@
         <v>3754</v>
       </c>
       <c r="G1222" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H1222">
         <v>19</v>
@@ -52037,7 +52049,7 @@
         <v>135676</v>
       </c>
       <c r="K1222" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="1223" spans="1:11">
@@ -52060,7 +52072,7 @@
         <v>3754</v>
       </c>
       <c r="G1223" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="H1223">
         <v>33</v>
@@ -52069,7 +52081,7 @@
         <v>135677</v>
       </c>
       <c r="K1223" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1224" spans="1:11">
@@ -52133,7 +52145,7 @@
         <v>135685</v>
       </c>
       <c r="K1225" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1226" spans="1:11">
@@ -52197,7 +52209,7 @@
         <v>135687</v>
       </c>
       <c r="K1227" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1228" spans="1:11">
@@ -52357,7 +52369,7 @@
         <v>135720</v>
       </c>
       <c r="K1232" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1233" spans="1:11">
@@ -52389,7 +52401,7 @@
         <v>135721</v>
       </c>
       <c r="K1233" t="s">
-        <v>4273</v>
+        <v>4274</v>
       </c>
     </row>
     <row r="1234" spans="1:11">
@@ -52421,7 +52433,7 @@
         <v>135799</v>
       </c>
       <c r="K1234" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1235" spans="1:11">
@@ -52453,7 +52465,7 @@
         <v>135801</v>
       </c>
       <c r="K1235" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1236" spans="1:11">
@@ -52517,7 +52529,7 @@
         <v>135803</v>
       </c>
       <c r="K1237" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1238" spans="1:11">
@@ -52549,7 +52561,7 @@
         <v>135805</v>
       </c>
       <c r="K1238" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1239" spans="1:11">
@@ -52770,7 +52782,7 @@
         <v>135887</v>
       </c>
       <c r="K1248" t="s">
-        <v>4274</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="1249" spans="1:11">
@@ -52810,7 +52822,7 @@
         <v>3754</v>
       </c>
       <c r="G1250" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1250">
         <v>33</v>
@@ -52839,7 +52851,7 @@
         <v>3754</v>
       </c>
       <c r="G1251" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1251">
         <v>33</v>
@@ -52897,7 +52909,7 @@
         <v>3754</v>
       </c>
       <c r="G1253" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="H1253">
         <v>33</v>
@@ -52906,7 +52918,7 @@
         <v>135952</v>
       </c>
       <c r="K1253" t="s">
-        <v>4275</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="1254" spans="1:11">
@@ -52984,7 +52996,7 @@
         <v>3754</v>
       </c>
       <c r="G1256" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1256">
         <v>30</v>
@@ -52993,7 +53005,7 @@
         <v>221714</v>
       </c>
       <c r="K1256" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1257" spans="1:11">
@@ -53057,7 +53069,7 @@
         <v>221760</v>
       </c>
       <c r="K1258" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1259" spans="1:11">
@@ -53080,7 +53092,7 @@
         <v>3754</v>
       </c>
       <c r="G1259" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="H1259">
         <v>14</v>
@@ -53089,7 +53101,7 @@
         <v>221766</v>
       </c>
       <c r="K1259" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1260" spans="1:11">
@@ -53153,7 +53165,7 @@
         <v>221850</v>
       </c>
       <c r="K1261" t="s">
-        <v>4232</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1262" spans="1:11">
@@ -53185,7 +53197,7 @@
         <v>221867</v>
       </c>
       <c r="K1262" t="s">
-        <v>4242</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="1263" spans="1:11">
@@ -53249,7 +53261,7 @@
         <v>222179</v>
       </c>
       <c r="K1264" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="1265" spans="1:11">
@@ -53313,7 +53325,7 @@
         <v>222211</v>
       </c>
       <c r="K1266" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1267" spans="1:11">
@@ -53345,7 +53357,7 @@
         <v>222235</v>
       </c>
       <c r="K1267" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1268" spans="1:11">
@@ -53377,7 +53389,7 @@
         <v>222249</v>
       </c>
       <c r="K1268" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1269" spans="1:11">
@@ -53441,7 +53453,7 @@
         <v>222320</v>
       </c>
       <c r="K1270" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1271" spans="1:11">
@@ -53505,7 +53517,7 @@
         <v>222462</v>
       </c>
       <c r="K1272" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="1273" spans="1:11">
@@ -53537,7 +53549,7 @@
         <v>222731</v>
       </c>
       <c r="K1273" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1274" spans="1:11">
@@ -53569,7 +53581,7 @@
         <v>223136</v>
       </c>
       <c r="K1274" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1275" spans="1:11">
@@ -53601,7 +53613,7 @@
         <v>223181</v>
       </c>
       <c r="K1275" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1276" spans="1:11">
@@ -53633,7 +53645,7 @@
         <v>223217</v>
       </c>
       <c r="K1276" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1277" spans="1:11">
@@ -53665,7 +53677,7 @@
         <v>223259</v>
       </c>
       <c r="K1277" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1278" spans="1:11">
@@ -53697,7 +53709,7 @@
         <v>223268</v>
       </c>
       <c r="K1278" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1279" spans="1:11">
@@ -53729,7 +53741,7 @@
         <v>223326</v>
       </c>
       <c r="K1279" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1280" spans="1:11">
@@ -53761,7 +53773,7 @@
         <v>223333</v>
       </c>
       <c r="K1280" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1281" spans="1:11">
@@ -53793,7 +53805,7 @@
         <v>223446</v>
       </c>
       <c r="K1281" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1282" spans="1:11">
@@ -53857,7 +53869,7 @@
         <v>223582</v>
       </c>
       <c r="K1283" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1284" spans="1:11">
@@ -53889,7 +53901,7 @@
         <v>223603</v>
       </c>
       <c r="K1284" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1285" spans="1:11">
@@ -53921,7 +53933,7 @@
         <v>223719</v>
       </c>
       <c r="K1285" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1286" spans="1:11">
@@ -53944,7 +53956,7 @@
         <v>3754</v>
       </c>
       <c r="G1286" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="H1286">
         <v>14</v>
@@ -53953,7 +53965,7 @@
         <v>223779</v>
       </c>
       <c r="K1286" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1287" spans="1:11">
@@ -54017,7 +54029,7 @@
         <v>223925</v>
       </c>
       <c r="K1288" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1289" spans="1:11">
@@ -54049,7 +54061,7 @@
         <v>223939</v>
       </c>
       <c r="K1289" t="s">
-        <v>4231</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="1290" spans="1:11">
@@ -54081,7 +54093,7 @@
         <v>223977</v>
       </c>
       <c r="K1290" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1291" spans="1:11">
@@ -54113,7 +54125,7 @@
         <v>224038</v>
       </c>
       <c r="K1291" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1292" spans="1:11">
@@ -54145,7 +54157,7 @@
         <v>224071</v>
       </c>
       <c r="K1292" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1293" spans="1:11">
@@ -54177,7 +54189,7 @@
         <v>224368</v>
       </c>
       <c r="K1293" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1294" spans="1:11">
@@ -54209,7 +54221,7 @@
         <v>224383</v>
       </c>
       <c r="K1294" t="s">
-        <v>4240</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="1295" spans="1:11">
@@ -54232,7 +54244,7 @@
         <v>3754</v>
       </c>
       <c r="G1295" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1295">
         <v>30</v>
@@ -54241,7 +54253,7 @@
         <v>224398</v>
       </c>
       <c r="K1295" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1296" spans="1:11">
@@ -54273,7 +54285,7 @@
         <v>224508</v>
       </c>
       <c r="K1296" t="s">
-        <v>4276</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="1297" spans="1:11">
@@ -54305,7 +54317,7 @@
         <v>224516</v>
       </c>
       <c r="K1297" t="s">
-        <v>4276</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="1298" spans="1:11">
@@ -54328,7 +54340,7 @@
         <v>3754</v>
       </c>
       <c r="G1298" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="H1298">
         <v>33</v>
@@ -54369,7 +54381,7 @@
         <v>224551</v>
       </c>
       <c r="K1299" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1300" spans="1:11">
@@ -54433,7 +54445,7 @@
         <v>224648</v>
       </c>
       <c r="K1301" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1302" spans="1:11">
@@ -54456,7 +54468,7 @@
         <v>3754</v>
       </c>
       <c r="G1302" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="H1302">
         <v>22</v>
@@ -54488,7 +54500,7 @@
         <v>3754</v>
       </c>
       <c r="G1303" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="H1303">
         <v>22</v>
@@ -54520,7 +54532,7 @@
         <v>3754</v>
       </c>
       <c r="G1304" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="H1304">
         <v>22</v>
@@ -54561,7 +54573,7 @@
         <v>224721</v>
       </c>
       <c r="K1305" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="1306" spans="1:11">
@@ -54593,7 +54605,7 @@
         <v>224733</v>
       </c>
       <c r="K1306" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="1307" spans="1:11">
@@ -54625,7 +54637,7 @@
         <v>224735</v>
       </c>
       <c r="K1307" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="1308" spans="1:11">
@@ -54657,7 +54669,7 @@
         <v>224738</v>
       </c>
       <c r="K1308" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="1309" spans="1:11">
@@ -54689,7 +54701,7 @@
         <v>224787</v>
       </c>
       <c r="K1309" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="1310" spans="1:11">
@@ -54721,7 +54733,7 @@
         <v>224820</v>
       </c>
       <c r="K1310" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1311" spans="1:11">
@@ -54753,7 +54765,7 @@
         <v>224882</v>
       </c>
       <c r="K1311" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1312" spans="1:11">
@@ -54776,7 +54788,7 @@
         <v>3754</v>
       </c>
       <c r="G1312" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="H1312">
         <v>34</v>
@@ -54785,7 +54797,7 @@
         <v>224918</v>
       </c>
       <c r="K1312" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1313" spans="1:11">
@@ -54808,7 +54820,7 @@
         <v>3754</v>
       </c>
       <c r="G1313" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="H1313">
         <v>34</v>
@@ -54817,7 +54829,7 @@
         <v>224927</v>
       </c>
       <c r="K1313" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1314" spans="1:11">
@@ -54881,7 +54893,7 @@
         <v>224961</v>
       </c>
       <c r="K1315" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="1316" spans="1:11">
@@ -54913,7 +54925,7 @@
         <v>225093</v>
       </c>
       <c r="K1316" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1317" spans="1:11">
@@ -54945,7 +54957,7 @@
         <v>225097</v>
       </c>
       <c r="K1317" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1318" spans="1:11">
@@ -54977,7 +54989,7 @@
         <v>225123</v>
       </c>
       <c r="K1318" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1319" spans="1:11">
@@ -55009,7 +55021,7 @@
         <v>225127</v>
       </c>
       <c r="K1319" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1320" spans="1:11">
@@ -55041,7 +55053,7 @@
         <v>225179</v>
       </c>
       <c r="K1320" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1321" spans="1:11">
@@ -55233,7 +55245,7 @@
         <v>225937</v>
       </c>
       <c r="K1326" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1327" spans="1:11">
@@ -55265,7 +55277,7 @@
         <v>225938</v>
       </c>
       <c r="K1327" t="s">
-        <v>4225</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="1328" spans="1:11">
@@ -55361,7 +55373,7 @@
         <v>226098</v>
       </c>
       <c r="K1330" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1331" spans="1:11">
@@ -55393,7 +55405,7 @@
         <v>226118</v>
       </c>
       <c r="K1331" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="1332" spans="1:11">
@@ -55425,7 +55437,7 @@
         <v>226129</v>
       </c>
       <c r="K1332" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="1333" spans="1:11">
@@ -55512,7 +55524,7 @@
         <v>3754</v>
       </c>
       <c r="G1335" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H1335">
         <v>34</v>
@@ -55521,7 +55533,7 @@
         <v>226186</v>
       </c>
       <c r="K1335" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1336" spans="1:11">
@@ -55617,7 +55629,7 @@
         <v>226395</v>
       </c>
       <c r="K1338" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1339" spans="1:11">
@@ -55649,7 +55661,7 @@
         <v>226414</v>
       </c>
       <c r="K1339" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1340" spans="1:11">
@@ -55672,7 +55684,7 @@
         <v>3754</v>
       </c>
       <c r="G1340" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="H1340">
         <v>19</v>
@@ -55713,7 +55725,7 @@
         <v>226611</v>
       </c>
       <c r="K1341" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1342" spans="1:11">
@@ -55809,7 +55821,7 @@
         <v>227181</v>
       </c>
       <c r="K1344" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1345" spans="1:11">
@@ -55841,7 +55853,7 @@
         <v>227182</v>
       </c>
       <c r="K1345" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1346" spans="1:11">
@@ -55873,7 +55885,7 @@
         <v>227305</v>
       </c>
       <c r="K1346" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1347" spans="1:11">
@@ -55905,7 +55917,7 @@
         <v>227317</v>
       </c>
       <c r="K1347" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1348" spans="1:11">
@@ -55937,7 +55949,7 @@
         <v>227330</v>
       </c>
       <c r="K1348" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1349" spans="1:11">
@@ -55969,7 +55981,7 @@
         <v>227361</v>
       </c>
       <c r="K1349" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1350" spans="1:11">
@@ -56001,7 +56013,7 @@
         <v>227375</v>
       </c>
       <c r="K1350" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1351" spans="1:11">
@@ -56033,7 +56045,7 @@
         <v>227427</v>
       </c>
       <c r="K1351" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1352" spans="1:11">
@@ -56056,7 +56068,7 @@
         <v>3754</v>
       </c>
       <c r="G1352" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="H1352">
         <v>14</v>
@@ -56065,7 +56077,7 @@
         <v>227498</v>
       </c>
       <c r="K1352" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1353" spans="1:11">
@@ -56129,7 +56141,7 @@
         <v>227565</v>
       </c>
       <c r="K1354" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1355" spans="1:11">
@@ -56161,7 +56173,7 @@
         <v>227566</v>
       </c>
       <c r="K1355" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1356" spans="1:11">
@@ -56193,7 +56205,7 @@
         <v>227580</v>
       </c>
       <c r="K1356" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1357" spans="1:11">
@@ -56225,7 +56237,7 @@
         <v>227614</v>
       </c>
       <c r="K1357" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1358" spans="1:11">
@@ -56257,7 +56269,7 @@
         <v>227624</v>
       </c>
       <c r="K1358" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1359" spans="1:11">
@@ -56289,7 +56301,7 @@
         <v>227633</v>
       </c>
       <c r="K1359" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1360" spans="1:11">
@@ -56321,7 +56333,7 @@
         <v>227684</v>
       </c>
       <c r="K1360" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1361" spans="1:11">
@@ -56353,7 +56365,7 @@
         <v>227720</v>
       </c>
       <c r="K1361" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1362" spans="1:11">
@@ -56385,7 +56397,7 @@
         <v>227749</v>
       </c>
       <c r="K1362" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1363" spans="1:11">
@@ -56449,7 +56461,7 @@
         <v>227788</v>
       </c>
       <c r="K1364" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1365" spans="1:11">
@@ -56481,7 +56493,7 @@
         <v>227803</v>
       </c>
       <c r="K1365" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="1366" spans="1:11">
@@ -56737,7 +56749,7 @@
         <v>228123</v>
       </c>
       <c r="K1373" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1374" spans="1:11">
@@ -56769,7 +56781,7 @@
         <v>228125</v>
       </c>
       <c r="K1374" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1375" spans="1:11">
@@ -56801,7 +56813,7 @@
         <v>228133</v>
       </c>
       <c r="K1375" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1376" spans="1:11">
@@ -56897,7 +56909,7 @@
         <v>228155</v>
       </c>
       <c r="K1378" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="1379" spans="1:11">
@@ -56929,7 +56941,7 @@
         <v>228156</v>
       </c>
       <c r="K1379" t="s">
-        <v>4236</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="1380" spans="1:11">
@@ -56961,7 +56973,7 @@
         <v>228173</v>
       </c>
       <c r="K1380" t="s">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1381" spans="1:11">
@@ -56993,7 +57005,7 @@
         <v>228307</v>
       </c>
       <c r="K1381" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1382" spans="1:11">
@@ -57025,7 +57037,7 @@
         <v>228308</v>
       </c>
       <c r="K1382" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1383" spans="1:11">
@@ -57249,7 +57261,7 @@
         <v>228505</v>
       </c>
       <c r="K1389" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1390" spans="1:11">
@@ -57281,7 +57293,7 @@
         <v>228517</v>
       </c>
       <c r="K1390" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1391" spans="1:11">
@@ -57313,7 +57325,7 @@
         <v>228519</v>
       </c>
       <c r="K1391" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1392" spans="1:11">
@@ -57345,7 +57357,7 @@
         <v>228553</v>
       </c>
       <c r="K1392" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1393" spans="1:11">
@@ -57377,7 +57389,7 @@
         <v>228582</v>
       </c>
       <c r="K1393" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1394" spans="1:11">
@@ -57409,7 +57421,7 @@
         <v>228586</v>
       </c>
       <c r="K1394" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1395" spans="1:11">
@@ -57441,7 +57453,7 @@
         <v>228591</v>
       </c>
       <c r="K1395" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1396" spans="1:11">
@@ -57473,7 +57485,7 @@
         <v>228592</v>
       </c>
       <c r="K1396" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1397" spans="1:11">
@@ -57505,7 +57517,7 @@
         <v>228643</v>
       </c>
       <c r="K1397" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1398" spans="1:11">
@@ -57537,7 +57549,7 @@
         <v>228644</v>
       </c>
       <c r="K1398" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1399" spans="1:11">
@@ -57569,7 +57581,7 @@
         <v>228647</v>
       </c>
       <c r="K1399" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1400" spans="1:11">
@@ -57601,7 +57613,7 @@
         <v>228704</v>
       </c>
       <c r="K1400" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1401" spans="1:11">
@@ -57633,7 +57645,7 @@
         <v>228759</v>
       </c>
       <c r="K1401" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1402" spans="1:11">
@@ -57665,7 +57677,7 @@
         <v>228763</v>
       </c>
       <c r="K1402" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1403" spans="1:11">
@@ -57697,7 +57709,7 @@
         <v>228844</v>
       </c>
       <c r="K1403" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1404" spans="1:11">
@@ -57729,7 +57741,7 @@
         <v>228845</v>
       </c>
       <c r="K1404" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1405" spans="1:11">
@@ -57921,7 +57933,7 @@
         <v>229009</v>
       </c>
       <c r="K1410" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1411" spans="1:11">
@@ -57953,7 +57965,7 @@
         <v>229063</v>
       </c>
       <c r="K1411" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1412" spans="1:11">
@@ -57976,7 +57988,7 @@
         <v>3754</v>
       </c>
       <c r="G1412" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="H1412">
         <v>21</v>
@@ -58177,7 +58189,7 @@
         <v>229123</v>
       </c>
       <c r="K1418" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1419" spans="1:11">
@@ -58209,7 +58221,7 @@
         <v>229141</v>
       </c>
       <c r="K1419" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1420" spans="1:11">
@@ -58241,7 +58253,7 @@
         <v>229181</v>
       </c>
       <c r="K1420" t="s">
-        <v>4244</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="1421" spans="1:11">
@@ -58488,7 +58500,7 @@
         <v>3754</v>
       </c>
       <c r="G1428" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1428">
         <v>31</v>
@@ -58497,7 +58509,7 @@
         <v>229323</v>
       </c>
       <c r="K1428" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1429" spans="1:11">
@@ -58529,7 +58541,7 @@
         <v>229343</v>
       </c>
       <c r="K1429" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1430" spans="1:11">
@@ -58561,7 +58573,7 @@
         <v>229349</v>
       </c>
       <c r="K1430" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1431" spans="1:11">
@@ -58593,7 +58605,7 @@
         <v>229351</v>
       </c>
       <c r="K1431" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1432" spans="1:11">
@@ -58625,7 +58637,7 @@
         <v>229369</v>
       </c>
       <c r="K1432" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1433" spans="1:11">
@@ -58657,7 +58669,7 @@
         <v>229370</v>
       </c>
       <c r="K1433" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1434" spans="1:11">
@@ -58689,7 +58701,7 @@
         <v>229387</v>
       </c>
       <c r="K1434" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1435" spans="1:11">
@@ -58721,7 +58733,7 @@
         <v>229403</v>
       </c>
       <c r="K1435" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1436" spans="1:11">
@@ -58753,7 +58765,7 @@
         <v>229406</v>
       </c>
       <c r="K1436" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1437" spans="1:11">
@@ -58785,7 +58797,7 @@
         <v>229429</v>
       </c>
       <c r="K1437" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1438" spans="1:11">
@@ -58817,7 +58829,7 @@
         <v>229434</v>
       </c>
       <c r="K1438" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1439" spans="1:11">
@@ -58849,7 +58861,7 @@
         <v>229506</v>
       </c>
       <c r="K1439" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1440" spans="1:11">
@@ -58881,7 +58893,7 @@
         <v>229515</v>
       </c>
       <c r="K1440" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1441" spans="1:11">
@@ -58913,7 +58925,7 @@
         <v>229560</v>
       </c>
       <c r="K1441" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1442" spans="1:11">
@@ -58945,7 +58957,7 @@
         <v>229568</v>
       </c>
       <c r="K1442" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1443" spans="1:11">
@@ -58977,7 +58989,7 @@
         <v>229576</v>
       </c>
       <c r="K1443" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1444" spans="1:11">
@@ -59009,7 +59021,7 @@
         <v>229578</v>
       </c>
       <c r="K1444" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1445" spans="1:11">
@@ -59041,7 +59053,7 @@
         <v>229579</v>
       </c>
       <c r="K1445" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1446" spans="1:11">
@@ -59073,7 +59085,7 @@
         <v>229585</v>
       </c>
       <c r="K1446" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1447" spans="1:11">
@@ -59105,7 +59117,7 @@
         <v>229588</v>
       </c>
       <c r="K1447" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1448" spans="1:11">
@@ -59137,7 +59149,7 @@
         <v>229589</v>
       </c>
       <c r="K1448" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1449" spans="1:11">
@@ -59169,7 +59181,7 @@
         <v>229597</v>
       </c>
       <c r="K1449" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1450" spans="1:11">
@@ -59201,7 +59213,7 @@
         <v>229618</v>
       </c>
       <c r="K1450" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1451" spans="1:11">
@@ -59233,7 +59245,7 @@
         <v>229619</v>
       </c>
       <c r="K1451" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1452" spans="1:11">
@@ -59265,7 +59277,7 @@
         <v>229624</v>
       </c>
       <c r="K1452" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1453" spans="1:11">
@@ -59297,7 +59309,7 @@
         <v>229639</v>
       </c>
       <c r="K1453" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1454" spans="1:11">
@@ -59329,7 +59341,7 @@
         <v>229645</v>
       </c>
       <c r="K1454" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1455" spans="1:11">
@@ -59361,7 +59373,7 @@
         <v>229648</v>
       </c>
       <c r="K1455" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1456" spans="1:11">
@@ -59457,7 +59469,7 @@
         <v>229711</v>
       </c>
       <c r="K1458" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1459" spans="1:11">
@@ -59567,7 +59579,7 @@
         <v>229743</v>
       </c>
       <c r="K1462" t="s">
-        <v>4277</v>
+        <v>4278</v>
       </c>
     </row>
     <row r="1463" spans="1:11">
@@ -59645,7 +59657,7 @@
         <v>229786</v>
       </c>
       <c r="K1465" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1466" spans="1:11">
@@ -59677,7 +59689,7 @@
         <v>229787</v>
       </c>
       <c r="K1466" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1467" spans="1:11">
@@ -59842,7 +59854,7 @@
         <v>229914</v>
       </c>
       <c r="K1472" t="s">
-        <v>4278</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="1473" spans="1:11">
@@ -59874,7 +59886,7 @@
         <v>229916</v>
       </c>
       <c r="K1473" t="s">
-        <v>4278</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="1474" spans="1:11">
@@ -60002,7 +60014,7 @@
         <v>230010</v>
       </c>
       <c r="K1477" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1478" spans="1:11">
@@ -60258,7 +60270,7 @@
         <v>230073</v>
       </c>
       <c r="K1485" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1486" spans="1:11">
@@ -60290,7 +60302,7 @@
         <v>230076</v>
       </c>
       <c r="K1486" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1487" spans="1:11">
@@ -60322,7 +60334,7 @@
         <v>230087</v>
       </c>
       <c r="K1487" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1488" spans="1:11">
@@ -60354,7 +60366,7 @@
         <v>230088</v>
       </c>
       <c r="K1488" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1489" spans="1:11">
@@ -60386,7 +60398,7 @@
         <v>230089</v>
       </c>
       <c r="K1489" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1490" spans="1:11">
@@ -60418,7 +60430,7 @@
         <v>230091</v>
       </c>
       <c r="K1490" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1491" spans="1:11">
@@ -60450,7 +60462,7 @@
         <v>230100</v>
       </c>
       <c r="K1491" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1492" spans="1:11">
@@ -60482,7 +60494,7 @@
         <v>230112</v>
       </c>
       <c r="K1492" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1493" spans="1:11">
@@ -60514,7 +60526,7 @@
         <v>230117</v>
       </c>
       <c r="K1493" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1494" spans="1:11">
@@ -60546,7 +60558,7 @@
         <v>230125</v>
       </c>
       <c r="K1494" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1495" spans="1:11">
@@ -60578,7 +60590,7 @@
         <v>230135</v>
       </c>
       <c r="K1495" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1496" spans="1:11">
@@ -60610,7 +60622,7 @@
         <v>230168</v>
       </c>
       <c r="K1496" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1497" spans="1:11">
@@ -60642,7 +60654,7 @@
         <v>230169</v>
       </c>
       <c r="K1497" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1498" spans="1:11">
@@ -60674,7 +60686,7 @@
         <v>230171</v>
       </c>
       <c r="K1498" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1499" spans="1:11">
@@ -60706,7 +60718,7 @@
         <v>230205</v>
       </c>
       <c r="K1499" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1500" spans="1:11">
@@ -60738,7 +60750,7 @@
         <v>230227</v>
       </c>
       <c r="K1500" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1501" spans="1:11">
@@ -60770,7 +60782,7 @@
         <v>230290</v>
       </c>
       <c r="K1501" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1502" spans="1:11">
@@ -60825,7 +60837,7 @@
         <v>230310</v>
       </c>
       <c r="K1503" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1504" spans="1:11">
@@ -60857,7 +60869,7 @@
         <v>230339</v>
       </c>
       <c r="K1504" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1505" spans="1:11">
@@ -60889,7 +60901,7 @@
         <v>230349</v>
       </c>
       <c r="K1505" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1506" spans="1:11">
@@ -60921,7 +60933,7 @@
         <v>230351</v>
       </c>
       <c r="K1506" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1507" spans="1:11">
@@ -60953,7 +60965,7 @@
         <v>230353</v>
       </c>
       <c r="K1507" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1508" spans="1:11">
@@ -60985,7 +60997,7 @@
         <v>230354</v>
       </c>
       <c r="K1508" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1509" spans="1:11">
@@ -61017,7 +61029,7 @@
         <v>230431</v>
       </c>
       <c r="K1509" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1510" spans="1:11">
@@ -61433,7 +61445,7 @@
         <v>230633</v>
       </c>
       <c r="K1522" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1523" spans="1:11">
@@ -61465,7 +61477,7 @@
         <v>230636</v>
       </c>
       <c r="K1523" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1524" spans="1:11">
@@ -61497,7 +61509,7 @@
         <v>230672</v>
       </c>
       <c r="K1524" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1525" spans="1:11">
@@ -61529,7 +61541,7 @@
         <v>230677</v>
       </c>
       <c r="K1525" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1526" spans="1:11">
@@ -61561,7 +61573,7 @@
         <v>230710</v>
       </c>
       <c r="K1526" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1527" spans="1:11">
@@ -61593,7 +61605,7 @@
         <v>230717</v>
       </c>
       <c r="K1527" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1528" spans="1:11">
@@ -61625,7 +61637,7 @@
         <v>230751</v>
       </c>
       <c r="K1528" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1529" spans="1:11">
@@ -61657,7 +61669,7 @@
         <v>230753</v>
       </c>
       <c r="K1529" t="s">
-        <v>4241</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="1530" spans="1:11">
@@ -61689,7 +61701,7 @@
         <v>230889</v>
       </c>
       <c r="K1530" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1531" spans="1:11">
@@ -61721,7 +61733,7 @@
         <v>230918</v>
       </c>
       <c r="K1531" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1532" spans="1:11">
@@ -61753,7 +61765,7 @@
         <v>230919</v>
       </c>
       <c r="K1532" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1533" spans="1:11">
@@ -61785,7 +61797,7 @@
         <v>230926</v>
       </c>
       <c r="K1533" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1534" spans="1:11">
@@ -61849,7 +61861,7 @@
         <v>230930</v>
       </c>
       <c r="K1535" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1536" spans="1:11">
@@ -61881,7 +61893,7 @@
         <v>230938</v>
       </c>
       <c r="K1536" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1537" spans="1:11">
@@ -61913,7 +61925,7 @@
         <v>230941</v>
       </c>
       <c r="K1537" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1538" spans="1:11">
@@ -61945,7 +61957,7 @@
         <v>230949</v>
       </c>
       <c r="K1538" t="s">
-        <v>4279</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="1539" spans="1:11">
@@ -61977,7 +61989,7 @@
         <v>231004</v>
       </c>
       <c r="K1539" t="s">
-        <v>4279</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="1540" spans="1:11">
@@ -62009,7 +62021,7 @@
         <v>231048</v>
       </c>
       <c r="K1540" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1541" spans="1:11">
@@ -62041,7 +62053,7 @@
         <v>231051</v>
       </c>
       <c r="K1541" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1542" spans="1:11">
@@ -62073,7 +62085,7 @@
         <v>231053</v>
       </c>
       <c r="K1542" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1543" spans="1:11">
@@ -62105,7 +62117,7 @@
         <v>231054</v>
       </c>
       <c r="K1543" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1544" spans="1:11">
@@ -62137,7 +62149,7 @@
         <v>231077</v>
       </c>
       <c r="K1544" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1545" spans="1:11">
@@ -62169,7 +62181,7 @@
         <v>231091</v>
       </c>
       <c r="K1545" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1546" spans="1:11">
@@ -62201,7 +62213,7 @@
         <v>231094</v>
       </c>
       <c r="K1546" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1547" spans="1:11">
@@ -62233,7 +62245,7 @@
         <v>231131</v>
       </c>
       <c r="K1547" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1548" spans="1:11">
@@ -62329,7 +62341,7 @@
         <v>231237</v>
       </c>
       <c r="K1550" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1551" spans="1:11">
@@ -62361,7 +62373,7 @@
         <v>231240</v>
       </c>
       <c r="K1551" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1552" spans="1:11">
@@ -62393,7 +62405,7 @@
         <v>231242</v>
       </c>
       <c r="K1552" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1553" spans="1:11">
@@ -62425,7 +62437,7 @@
         <v>231246</v>
       </c>
       <c r="K1553" t="s">
-        <v>4280</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="1554" spans="1:11">
@@ -62512,7 +62524,7 @@
         <v>3754</v>
       </c>
       <c r="G1556" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1556">
         <v>31</v>
@@ -62521,7 +62533,7 @@
         <v>231321</v>
       </c>
       <c r="K1556" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1557" spans="1:11">
@@ -62553,7 +62565,7 @@
         <v>231343</v>
       </c>
       <c r="K1557" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1558" spans="1:11">
@@ -62585,7 +62597,7 @@
         <v>231376</v>
       </c>
       <c r="K1558" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1559" spans="1:11">
@@ -62617,7 +62629,7 @@
         <v>231377</v>
       </c>
       <c r="K1559" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1560" spans="1:11">
@@ -62649,7 +62661,7 @@
         <v>231400</v>
       </c>
       <c r="K1560" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1561" spans="1:11">
@@ -62681,7 +62693,7 @@
         <v>231404</v>
       </c>
       <c r="K1561" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1562" spans="1:11">
@@ -62713,7 +62725,7 @@
         <v>231415</v>
       </c>
       <c r="K1562" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1563" spans="1:11">
@@ -62745,7 +62757,7 @@
         <v>231427</v>
       </c>
       <c r="K1563" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1564" spans="1:11">
@@ -62777,7 +62789,7 @@
         <v>231446</v>
       </c>
       <c r="K1564" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1565" spans="1:11">
@@ -62809,7 +62821,7 @@
         <v>231447</v>
       </c>
       <c r="K1565" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1566" spans="1:11">
@@ -62841,7 +62853,7 @@
         <v>231455</v>
       </c>
       <c r="K1566" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1567" spans="1:11">
@@ -62873,7 +62885,7 @@
         <v>231483</v>
       </c>
       <c r="K1567" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1568" spans="1:11">
@@ -62905,7 +62917,7 @@
         <v>231487</v>
       </c>
       <c r="K1568" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1569" spans="1:11">
@@ -62937,7 +62949,7 @@
         <v>231575</v>
       </c>
       <c r="K1569" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1570" spans="1:11">
@@ -62969,7 +62981,7 @@
         <v>231576</v>
       </c>
       <c r="K1570" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1571" spans="1:11">
@@ -63001,7 +63013,7 @@
         <v>231577</v>
       </c>
       <c r="K1571" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1572" spans="1:11">
@@ -63033,7 +63045,7 @@
         <v>231597</v>
       </c>
       <c r="K1572" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1573" spans="1:11">
@@ -63065,7 +63077,7 @@
         <v>231598</v>
       </c>
       <c r="K1573" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1574" spans="1:11">
@@ -63097,7 +63109,7 @@
         <v>231599</v>
       </c>
       <c r="K1574" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1575" spans="1:11">
@@ -63129,7 +63141,7 @@
         <v>231616</v>
       </c>
       <c r="K1575" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1576" spans="1:11">
@@ -63161,7 +63173,7 @@
         <v>231622</v>
       </c>
       <c r="K1576" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1577" spans="1:11">
@@ -63193,7 +63205,7 @@
         <v>231638</v>
       </c>
       <c r="K1577" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1578" spans="1:11">
@@ -63225,7 +63237,7 @@
         <v>231646</v>
       </c>
       <c r="K1578" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1579" spans="1:11">
@@ -63257,7 +63269,7 @@
         <v>231647</v>
       </c>
       <c r="K1579" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1580" spans="1:11">
@@ -63289,7 +63301,7 @@
         <v>231679</v>
       </c>
       <c r="K1580" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1581" spans="1:11">
@@ -63321,7 +63333,7 @@
         <v>231687</v>
       </c>
       <c r="K1581" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1582" spans="1:11">
@@ -63353,7 +63365,7 @@
         <v>231699</v>
       </c>
       <c r="K1582" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1583" spans="1:11">
@@ -63385,7 +63397,7 @@
         <v>231740</v>
       </c>
       <c r="K1583" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1584" spans="1:11">
@@ -63417,7 +63429,7 @@
         <v>231764</v>
       </c>
       <c r="K1584" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1585" spans="1:11">
@@ -63449,7 +63461,7 @@
         <v>231805</v>
       </c>
       <c r="K1585" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1586" spans="1:11">
@@ -63481,7 +63493,7 @@
         <v>231847</v>
       </c>
       <c r="K1586" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1587" spans="1:11">
@@ -63513,7 +63525,7 @@
         <v>231848</v>
       </c>
       <c r="K1587" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1588" spans="1:11">
@@ -63737,7 +63749,7 @@
         <v>231868</v>
       </c>
       <c r="K1594" t="s">
-        <v>4281</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="1595" spans="1:11">
@@ -63801,7 +63813,7 @@
         <v>231871</v>
       </c>
       <c r="K1596" t="s">
-        <v>4282</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="1597" spans="1:11">
@@ -63865,7 +63877,7 @@
         <v>231873</v>
       </c>
       <c r="K1598" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1599" spans="1:11">
@@ -63897,7 +63909,7 @@
         <v>231874</v>
       </c>
       <c r="K1599" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1600" spans="1:11">
@@ -64025,7 +64037,7 @@
         <v>231878</v>
       </c>
       <c r="K1603" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1604" spans="1:11">
@@ -64057,7 +64069,7 @@
         <v>231879</v>
       </c>
       <c r="K1604" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1605" spans="1:11">
@@ -64089,7 +64101,7 @@
         <v>231880</v>
       </c>
       <c r="K1605" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1606" spans="1:11">
@@ -64153,7 +64165,7 @@
         <v>231894</v>
       </c>
       <c r="K1607" t="s">
-        <v>4283</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="1608" spans="1:11">
@@ -64217,7 +64229,7 @@
         <v>231896</v>
       </c>
       <c r="K1609" t="s">
-        <v>4284</v>
+        <v>4285</v>
       </c>
     </row>
     <row r="1610" spans="1:11">
@@ -64249,7 +64261,7 @@
         <v>231897</v>
       </c>
       <c r="K1610" t="s">
-        <v>4285</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="1611" spans="1:11">
@@ -64313,7 +64325,7 @@
         <v>231902</v>
       </c>
       <c r="K1612" t="s">
-        <v>4286</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="1613" spans="1:11">
@@ -64409,7 +64421,7 @@
         <v>231905</v>
       </c>
       <c r="K1615" t="s">
-        <v>4287</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1616" spans="1:11">
@@ -64537,7 +64549,7 @@
         <v>231940</v>
       </c>
       <c r="K1619" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1620" spans="1:11">
@@ -64569,7 +64581,7 @@
         <v>231941</v>
       </c>
       <c r="K1620" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1621" spans="1:11">
@@ -64601,7 +64613,7 @@
         <v>231943</v>
       </c>
       <c r="K1621" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1622" spans="1:11">
@@ -64633,7 +64645,7 @@
         <v>231965</v>
       </c>
       <c r="K1622" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1623" spans="1:11">
@@ -64665,7 +64677,7 @@
         <v>231966</v>
       </c>
       <c r="K1623" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1624" spans="1:11">
@@ -64985,7 +64997,7 @@
         <v>231994</v>
       </c>
       <c r="K1633" t="s">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1634" spans="1:11">
@@ -65145,7 +65157,7 @@
         <v>231999</v>
       </c>
       <c r="K1638" t="s">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1639" spans="1:11">
@@ -65177,7 +65189,7 @@
         <v>232000</v>
       </c>
       <c r="K1639" t="s">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1640" spans="1:11">
@@ -65273,7 +65285,7 @@
         <v>232008</v>
       </c>
       <c r="K1642" t="s">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1643" spans="1:11">
@@ -65406,7 +65418,7 @@
         <v>232050</v>
       </c>
       <c r="K1647" t="s">
-        <v>4289</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="1648" spans="1:11">
@@ -65502,7 +65514,7 @@
         <v>232054</v>
       </c>
       <c r="K1650" t="s">
-        <v>4289</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="1651" spans="1:11">
@@ -65598,7 +65610,7 @@
         <v>232058</v>
       </c>
       <c r="K1653" t="s">
-        <v>4290</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="1654" spans="1:11">
@@ -65717,7 +65729,7 @@
         <v>232087</v>
       </c>
       <c r="K1657" t="s">
-        <v>4291</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="1658" spans="1:11">
@@ -65941,7 +65953,7 @@
         <v>232095</v>
       </c>
       <c r="K1664" t="s">
-        <v>4292</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="1665" spans="1:11">
@@ -66069,7 +66081,7 @@
         <v>232099</v>
       </c>
       <c r="K1668" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1669" spans="1:11">
@@ -66124,7 +66136,7 @@
         <v>3754</v>
       </c>
       <c r="G1670" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1670">
         <v>30</v>
@@ -66156,7 +66168,7 @@
         <v>3754</v>
       </c>
       <c r="G1671" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="H1671">
         <v>30</v>
@@ -66197,7 +66209,7 @@
         <v>232107</v>
       </c>
       <c r="K1672" t="s">
-        <v>4293</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="1673" spans="1:11">
@@ -66421,7 +66433,7 @@
         <v>232117</v>
       </c>
       <c r="K1679" t="s">
-        <v>4294</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="1680" spans="1:11">
@@ -66517,7 +66529,7 @@
         <v>232134</v>
       </c>
       <c r="K1682" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1683" spans="1:11">
@@ -66581,7 +66593,7 @@
         <v>232136</v>
       </c>
       <c r="K1684" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1685" spans="1:11">
@@ -66613,7 +66625,7 @@
         <v>232137</v>
       </c>
       <c r="K1685" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1686" spans="1:11">
@@ -66645,7 +66657,7 @@
         <v>232138</v>
       </c>
       <c r="K1686" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1687" spans="1:11">
@@ -66677,7 +66689,7 @@
         <v>232143</v>
       </c>
       <c r="K1687" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1688" spans="1:11">
@@ -66764,7 +66776,7 @@
         <v>3754</v>
       </c>
       <c r="G1690" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="H1690">
         <v>33</v>
@@ -66805,7 +66817,7 @@
         <v>232178</v>
       </c>
       <c r="K1691" t="s">
-        <v>4293</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="1692" spans="1:11">
@@ -66965,7 +66977,7 @@
         <v>232184</v>
       </c>
       <c r="K1696" t="s">
-        <v>4293</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="1697" spans="1:11">
@@ -67020,7 +67032,7 @@
         <v>3754</v>
       </c>
       <c r="G1698" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="H1698">
         <v>33</v>
@@ -67093,7 +67105,7 @@
         <v>232188</v>
       </c>
       <c r="K1700" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1701" spans="1:11">
@@ -67180,7 +67192,7 @@
         <v>3754</v>
       </c>
       <c r="G1703" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="H1703">
         <v>40</v>
@@ -69164,7 +69176,7 @@
         <v>3754</v>
       </c>
       <c r="G1765" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="H1765">
         <v>31</v>
@@ -69237,7 +69249,7 @@
         <v>232503</v>
       </c>
       <c r="K1767" t="s">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1768" spans="1:11">
@@ -69301,7 +69313,7 @@
         <v>232505</v>
       </c>
       <c r="K1769" t="s">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1770" spans="1:11">
@@ -69333,7 +69345,7 @@
         <v>232507</v>
       </c>
       <c r="K1770" t="s">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1771" spans="1:11">
@@ -69717,7 +69729,7 @@
         <v>232570</v>
       </c>
       <c r="K1782" t="s">
-        <v>4295</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="1783" spans="1:11">
@@ -71381,7 +71393,7 @@
         <v>230437</v>
       </c>
       <c r="K1852" t="s">
-        <v>4247</v>
+        <v>4248</v>
       </c>
     </row>
   </sheetData>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -12911,8 +12911,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -12928,7 +12936,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -12936,12 +12944,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13240,37 +13266,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10897" uniqueCount="4297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10895" uniqueCount="4296">
   <si>
     <t>employeeCode</t>
   </si>
@@ -12178,84 +12178,84 @@
     <t>Nageshvr vidyalay chikhali</t>
   </si>
   <si>
+    <t>CHAKAN  CHOWK</t>
+  </si>
+  <si>
+    <t>RANUBAI MALA</t>
+  </si>
+  <si>
+    <t>AROGYAM HOSPITAL</t>
+  </si>
+  <si>
+    <t>AKURDI GATE</t>
+  </si>
+  <si>
+    <t>Canbay Chowk Dehugaon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT CHOWK BHOSARI </t>
+  </si>
+  <si>
+    <t>ABHILASHA PARK</t>
+  </si>
+  <si>
+    <t>TALAWADE CHOWK</t>
+  </si>
+  <si>
+    <t>TRIVENINAGR CHOWK</t>
+  </si>
+  <si>
+    <t>MAHINDRA GATE</t>
+  </si>
+  <si>
+    <t>EIFFEL CITY</t>
+  </si>
+  <si>
+    <t>INDRAYNI COLLEGE</t>
+  </si>
+  <si>
+    <t>MEDANKARWADI</t>
+  </si>
+  <si>
+    <t>TALEGOAN</t>
+  </si>
+  <si>
+    <t>AKURDI</t>
+  </si>
+  <si>
+    <t>CHAKAN</t>
+  </si>
+  <si>
+    <t>khandoba chowk</t>
+  </si>
+  <si>
+    <t>KHANDOBA CHOWK</t>
+  </si>
+  <si>
+    <t>DHORE WASTI</t>
+  </si>
+  <si>
+    <t>MANGLE MURTI MEDICAL</t>
+  </si>
+  <si>
+    <t>KAMINI GATE</t>
+  </si>
+  <si>
+    <t>VITTAL RUKMINI CHOWK</t>
+  </si>
+  <si>
+    <t>SHREE RAM CHWOK</t>
+  </si>
+  <si>
+    <t>WAKI PHATA</t>
+  </si>
+  <si>
+    <t>TAWADE CHOWK</t>
+  </si>
+  <si>
     <t>TALWADE CHOWK</t>
   </si>
   <si>
-    <t>CHAKAN  CHOWK</t>
-  </si>
-  <si>
-    <t>RANUBAI MALA</t>
-  </si>
-  <si>
-    <t>AROGYAM HOSPITAL</t>
-  </si>
-  <si>
-    <t>AKURDI GATE</t>
-  </si>
-  <si>
-    <t>Canbay Chowk Dehugaon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMT CHOWK BHOSARI </t>
-  </si>
-  <si>
-    <t>ABHILASHA PARK</t>
-  </si>
-  <si>
-    <t>TALAWADE CHOWK</t>
-  </si>
-  <si>
-    <t>TRIVENINAGR CHOWK</t>
-  </si>
-  <si>
-    <t>MAHINDRA GATE</t>
-  </si>
-  <si>
-    <t>EIFFEL CITY</t>
-  </si>
-  <si>
-    <t>INDRAYNI COLLEGE</t>
-  </si>
-  <si>
-    <t>MEDANKARWADI</t>
-  </si>
-  <si>
-    <t>TALEGOAN</t>
-  </si>
-  <si>
-    <t>AKURDI</t>
-  </si>
-  <si>
-    <t>CHAKAN</t>
-  </si>
-  <si>
-    <t>khandoba chowk</t>
-  </si>
-  <si>
-    <t>KHANDOBA CHOWK</t>
-  </si>
-  <si>
-    <t>DHORE WASTI</t>
-  </si>
-  <si>
-    <t>MANGLE MURTI MEDICAL</t>
-  </si>
-  <si>
-    <t>KAMINI GATE</t>
-  </si>
-  <si>
-    <t>VITTAL RUKMINI CHOWK</t>
-  </si>
-  <si>
-    <t>SHREE RAM CHWOK</t>
-  </si>
-  <si>
-    <t>WAKI PHATA</t>
-  </si>
-  <si>
-    <t>TAWADE CHOWK</t>
-  </si>
-  <si>
     <t>CHAKANCHOWK</t>
   </si>
   <si>
@@ -12689,9 +12689,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>F</t>
   </si>
   <si>
     <t>SHAHUNAGAR</t>
@@ -12911,16 +12908,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -12936,7 +12925,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -12944,30 +12933,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13266,37 +13237,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -13486,7 +13457,7 @@
         <v>48092</v>
       </c>
       <c r="K7" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -13576,7 +13547,7 @@
         <v>48198</v>
       </c>
       <c r="K10" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -13608,7 +13579,7 @@
         <v>48199</v>
       </c>
       <c r="K11" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -13640,7 +13611,7 @@
         <v>48202</v>
       </c>
       <c r="K12" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -13765,7 +13736,7 @@
         <v>53533</v>
       </c>
       <c r="K16" t="s">
-        <v>4228</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -13797,7 +13768,7 @@
         <v>55968</v>
       </c>
       <c r="K17" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -13861,7 +13832,7 @@
         <v>60026</v>
       </c>
       <c r="K19" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -13957,7 +13928,7 @@
         <v>60033</v>
       </c>
       <c r="K22" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -13989,7 +13960,7 @@
         <v>60039</v>
       </c>
       <c r="K23" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -14085,7 +14056,7 @@
         <v>60044</v>
       </c>
       <c r="K26" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -14117,7 +14088,7 @@
         <v>60046</v>
       </c>
       <c r="K27" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -14149,7 +14120,7 @@
         <v>60051</v>
       </c>
       <c r="K28" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -14213,7 +14184,7 @@
         <v>60137</v>
       </c>
       <c r="K30" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -14274,7 +14245,7 @@
         <v>60166</v>
       </c>
       <c r="K32" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -14306,7 +14277,7 @@
         <v>60175</v>
       </c>
       <c r="K33" t="s">
-        <v>4228</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -14338,7 +14309,7 @@
         <v>60176</v>
       </c>
       <c r="K34" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -14434,7 +14405,7 @@
         <v>60210</v>
       </c>
       <c r="K37" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -14530,7 +14501,7 @@
         <v>60215</v>
       </c>
       <c r="K40" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -14562,7 +14533,7 @@
         <v>60216</v>
       </c>
       <c r="K41" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -14620,7 +14591,7 @@
         <v>60218</v>
       </c>
       <c r="K43" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -14748,7 +14719,7 @@
         <v>60230</v>
       </c>
       <c r="K47" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -14780,7 +14751,7 @@
         <v>60232</v>
       </c>
       <c r="K48" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -14812,7 +14783,7 @@
         <v>60233</v>
       </c>
       <c r="K49" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -14873,7 +14844,7 @@
         <v>60240</v>
       </c>
       <c r="K51" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -14905,7 +14876,7 @@
         <v>60242</v>
       </c>
       <c r="K52" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -14937,7 +14908,7 @@
         <v>60247</v>
       </c>
       <c r="K53" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -15033,7 +15004,7 @@
         <v>60256</v>
       </c>
       <c r="K56" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -15065,7 +15036,7 @@
         <v>60258</v>
       </c>
       <c r="K57" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -15097,7 +15068,7 @@
         <v>60259</v>
       </c>
       <c r="K58" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -15286,7 +15257,7 @@
         <v>60355</v>
       </c>
       <c r="K64" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -15382,7 +15353,7 @@
         <v>60359</v>
       </c>
       <c r="K67" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -15446,7 +15417,7 @@
         <v>60361</v>
       </c>
       <c r="K69" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -15507,7 +15478,7 @@
         <v>60363</v>
       </c>
       <c r="K71" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -15571,7 +15542,7 @@
         <v>60367</v>
       </c>
       <c r="K73" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -15603,7 +15574,7 @@
         <v>60369</v>
       </c>
       <c r="K74" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -15635,7 +15606,7 @@
         <v>60370</v>
       </c>
       <c r="K75" t="s">
-        <v>4238</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -15763,7 +15734,7 @@
         <v>60376</v>
       </c>
       <c r="K79" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -15827,7 +15798,7 @@
         <v>60378</v>
       </c>
       <c r="K81" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -15859,7 +15830,7 @@
         <v>60379</v>
       </c>
       <c r="K82" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -15891,7 +15862,7 @@
         <v>60380</v>
       </c>
       <c r="K83" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -15955,7 +15926,7 @@
         <v>60382</v>
       </c>
       <c r="K85" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -15987,7 +15958,7 @@
         <v>60384</v>
       </c>
       <c r="K86" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -16019,7 +15990,7 @@
         <v>60386</v>
       </c>
       <c r="K87" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -16083,7 +16054,7 @@
         <v>60388</v>
       </c>
       <c r="K89" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -16115,7 +16086,7 @@
         <v>60389</v>
       </c>
       <c r="K90" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -16147,7 +16118,7 @@
         <v>60390</v>
       </c>
       <c r="K91" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -16179,7 +16150,7 @@
         <v>60391</v>
       </c>
       <c r="K92" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -16243,7 +16214,7 @@
         <v>60397</v>
       </c>
       <c r="K94" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -16275,7 +16246,7 @@
         <v>60398</v>
       </c>
       <c r="K95" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -16339,7 +16310,7 @@
         <v>60400</v>
       </c>
       <c r="K97" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -16371,7 +16342,7 @@
         <v>60401</v>
       </c>
       <c r="K98" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -16435,7 +16406,7 @@
         <v>60403</v>
       </c>
       <c r="K100" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -16467,7 +16438,7 @@
         <v>60404</v>
       </c>
       <c r="K101" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -16499,7 +16470,7 @@
         <v>60406</v>
       </c>
       <c r="K102" t="s">
-        <v>4243</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -16563,7 +16534,7 @@
         <v>60409</v>
       </c>
       <c r="K104" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -16595,7 +16566,7 @@
         <v>60410</v>
       </c>
       <c r="K105" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -16627,7 +16598,7 @@
         <v>60424</v>
       </c>
       <c r="K106" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -16659,7 +16630,7 @@
         <v>60455</v>
       </c>
       <c r="K107" t="s">
-        <v>4244</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -16691,7 +16662,7 @@
         <v>60463</v>
       </c>
       <c r="K108" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -16723,7 +16694,7 @@
         <v>60465</v>
       </c>
       <c r="K109" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -16787,7 +16758,7 @@
         <v>60473</v>
       </c>
       <c r="K111" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -16851,7 +16822,7 @@
         <v>60479</v>
       </c>
       <c r="K113" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -16947,7 +16918,7 @@
         <v>60483</v>
       </c>
       <c r="K116" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -17104,7 +17075,7 @@
         <v>60490</v>
       </c>
       <c r="K121" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -17232,7 +17203,7 @@
         <v>60495</v>
       </c>
       <c r="K125" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -17296,7 +17267,7 @@
         <v>60499</v>
       </c>
       <c r="K127" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -17328,7 +17299,7 @@
         <v>60501</v>
       </c>
       <c r="K128" t="s">
-        <v>4243</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -17360,7 +17331,7 @@
         <v>60502</v>
       </c>
       <c r="K129" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -17424,7 +17395,7 @@
         <v>60505</v>
       </c>
       <c r="K131" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -17520,7 +17491,7 @@
         <v>60508</v>
       </c>
       <c r="K134" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -17552,7 +17523,7 @@
         <v>60509</v>
       </c>
       <c r="K135" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -17616,7 +17587,7 @@
         <v>60512</v>
       </c>
       <c r="K137" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -17712,7 +17683,7 @@
         <v>60516</v>
       </c>
       <c r="K140" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -17744,7 +17715,7 @@
         <v>60517</v>
       </c>
       <c r="K141" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -17872,7 +17843,7 @@
         <v>60522</v>
       </c>
       <c r="K145" t="s">
-        <v>4238</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -17936,7 +17907,7 @@
         <v>60528</v>
       </c>
       <c r="K147" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -17968,7 +17939,7 @@
         <v>60531</v>
       </c>
       <c r="K148" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -18000,7 +17971,7 @@
         <v>60532</v>
       </c>
       <c r="K149" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -18032,7 +18003,7 @@
         <v>60539</v>
       </c>
       <c r="K150" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -18064,7 +18035,7 @@
         <v>60540</v>
       </c>
       <c r="K151" t="s">
-        <v>4246</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -18160,7 +18131,7 @@
         <v>60563</v>
       </c>
       <c r="K154" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -18192,7 +18163,7 @@
         <v>60568</v>
       </c>
       <c r="K155" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -18224,7 +18195,7 @@
         <v>60612</v>
       </c>
       <c r="K156" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -18256,7 +18227,7 @@
         <v>60613</v>
       </c>
       <c r="K157" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -18349,7 +18320,7 @@
         <v>60646</v>
       </c>
       <c r="K160" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -18381,7 +18352,7 @@
         <v>60658</v>
       </c>
       <c r="K161" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -18413,7 +18384,7 @@
         <v>60661</v>
       </c>
       <c r="K162" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -18573,7 +18544,7 @@
         <v>60712</v>
       </c>
       <c r="K167" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -18605,7 +18576,7 @@
         <v>60714</v>
       </c>
       <c r="K168" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -18637,7 +18608,7 @@
         <v>60729</v>
       </c>
       <c r="K169" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -18765,7 +18736,7 @@
         <v>60777</v>
       </c>
       <c r="K173" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -18797,7 +18768,7 @@
         <v>60778</v>
       </c>
       <c r="K174" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -18861,7 +18832,7 @@
         <v>60780</v>
       </c>
       <c r="K176" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -18893,7 +18864,7 @@
         <v>60781</v>
       </c>
       <c r="K177" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -18957,7 +18928,7 @@
         <v>60783</v>
       </c>
       <c r="K179" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -18989,7 +18960,7 @@
         <v>60784</v>
       </c>
       <c r="K180" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -19021,7 +18992,7 @@
         <v>60785</v>
       </c>
       <c r="K181" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -19053,7 +19024,7 @@
         <v>60787</v>
       </c>
       <c r="K182" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -19149,7 +19120,7 @@
         <v>60791</v>
       </c>
       <c r="K185" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -19181,7 +19152,7 @@
         <v>60792</v>
       </c>
       <c r="K186" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -19213,7 +19184,7 @@
         <v>60793</v>
       </c>
       <c r="K187" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -19277,7 +19248,7 @@
         <v>60795</v>
       </c>
       <c r="K189" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -19341,7 +19312,7 @@
         <v>60798</v>
       </c>
       <c r="K191" t="s">
-        <v>4244</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -19373,7 +19344,7 @@
         <v>60800</v>
       </c>
       <c r="K192" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -19533,7 +19504,7 @@
         <v>60807</v>
       </c>
       <c r="K197" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -19565,7 +19536,7 @@
         <v>60808</v>
       </c>
       <c r="K198" t="s">
-        <v>4247</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -19725,7 +19696,7 @@
         <v>60815</v>
       </c>
       <c r="K203" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -19789,7 +19760,7 @@
         <v>60857</v>
       </c>
       <c r="K205" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -19821,7 +19792,7 @@
         <v>60858</v>
       </c>
       <c r="K206" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -19853,7 +19824,7 @@
         <v>60859</v>
       </c>
       <c r="K207" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -19885,7 +19856,7 @@
         <v>60860</v>
       </c>
       <c r="K208" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -19917,7 +19888,7 @@
         <v>60870</v>
       </c>
       <c r="K209" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -19981,7 +19952,7 @@
         <v>60974</v>
       </c>
       <c r="K211" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -20045,7 +20016,7 @@
         <v>60981</v>
       </c>
       <c r="K213" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -20109,7 +20080,7 @@
         <v>61017</v>
       </c>
       <c r="K215" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -20141,7 +20112,7 @@
         <v>61020</v>
       </c>
       <c r="K216" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -20237,7 +20208,7 @@
         <v>61023</v>
       </c>
       <c r="K219" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -20301,7 +20272,7 @@
         <v>61025</v>
       </c>
       <c r="K221" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -20429,7 +20400,7 @@
         <v>61029</v>
       </c>
       <c r="K225" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -20461,7 +20432,7 @@
         <v>61030</v>
       </c>
       <c r="K226" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -20525,7 +20496,7 @@
         <v>61032</v>
       </c>
       <c r="K228" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -20621,7 +20592,7 @@
         <v>61037</v>
       </c>
       <c r="K231" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -20685,7 +20656,7 @@
         <v>61039</v>
       </c>
       <c r="K233" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -20845,7 +20816,7 @@
         <v>61045</v>
       </c>
       <c r="K238" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -21005,7 +20976,7 @@
         <v>61050</v>
       </c>
       <c r="K243" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -21037,7 +21008,7 @@
         <v>61051</v>
       </c>
       <c r="K244" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -21101,7 +21072,7 @@
         <v>61070</v>
       </c>
       <c r="K246" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -21165,7 +21136,7 @@
         <v>61073</v>
       </c>
       <c r="K248" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -21197,7 +21168,7 @@
         <v>61074</v>
       </c>
       <c r="K249" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -21293,7 +21264,7 @@
         <v>61077</v>
       </c>
       <c r="K252" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -21421,7 +21392,7 @@
         <v>61087</v>
       </c>
       <c r="K256" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -21453,7 +21424,7 @@
         <v>61088</v>
       </c>
       <c r="K257" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -21485,7 +21456,7 @@
         <v>61089</v>
       </c>
       <c r="K258" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -21517,7 +21488,7 @@
         <v>61090</v>
       </c>
       <c r="K259" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -21581,7 +21552,7 @@
         <v>61092</v>
       </c>
       <c r="K261" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -21613,7 +21584,7 @@
         <v>61093</v>
       </c>
       <c r="K262" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -21677,7 +21648,7 @@
         <v>61095</v>
       </c>
       <c r="K264" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -21773,7 +21744,7 @@
         <v>61099</v>
       </c>
       <c r="K267" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -21805,7 +21776,7 @@
         <v>61102</v>
       </c>
       <c r="K268" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -21837,7 +21808,7 @@
         <v>61124</v>
       </c>
       <c r="K269" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -21869,7 +21840,7 @@
         <v>61126</v>
       </c>
       <c r="K270" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -21901,7 +21872,7 @@
         <v>61137</v>
       </c>
       <c r="K271" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -21933,7 +21904,7 @@
         <v>61150</v>
       </c>
       <c r="K272" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -21965,7 +21936,7 @@
         <v>61154</v>
       </c>
       <c r="K273" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -21997,7 +21968,7 @@
         <v>61160</v>
       </c>
       <c r="K274" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -22029,7 +22000,7 @@
         <v>61168</v>
       </c>
       <c r="K275" t="s">
-        <v>4249</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -22061,7 +22032,7 @@
         <v>61177</v>
       </c>
       <c r="K276" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="277" spans="1:11">
@@ -22125,7 +22096,7 @@
         <v>61189</v>
       </c>
       <c r="K278" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -22157,7 +22128,7 @@
         <v>61191</v>
       </c>
       <c r="K279" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -22221,7 +22192,7 @@
         <v>61193</v>
       </c>
       <c r="K281" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -22253,7 +22224,7 @@
         <v>61214</v>
       </c>
       <c r="K282" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -22317,7 +22288,7 @@
         <v>61227</v>
       </c>
       <c r="K284" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -22349,7 +22320,7 @@
         <v>61249</v>
       </c>
       <c r="K285" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -22413,7 +22384,7 @@
         <v>61255</v>
       </c>
       <c r="K287" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -22541,7 +22512,7 @@
         <v>61260</v>
       </c>
       <c r="K291" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -22573,7 +22544,7 @@
         <v>61263</v>
       </c>
       <c r="K292" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -22701,7 +22672,7 @@
         <v>61273</v>
       </c>
       <c r="K296" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="297" spans="1:11">
@@ -22765,7 +22736,7 @@
         <v>61275</v>
       </c>
       <c r="K298" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="299" spans="1:11">
@@ -22797,7 +22768,7 @@
         <v>61278</v>
       </c>
       <c r="K299" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="300" spans="1:11">
@@ -22829,7 +22800,7 @@
         <v>61279</v>
       </c>
       <c r="K300" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="301" spans="1:11">
@@ -22893,7 +22864,7 @@
         <v>61281</v>
       </c>
       <c r="K302" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="303" spans="1:11">
@@ -22925,7 +22896,7 @@
         <v>61282</v>
       </c>
       <c r="K303" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="304" spans="1:11">
@@ -22957,7 +22928,7 @@
         <v>61283</v>
       </c>
       <c r="K304" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="305" spans="1:11">
@@ -23021,7 +22992,7 @@
         <v>61285</v>
       </c>
       <c r="K306" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="307" spans="1:11">
@@ -23053,7 +23024,7 @@
         <v>61287</v>
       </c>
       <c r="K307" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="308" spans="1:11">
@@ -23085,7 +23056,7 @@
         <v>61288</v>
       </c>
       <c r="K308" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="309" spans="1:11">
@@ -23149,7 +23120,7 @@
         <v>61291</v>
       </c>
       <c r="K310" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="311" spans="1:11">
@@ -23213,7 +23184,7 @@
         <v>61308</v>
       </c>
       <c r="K312" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="313" spans="1:11">
@@ -23245,7 +23216,7 @@
         <v>61311</v>
       </c>
       <c r="K313" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="314" spans="1:11">
@@ -23405,7 +23376,7 @@
         <v>61366</v>
       </c>
       <c r="K318" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="319" spans="1:11">
@@ -23437,7 +23408,7 @@
         <v>61373</v>
       </c>
       <c r="K319" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="320" spans="1:11">
@@ -23469,7 +23440,7 @@
         <v>61467</v>
       </c>
       <c r="K320" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="321" spans="1:11">
@@ -23501,7 +23472,7 @@
         <v>61469</v>
       </c>
       <c r="K321" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="322" spans="1:11">
@@ -23533,7 +23504,7 @@
         <v>61471</v>
       </c>
       <c r="K322" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="323" spans="1:11">
@@ -23565,7 +23536,7 @@
         <v>61473</v>
       </c>
       <c r="K323" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="324" spans="1:11">
@@ -23597,7 +23568,7 @@
         <v>61474</v>
       </c>
       <c r="K324" t="s">
-        <v>4243</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="325" spans="1:11">
@@ -23629,7 +23600,7 @@
         <v>61475</v>
       </c>
       <c r="K325" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="326" spans="1:11">
@@ -23661,7 +23632,7 @@
         <v>61481</v>
       </c>
       <c r="K326" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="327" spans="1:11">
@@ -23693,7 +23664,7 @@
         <v>61484</v>
       </c>
       <c r="K327" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="328" spans="1:11">
@@ -23757,7 +23728,7 @@
         <v>61491</v>
       </c>
       <c r="K329" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="330" spans="1:11">
@@ -23821,7 +23792,7 @@
         <v>61493</v>
       </c>
       <c r="K331" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="332" spans="1:11">
@@ -23853,7 +23824,7 @@
         <v>61494</v>
       </c>
       <c r="K332" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="333" spans="1:11">
@@ -23885,7 +23856,7 @@
         <v>61510</v>
       </c>
       <c r="K333" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="334" spans="1:11">
@@ -23917,7 +23888,7 @@
         <v>61527</v>
       </c>
       <c r="K334" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="335" spans="1:11">
@@ -24013,7 +23984,7 @@
         <v>61568</v>
       </c>
       <c r="K337" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="338" spans="1:11">
@@ -24077,7 +24048,7 @@
         <v>61591</v>
       </c>
       <c r="K339" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="340" spans="1:11">
@@ -24109,7 +24080,7 @@
         <v>61749</v>
       </c>
       <c r="K340" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="341" spans="1:11">
@@ -24141,7 +24112,7 @@
         <v>61750</v>
       </c>
       <c r="K341" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="342" spans="1:11">
@@ -24237,7 +24208,7 @@
         <v>61772</v>
       </c>
       <c r="K344" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="345" spans="1:11">
@@ -24301,7 +24272,7 @@
         <v>61775</v>
       </c>
       <c r="K346" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="347" spans="1:11">
@@ -24333,7 +24304,7 @@
         <v>61776</v>
       </c>
       <c r="K347" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="348" spans="1:11">
@@ -24365,7 +24336,7 @@
         <v>61782</v>
       </c>
       <c r="K348" t="s">
-        <v>4228</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="349" spans="1:11">
@@ -24397,7 +24368,7 @@
         <v>61783</v>
       </c>
       <c r="K349" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="350" spans="1:11">
@@ -24461,7 +24432,7 @@
         <v>61785</v>
       </c>
       <c r="K351" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="352" spans="1:11">
@@ -24493,7 +24464,7 @@
         <v>61786</v>
       </c>
       <c r="K352" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="353" spans="1:11">
@@ -24525,7 +24496,7 @@
         <v>61787</v>
       </c>
       <c r="K353" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="354" spans="1:11">
@@ -24589,7 +24560,7 @@
         <v>61789</v>
       </c>
       <c r="K355" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="356" spans="1:11">
@@ -24653,7 +24624,7 @@
         <v>61791</v>
       </c>
       <c r="K357" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="358" spans="1:11">
@@ -24685,7 +24656,7 @@
         <v>61792</v>
       </c>
       <c r="K358" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="359" spans="1:11">
@@ -24813,7 +24784,7 @@
         <v>61796</v>
       </c>
       <c r="K362" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="363" spans="1:11">
@@ -24909,7 +24880,7 @@
         <v>61819</v>
       </c>
       <c r="K365" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="366" spans="1:11">
@@ -24941,7 +24912,7 @@
         <v>61820</v>
       </c>
       <c r="K366" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="367" spans="1:11">
@@ -25005,7 +24976,7 @@
         <v>61822</v>
       </c>
       <c r="K368" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="369" spans="1:11">
@@ -25069,7 +25040,7 @@
         <v>61828</v>
       </c>
       <c r="K370" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="371" spans="1:11">
@@ -25165,7 +25136,7 @@
         <v>61883</v>
       </c>
       <c r="K373" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="374" spans="1:11">
@@ -25197,7 +25168,7 @@
         <v>61886</v>
       </c>
       <c r="K374" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="375" spans="1:11">
@@ -25229,7 +25200,7 @@
         <v>61887</v>
       </c>
       <c r="K375" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="376" spans="1:11">
@@ -25293,7 +25264,7 @@
         <v>61890</v>
       </c>
       <c r="K377" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="378" spans="1:11">
@@ -25325,7 +25296,7 @@
         <v>61893</v>
       </c>
       <c r="K378" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="379" spans="1:11">
@@ -25421,7 +25392,7 @@
         <v>61912</v>
       </c>
       <c r="K381" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="382" spans="1:11">
@@ -25453,7 +25424,7 @@
         <v>61915</v>
       </c>
       <c r="K382" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="383" spans="1:11">
@@ -25485,7 +25456,7 @@
         <v>61919</v>
       </c>
       <c r="K383" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="384" spans="1:11">
@@ -25549,7 +25520,7 @@
         <v>61922</v>
       </c>
       <c r="K385" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="386" spans="1:11">
@@ -25613,7 +25584,7 @@
         <v>61931</v>
       </c>
       <c r="K387" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="388" spans="1:11">
@@ -25645,7 +25616,7 @@
         <v>61933</v>
       </c>
       <c r="K388" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="389" spans="1:11">
@@ -25677,7 +25648,7 @@
         <v>61945</v>
       </c>
       <c r="K389" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="390" spans="1:11">
@@ -25709,7 +25680,7 @@
         <v>61948</v>
       </c>
       <c r="K390" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="391" spans="1:11">
@@ -25773,7 +25744,7 @@
         <v>61960</v>
       </c>
       <c r="K392" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="393" spans="1:11">
@@ -25837,7 +25808,7 @@
         <v>61964</v>
       </c>
       <c r="K394" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="395" spans="1:11">
@@ -25869,7 +25840,7 @@
         <v>61965</v>
       </c>
       <c r="K395" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="396" spans="1:11">
@@ -25933,7 +25904,7 @@
         <v>61970</v>
       </c>
       <c r="K397" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="398" spans="1:11">
@@ -25965,7 +25936,7 @@
         <v>62031</v>
       </c>
       <c r="K398" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="399" spans="1:11">
@@ -25997,7 +25968,7 @@
         <v>62067</v>
       </c>
       <c r="K399" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="400" spans="1:11">
@@ -26029,7 +26000,7 @@
         <v>62074</v>
       </c>
       <c r="K400" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="401" spans="1:11">
@@ -26125,7 +26096,7 @@
         <v>62117</v>
       </c>
       <c r="K403" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="404" spans="1:11">
@@ -26157,7 +26128,7 @@
         <v>62121</v>
       </c>
       <c r="K404" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="405" spans="1:11">
@@ -26189,7 +26160,7 @@
         <v>62140</v>
       </c>
       <c r="K405" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="406" spans="1:11">
@@ -26221,7 +26192,7 @@
         <v>62141</v>
       </c>
       <c r="K406" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="407" spans="1:11">
@@ -26285,7 +26256,7 @@
         <v>62144</v>
       </c>
       <c r="K408" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="409" spans="1:11">
@@ -26317,7 +26288,7 @@
         <v>62146</v>
       </c>
       <c r="K409" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="410" spans="1:11">
@@ -26349,7 +26320,7 @@
         <v>62147</v>
       </c>
       <c r="K410" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="411" spans="1:11">
@@ -26381,7 +26352,7 @@
         <v>62148</v>
       </c>
       <c r="K411" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="412" spans="1:11">
@@ -26413,7 +26384,7 @@
         <v>62149</v>
       </c>
       <c r="K412" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="413" spans="1:11">
@@ -26445,7 +26416,7 @@
         <v>62150</v>
       </c>
       <c r="K413" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="414" spans="1:11">
@@ -26477,7 +26448,7 @@
         <v>62178</v>
       </c>
       <c r="K414" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="415" spans="1:11">
@@ -26509,7 +26480,7 @@
         <v>62181</v>
       </c>
       <c r="K415" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="416" spans="1:11">
@@ -26541,7 +26512,7 @@
         <v>62183</v>
       </c>
       <c r="K416" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="417" spans="1:11">
@@ -26573,7 +26544,7 @@
         <v>62186</v>
       </c>
       <c r="K417" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="418" spans="1:11">
@@ -26605,7 +26576,7 @@
         <v>62191</v>
       </c>
       <c r="K418" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="419" spans="1:11">
@@ -26637,7 +26608,7 @@
         <v>62193</v>
       </c>
       <c r="K419" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="420" spans="1:11">
@@ -26701,7 +26672,7 @@
         <v>62195</v>
       </c>
       <c r="K421" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="422" spans="1:11">
@@ -26829,7 +26800,7 @@
         <v>62225</v>
       </c>
       <c r="K425" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="426" spans="1:11">
@@ -26861,7 +26832,7 @@
         <v>62233</v>
       </c>
       <c r="K426" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="427" spans="1:11">
@@ -26893,7 +26864,7 @@
         <v>62242</v>
       </c>
       <c r="K427" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="428" spans="1:11">
@@ -26925,7 +26896,7 @@
         <v>62256</v>
       </c>
       <c r="K428" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="429" spans="1:11">
@@ -26954,7 +26925,7 @@
         <v>62257</v>
       </c>
       <c r="K429" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="430" spans="1:11">
@@ -26986,7 +26957,7 @@
         <v>62259</v>
       </c>
       <c r="K430" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="431" spans="1:11">
@@ -27047,7 +27018,7 @@
         <v>62266</v>
       </c>
       <c r="K432" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="433" spans="1:11">
@@ -27079,7 +27050,7 @@
         <v>62334</v>
       </c>
       <c r="K433" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="434" spans="1:11">
@@ -27143,7 +27114,7 @@
         <v>62517</v>
       </c>
       <c r="K435" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="436" spans="1:11">
@@ -27175,7 +27146,7 @@
         <v>62529</v>
       </c>
       <c r="K436" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="437" spans="1:11">
@@ -27207,7 +27178,7 @@
         <v>62531</v>
       </c>
       <c r="K437" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="438" spans="1:11">
@@ -27239,7 +27210,7 @@
         <v>62532</v>
       </c>
       <c r="K438" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="439" spans="1:11">
@@ -27271,7 +27242,7 @@
         <v>62592</v>
       </c>
       <c r="K439" t="s">
-        <v>4250</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="440" spans="1:11">
@@ -27303,7 +27274,7 @@
         <v>62593</v>
       </c>
       <c r="K440" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="441" spans="1:11">
@@ -27559,7 +27530,7 @@
         <v>62633</v>
       </c>
       <c r="K448" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="449" spans="1:11">
@@ -27655,7 +27626,7 @@
         <v>62680</v>
       </c>
       <c r="K451" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="452" spans="1:11">
@@ -27751,7 +27722,7 @@
         <v>62683</v>
       </c>
       <c r="K454" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="455" spans="1:11">
@@ -27783,7 +27754,7 @@
         <v>62684</v>
       </c>
       <c r="K455" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="456" spans="1:11">
@@ -27847,7 +27818,7 @@
         <v>62724</v>
       </c>
       <c r="K457" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="458" spans="1:11">
@@ -27943,7 +27914,7 @@
         <v>62727</v>
       </c>
       <c r="K460" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="461" spans="1:11">
@@ -28071,7 +28042,7 @@
         <v>62762</v>
       </c>
       <c r="K464" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="465" spans="1:11">
@@ -28103,7 +28074,7 @@
         <v>62763</v>
       </c>
       <c r="K465" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="466" spans="1:11">
@@ -28263,7 +28234,7 @@
         <v>62794</v>
       </c>
       <c r="K470" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="471" spans="1:11">
@@ -28359,7 +28330,7 @@
         <v>62805</v>
       </c>
       <c r="K473" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="474" spans="1:11">
@@ -28391,7 +28362,7 @@
         <v>62812</v>
       </c>
       <c r="K474" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="475" spans="1:11">
@@ -28455,7 +28426,7 @@
         <v>62818</v>
       </c>
       <c r="K476" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="477" spans="1:11">
@@ -28487,7 +28458,7 @@
         <v>62835</v>
       </c>
       <c r="K477" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="478" spans="1:11">
@@ -28551,7 +28522,7 @@
         <v>62853</v>
       </c>
       <c r="K479" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="480" spans="1:11">
@@ -28583,7 +28554,7 @@
         <v>62855</v>
       </c>
       <c r="K480" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="481" spans="1:11">
@@ -28615,7 +28586,7 @@
         <v>62857</v>
       </c>
       <c r="K481" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="482" spans="1:11">
@@ -28647,7 +28618,7 @@
         <v>62858</v>
       </c>
       <c r="K482" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="483" spans="1:11">
@@ -28679,7 +28650,7 @@
         <v>62859</v>
       </c>
       <c r="K483" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="484" spans="1:11">
@@ -28743,7 +28714,7 @@
         <v>62862</v>
       </c>
       <c r="K485" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="486" spans="1:11">
@@ -28967,7 +28938,7 @@
         <v>62879</v>
       </c>
       <c r="K492" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="493" spans="1:11">
@@ -28999,7 +28970,7 @@
         <v>62880</v>
       </c>
       <c r="K493" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="494" spans="1:11">
@@ -29031,7 +29002,7 @@
         <v>62881</v>
       </c>
       <c r="K494" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="495" spans="1:11">
@@ -29063,7 +29034,7 @@
         <v>62882</v>
       </c>
       <c r="K495" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="496" spans="1:11">
@@ -29415,7 +29386,7 @@
         <v>62921</v>
       </c>
       <c r="K506" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="507" spans="1:11">
@@ -29479,7 +29450,7 @@
         <v>62923</v>
       </c>
       <c r="K508" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="509" spans="1:11">
@@ -29671,7 +29642,7 @@
         <v>62941</v>
       </c>
       <c r="K514" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="515" spans="1:11">
@@ -29767,7 +29738,7 @@
         <v>62959</v>
       </c>
       <c r="K517" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="518" spans="1:11">
@@ -29895,7 +29866,7 @@
         <v>62977</v>
       </c>
       <c r="K521" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="522" spans="1:11">
@@ -29927,7 +29898,7 @@
         <v>62979</v>
       </c>
       <c r="K522" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="523" spans="1:11">
@@ -29959,7 +29930,7 @@
         <v>62980</v>
       </c>
       <c r="K523" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="524" spans="1:11">
@@ -29991,7 +29962,7 @@
         <v>62983</v>
       </c>
       <c r="K524" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="525" spans="1:11">
@@ -30087,7 +30058,7 @@
         <v>62996</v>
       </c>
       <c r="K527" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="528" spans="1:11">
@@ -30119,7 +30090,7 @@
         <v>62997</v>
       </c>
       <c r="K528" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="529" spans="1:11">
@@ -30183,7 +30154,7 @@
         <v>63005</v>
       </c>
       <c r="K530" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="531" spans="1:11">
@@ -30215,7 +30186,7 @@
         <v>63006</v>
       </c>
       <c r="K531" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="532" spans="1:11">
@@ -30279,7 +30250,7 @@
         <v>63010</v>
       </c>
       <c r="K533" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="534" spans="1:11">
@@ -30471,7 +30442,7 @@
         <v>63018</v>
       </c>
       <c r="K539" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="540" spans="1:11">
@@ -30503,7 +30474,7 @@
         <v>63020</v>
       </c>
       <c r="K540" t="s">
-        <v>4251</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="541" spans="1:11">
@@ -30535,7 +30506,7 @@
         <v>63021</v>
       </c>
       <c r="K541" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="542" spans="1:11">
@@ -30567,7 +30538,7 @@
         <v>63022</v>
       </c>
       <c r="K542" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="543" spans="1:11">
@@ -30599,7 +30570,7 @@
         <v>63023</v>
       </c>
       <c r="K543" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="544" spans="1:11">
@@ -30631,7 +30602,7 @@
         <v>63025</v>
       </c>
       <c r="K544" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="545" spans="1:11">
@@ -30663,7 +30634,7 @@
         <v>63026</v>
       </c>
       <c r="K545" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="546" spans="1:11">
@@ -30695,7 +30666,7 @@
         <v>63028</v>
       </c>
       <c r="K546" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="547" spans="1:11">
@@ -30727,7 +30698,7 @@
         <v>63029</v>
       </c>
       <c r="K547" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="548" spans="1:11">
@@ -30791,7 +30762,7 @@
         <v>63031</v>
       </c>
       <c r="K549" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="550" spans="1:11">
@@ -30919,7 +30890,7 @@
         <v>63051</v>
       </c>
       <c r="K553" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="554" spans="1:11">
@@ -30951,7 +30922,7 @@
         <v>63052</v>
       </c>
       <c r="K554" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="555" spans="1:11">
@@ -30983,7 +30954,7 @@
         <v>63082</v>
       </c>
       <c r="K555" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="556" spans="1:11">
@@ -31015,7 +30986,7 @@
         <v>63085</v>
       </c>
       <c r="K556" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="557" spans="1:11">
@@ -31047,7 +31018,7 @@
         <v>63086</v>
       </c>
       <c r="K557" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="558" spans="1:11">
@@ -31079,7 +31050,7 @@
         <v>63091</v>
       </c>
       <c r="K558" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="559" spans="1:11">
@@ -31175,7 +31146,7 @@
         <v>63108</v>
       </c>
       <c r="K561" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="562" spans="1:11">
@@ -31271,7 +31242,7 @@
         <v>63130</v>
       </c>
       <c r="K564" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="565" spans="1:11">
@@ -31431,7 +31402,7 @@
         <v>63227</v>
       </c>
       <c r="K569" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="570" spans="1:11">
@@ -31559,7 +31530,7 @@
         <v>63338</v>
       </c>
       <c r="K573" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="574" spans="1:11">
@@ -31687,7 +31658,7 @@
         <v>63364</v>
       </c>
       <c r="K577" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="578" spans="1:11">
@@ -31719,7 +31690,7 @@
         <v>63372</v>
       </c>
       <c r="K578" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="579" spans="1:11">
@@ -31780,7 +31751,7 @@
         <v>63389</v>
       </c>
       <c r="K580" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="581" spans="1:11">
@@ -31812,7 +31783,7 @@
         <v>63391</v>
       </c>
       <c r="K581" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="582" spans="1:11">
@@ -31844,7 +31815,7 @@
         <v>63395</v>
       </c>
       <c r="K582" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="583" spans="1:11">
@@ -31908,7 +31879,7 @@
         <v>63398</v>
       </c>
       <c r="K584" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="585" spans="1:11">
@@ -31940,7 +31911,7 @@
         <v>63403</v>
       </c>
       <c r="K585" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="586" spans="1:11">
@@ -31972,7 +31943,7 @@
         <v>63405</v>
       </c>
       <c r="K586" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="587" spans="1:11">
@@ -32004,7 +31975,7 @@
         <v>63413</v>
       </c>
       <c r="K587" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="588" spans="1:11">
@@ -32100,7 +32071,7 @@
         <v>63479</v>
       </c>
       <c r="K590" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="591" spans="1:11">
@@ -32260,7 +32231,7 @@
         <v>63534</v>
       </c>
       <c r="K595" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="596" spans="1:11">
@@ -32292,7 +32263,7 @@
         <v>63536</v>
       </c>
       <c r="K596" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="597" spans="1:11">
@@ -32324,7 +32295,7 @@
         <v>63537</v>
       </c>
       <c r="K597" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="598" spans="1:11">
@@ -32388,7 +32359,7 @@
         <v>63539</v>
       </c>
       <c r="K599" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="600" spans="1:11">
@@ -32452,7 +32423,7 @@
         <v>63550</v>
       </c>
       <c r="K601" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="602" spans="1:11">
@@ -32548,7 +32519,7 @@
         <v>63613</v>
       </c>
       <c r="K604" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="605" spans="1:11">
@@ -32580,7 +32551,7 @@
         <v>63614</v>
       </c>
       <c r="K605" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="606" spans="1:11">
@@ -32644,7 +32615,7 @@
         <v>63617</v>
       </c>
       <c r="K607" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="608" spans="1:11">
@@ -32676,7 +32647,7 @@
         <v>63618</v>
       </c>
       <c r="K608" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="609" spans="1:11">
@@ -32740,7 +32711,7 @@
         <v>63684</v>
       </c>
       <c r="K610" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="611" spans="1:11">
@@ -32772,7 +32743,7 @@
         <v>63693</v>
       </c>
       <c r="K611" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="612" spans="1:11">
@@ -32804,7 +32775,7 @@
         <v>63797</v>
       </c>
       <c r="K612" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="613" spans="1:11">
@@ -32836,7 +32807,7 @@
         <v>63819</v>
       </c>
       <c r="K613" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="614" spans="1:11">
@@ -32900,7 +32871,7 @@
         <v>63842</v>
       </c>
       <c r="K615" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="616" spans="1:11">
@@ -32932,7 +32903,7 @@
         <v>63846</v>
       </c>
       <c r="K616" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="617" spans="1:11">
@@ -32964,7 +32935,7 @@
         <v>63850</v>
       </c>
       <c r="K617" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="618" spans="1:11">
@@ -32996,7 +32967,7 @@
         <v>63851</v>
       </c>
       <c r="K618" t="s">
-        <v>4243</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="619" spans="1:11">
@@ -33028,7 +32999,7 @@
         <v>63853</v>
       </c>
       <c r="K619" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="620" spans="1:11">
@@ -33092,7 +33063,7 @@
         <v>63873</v>
       </c>
       <c r="K621" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="622" spans="1:11">
@@ -33124,7 +33095,7 @@
         <v>63893</v>
       </c>
       <c r="K622" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="623" spans="1:11">
@@ -33156,7 +33127,7 @@
         <v>63894</v>
       </c>
       <c r="K623" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="624" spans="1:11">
@@ -33220,7 +33191,7 @@
         <v>63900</v>
       </c>
       <c r="K625" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="626" spans="1:11">
@@ -33252,7 +33223,7 @@
         <v>63954</v>
       </c>
       <c r="K626" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="627" spans="1:11">
@@ -33284,7 +33255,7 @@
         <v>63955</v>
       </c>
       <c r="K627" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="628" spans="1:11">
@@ -33316,7 +33287,7 @@
         <v>63959</v>
       </c>
       <c r="K628" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="629" spans="1:11">
@@ -33348,7 +33319,7 @@
         <v>63985</v>
       </c>
       <c r="K629" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="630" spans="1:11">
@@ -33380,7 +33351,7 @@
         <v>64060</v>
       </c>
       <c r="K630" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="631" spans="1:11">
@@ -33412,7 +33383,7 @@
         <v>64073</v>
       </c>
       <c r="K631" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="632" spans="1:11">
@@ -33444,7 +33415,7 @@
         <v>64077</v>
       </c>
       <c r="K632" t="s">
-        <v>4246</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="633" spans="1:11">
@@ -33508,7 +33479,7 @@
         <v>64109</v>
       </c>
       <c r="K634" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="635" spans="1:11">
@@ -33540,7 +33511,7 @@
         <v>64121</v>
       </c>
       <c r="K635" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="636" spans="1:11">
@@ -33572,7 +33543,7 @@
         <v>64122</v>
       </c>
       <c r="K636" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="637" spans="1:11">
@@ -33604,7 +33575,7 @@
         <v>64123</v>
       </c>
       <c r="K637" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="638" spans="1:11">
@@ -33636,7 +33607,7 @@
         <v>64124</v>
       </c>
       <c r="K638" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="639" spans="1:11">
@@ -33668,7 +33639,7 @@
         <v>64152</v>
       </c>
       <c r="K639" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="640" spans="1:11">
@@ -33732,7 +33703,7 @@
         <v>64197</v>
       </c>
       <c r="K641" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="642" spans="1:11">
@@ -33828,7 +33799,7 @@
         <v>64249</v>
       </c>
       <c r="K644" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="645" spans="1:11">
@@ -33924,7 +33895,7 @@
         <v>64397</v>
       </c>
       <c r="K647" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="648" spans="1:11">
@@ -33956,7 +33927,7 @@
         <v>64408</v>
       </c>
       <c r="K648" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="649" spans="1:11">
@@ -34020,7 +33991,7 @@
         <v>64410</v>
       </c>
       <c r="K650" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="651" spans="1:11">
@@ -34052,7 +34023,7 @@
         <v>64438</v>
       </c>
       <c r="K651" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="652" spans="1:11">
@@ -34084,7 +34055,7 @@
         <v>64449</v>
       </c>
       <c r="K652" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="653" spans="1:11">
@@ -34180,7 +34151,7 @@
         <v>64516</v>
       </c>
       <c r="K655" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="656" spans="1:11">
@@ -34276,7 +34247,7 @@
         <v>64548</v>
       </c>
       <c r="K658" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="659" spans="1:11">
@@ -34308,7 +34279,7 @@
         <v>64560</v>
       </c>
       <c r="K659" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="660" spans="1:11">
@@ -34401,7 +34372,7 @@
         <v>64762</v>
       </c>
       <c r="K662" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="663" spans="1:11">
@@ -34433,7 +34404,7 @@
         <v>64763</v>
       </c>
       <c r="K663" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="664" spans="1:11">
@@ -34529,7 +34500,7 @@
         <v>64769</v>
       </c>
       <c r="K666" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="667" spans="1:11">
@@ -34561,7 +34532,7 @@
         <v>64770</v>
       </c>
       <c r="K667" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="668" spans="1:11">
@@ -34625,7 +34596,7 @@
         <v>64777</v>
       </c>
       <c r="K669" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="670" spans="1:11">
@@ -35000,7 +34971,7 @@
         <v>65994</v>
       </c>
       <c r="K681" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="682" spans="1:11">
@@ -35032,7 +35003,7 @@
         <v>66555</v>
       </c>
       <c r="K682" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="683" spans="1:11">
@@ -35241,7 +35212,7 @@
         <v>99309</v>
       </c>
       <c r="K689" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="690" spans="1:11">
@@ -35273,7 +35244,7 @@
         <v>99310</v>
       </c>
       <c r="K690" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="691" spans="1:11">
@@ -35305,7 +35276,7 @@
         <v>101166</v>
       </c>
       <c r="K691" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="692" spans="1:11">
@@ -35337,7 +35308,7 @@
         <v>101316</v>
       </c>
       <c r="K692" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="693" spans="1:11">
@@ -35398,7 +35369,7 @@
         <v>101374</v>
       </c>
       <c r="K694" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="695" spans="1:11">
@@ -35526,7 +35497,7 @@
         <v>103231</v>
       </c>
       <c r="K698" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="699" spans="1:11">
@@ -35622,7 +35593,7 @@
         <v>103805</v>
       </c>
       <c r="K701" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="702" spans="1:11">
@@ -35846,7 +35817,7 @@
         <v>104796</v>
       </c>
       <c r="K708" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="709" spans="1:11">
@@ -35878,7 +35849,7 @@
         <v>105309</v>
       </c>
       <c r="K709" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="710" spans="1:11">
@@ -35942,7 +35913,7 @@
         <v>106029</v>
       </c>
       <c r="K711" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="712" spans="1:11">
@@ -35974,7 +35945,7 @@
         <v>106034</v>
       </c>
       <c r="K712" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="713" spans="1:11">
@@ -36038,7 +36009,7 @@
         <v>107137</v>
       </c>
       <c r="K714" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="715" spans="1:11">
@@ -36102,7 +36073,7 @@
         <v>107488</v>
       </c>
       <c r="K716" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="717" spans="1:11">
@@ -36134,7 +36105,7 @@
         <v>109957</v>
       </c>
       <c r="K717" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="718" spans="1:11">
@@ -36230,7 +36201,7 @@
         <v>110221</v>
       </c>
       <c r="K720" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="721" spans="1:11">
@@ -36294,7 +36265,7 @@
         <v>110513</v>
       </c>
       <c r="K722" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="723" spans="1:11">
@@ -36361,7 +36332,7 @@
         <v>111560</v>
       </c>
       <c r="K724" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="725" spans="1:11">
@@ -36393,7 +36364,7 @@
         <v>111606</v>
       </c>
       <c r="K725" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="726" spans="1:11">
@@ -36489,7 +36460,7 @@
         <v>112015</v>
       </c>
       <c r="K728" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="729" spans="1:11">
@@ -36521,7 +36492,7 @@
         <v>112563</v>
       </c>
       <c r="K729" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="730" spans="1:11">
@@ -36553,7 +36524,7 @@
         <v>113827</v>
       </c>
       <c r="K730" t="s">
-        <v>4243</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="731" spans="1:11">
@@ -36742,7 +36713,7 @@
         <v>118860</v>
       </c>
       <c r="K736" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="737" spans="1:11">
@@ -36774,7 +36745,7 @@
         <v>120077</v>
       </c>
       <c r="K737" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="738" spans="1:11">
@@ -36806,7 +36777,7 @@
         <v>120305</v>
       </c>
       <c r="K738" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="739" spans="1:11">
@@ -36838,7 +36809,7 @@
         <v>120627</v>
       </c>
       <c r="K739" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="740" spans="1:11">
@@ -36899,7 +36870,7 @@
         <v>121959</v>
       </c>
       <c r="K741" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="742" spans="1:11">
@@ -36931,7 +36902,7 @@
         <v>122272</v>
       </c>
       <c r="K742" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="743" spans="1:11">
@@ -37050,7 +37021,7 @@
         <v>122882</v>
       </c>
       <c r="K746" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="747" spans="1:11">
@@ -37082,7 +37053,7 @@
         <v>123288</v>
       </c>
       <c r="K747" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="748" spans="1:11">
@@ -37233,7 +37204,7 @@
         <v>127235</v>
       </c>
       <c r="K752" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="753" spans="1:11">
@@ -37265,7 +37236,7 @@
         <v>127268</v>
       </c>
       <c r="K753" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="754" spans="1:11">
@@ -37297,7 +37268,7 @@
         <v>127289</v>
       </c>
       <c r="K754" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="755" spans="1:11">
@@ -37457,7 +37428,7 @@
         <v>129297</v>
       </c>
       <c r="K759" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="760" spans="1:11">
@@ -37486,7 +37457,7 @@
         <v>129313</v>
       </c>
       <c r="K760" t="s">
-        <v>4252</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="761" spans="1:11">
@@ -37518,7 +37489,7 @@
         <v>129400</v>
       </c>
       <c r="K761" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="762" spans="1:11">
@@ -37550,7 +37521,7 @@
         <v>129401</v>
       </c>
       <c r="K762" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="763" spans="1:11">
@@ -37582,7 +37553,7 @@
         <v>129421</v>
       </c>
       <c r="K763" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="764" spans="1:11">
@@ -37646,7 +37617,7 @@
         <v>129444</v>
       </c>
       <c r="K765" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="766" spans="1:11">
@@ -37710,7 +37681,7 @@
         <v>129452</v>
       </c>
       <c r="K767" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="768" spans="1:11">
@@ -37742,7 +37713,7 @@
         <v>129454</v>
       </c>
       <c r="K768" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="769" spans="1:11">
@@ -37774,7 +37745,7 @@
         <v>129456</v>
       </c>
       <c r="K769" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="770" spans="1:11">
@@ -37902,7 +37873,7 @@
         <v>129464</v>
       </c>
       <c r="K773" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="774" spans="1:11">
@@ -37934,7 +37905,7 @@
         <v>129510</v>
       </c>
       <c r="K774" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="775" spans="1:11">
@@ -37966,7 +37937,7 @@
         <v>129525</v>
       </c>
       <c r="K775" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="776" spans="1:11">
@@ -38030,7 +38001,7 @@
         <v>129536</v>
       </c>
       <c r="K777" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="778" spans="1:11">
@@ -38126,7 +38097,7 @@
         <v>129569</v>
       </c>
       <c r="K780" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="781" spans="1:11">
@@ -38190,7 +38161,7 @@
         <v>129586</v>
       </c>
       <c r="K782" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="783" spans="1:11">
@@ -38222,7 +38193,7 @@
         <v>129588</v>
       </c>
       <c r="K783" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="784" spans="1:11">
@@ -38254,7 +38225,7 @@
         <v>129589</v>
       </c>
       <c r="K784" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="785" spans="1:11">
@@ -38286,7 +38257,7 @@
         <v>129592</v>
       </c>
       <c r="K785" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="786" spans="1:11">
@@ -38350,7 +38321,7 @@
         <v>129594</v>
       </c>
       <c r="K787" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="788" spans="1:11">
@@ -38446,7 +38417,7 @@
         <v>129603</v>
       </c>
       <c r="K790" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="791" spans="1:11">
@@ -38478,7 +38449,7 @@
         <v>129605</v>
       </c>
       <c r="K791" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="792" spans="1:11">
@@ -38510,7 +38481,7 @@
         <v>129656</v>
       </c>
       <c r="K792" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="793" spans="1:11">
@@ -38699,7 +38670,7 @@
         <v>129692</v>
       </c>
       <c r="K798" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="799" spans="1:11">
@@ -38731,7 +38702,7 @@
         <v>129706</v>
       </c>
       <c r="K799" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="800" spans="1:11">
@@ -38795,7 +38766,7 @@
         <v>129769</v>
       </c>
       <c r="K801" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="802" spans="1:11">
@@ -38919,9 +38890,6 @@
       <c r="H805">
         <v>11</v>
       </c>
-      <c r="I805" t="s">
-        <v>4225</v>
-      </c>
       <c r="J805">
         <v>129792</v>
       </c>
@@ -38958,7 +38926,7 @@
         <v>129794</v>
       </c>
       <c r="K806" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="807" spans="1:11">
@@ -39022,7 +38990,7 @@
         <v>129796</v>
       </c>
       <c r="K808" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="809" spans="1:11">
@@ -39054,7 +39022,7 @@
         <v>129797</v>
       </c>
       <c r="K809" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="810" spans="1:11">
@@ -39086,7 +39054,7 @@
         <v>129798</v>
       </c>
       <c r="K810" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="811" spans="1:11">
@@ -39118,7 +39086,7 @@
         <v>129801</v>
       </c>
       <c r="K811" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="812" spans="1:11">
@@ -39150,7 +39118,7 @@
         <v>129863</v>
       </c>
       <c r="K812" t="s">
-        <v>4253</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="813" spans="1:11">
@@ -39182,7 +39150,7 @@
         <v>129867</v>
       </c>
       <c r="K813" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="814" spans="1:11">
@@ -39214,7 +39182,7 @@
         <v>129869</v>
       </c>
       <c r="K814" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="815" spans="1:11">
@@ -39301,16 +39269,16 @@
         <v>3754</v>
       </c>
       <c r="G817" t="s">
-        <v>4054</v>
+        <v>3982</v>
       </c>
       <c r="H817">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J817">
         <v>129902</v>
       </c>
       <c r="K817" t="s">
-        <v>4088</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="818" spans="1:11">
@@ -39397,7 +39365,7 @@
         <v>3754</v>
       </c>
       <c r="G820" t="s">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="H820">
         <v>33</v>
@@ -39502,7 +39470,7 @@
         <v>130079</v>
       </c>
       <c r="K823" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="824" spans="1:11">
@@ -39534,7 +39502,7 @@
         <v>130080</v>
       </c>
       <c r="K824" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="825" spans="1:11">
@@ -39566,7 +39534,7 @@
         <v>130082</v>
       </c>
       <c r="K825" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="826" spans="1:11">
@@ -39598,7 +39566,7 @@
         <v>130083</v>
       </c>
       <c r="K826" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="827" spans="1:11">
@@ -39685,7 +39653,7 @@
         <v>3754</v>
       </c>
       <c r="G829" t="s">
-        <v>4056</v>
+        <v>4055</v>
       </c>
       <c r="H829">
         <v>33</v>
@@ -39694,7 +39662,7 @@
         <v>130162</v>
       </c>
       <c r="K829" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="830" spans="1:11">
@@ -39717,7 +39685,7 @@
         <v>3754</v>
       </c>
       <c r="G830" t="s">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="H830">
         <v>33</v>
@@ -39726,7 +39694,7 @@
         <v>130163</v>
       </c>
       <c r="K830" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="831" spans="1:11">
@@ -39749,7 +39717,7 @@
         <v>3754</v>
       </c>
       <c r="G831" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="H831">
         <v>35</v>
@@ -39781,7 +39749,7 @@
         <v>3754</v>
       </c>
       <c r="G832" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="H832">
         <v>35</v>
@@ -39845,7 +39813,7 @@
         <v>3754</v>
       </c>
       <c r="G834" t="s">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="H834">
         <v>18</v>
@@ -39854,7 +39822,7 @@
         <v>130217</v>
       </c>
       <c r="K834" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="835" spans="1:11">
@@ -39877,7 +39845,7 @@
         <v>3754</v>
       </c>
       <c r="G835" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="H835">
         <v>18</v>
@@ -39886,7 +39854,7 @@
         <v>130218</v>
       </c>
       <c r="K835" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="836" spans="1:11">
@@ -39918,7 +39886,7 @@
         <v>130224</v>
       </c>
       <c r="K836" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="837" spans="1:11">
@@ -39950,7 +39918,7 @@
         <v>130229</v>
       </c>
       <c r="K837" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="838" spans="1:11">
@@ -39982,7 +39950,7 @@
         <v>130230</v>
       </c>
       <c r="K838" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="839" spans="1:11">
@@ -40005,7 +39973,7 @@
         <v>3754</v>
       </c>
       <c r="G839" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="H839">
         <v>14</v>
@@ -40014,7 +39982,7 @@
         <v>130293</v>
       </c>
       <c r="K839" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="840" spans="1:11">
@@ -40046,7 +40014,7 @@
         <v>130294</v>
       </c>
       <c r="K840" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="841" spans="1:11">
@@ -40101,7 +40069,7 @@
         <v>3754</v>
       </c>
       <c r="G842" t="s">
-        <v>4061</v>
+        <v>4060</v>
       </c>
       <c r="H842">
         <v>15</v>
@@ -40110,7 +40078,7 @@
         <v>130512</v>
       </c>
       <c r="K842" t="s">
-        <v>4255</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="843" spans="1:11">
@@ -40142,7 +40110,7 @@
         <v>130675</v>
       </c>
       <c r="K843" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="844" spans="1:11">
@@ -40197,7 +40165,7 @@
         <v>3754</v>
       </c>
       <c r="G845" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="H845">
         <v>28</v>
@@ -40206,7 +40174,7 @@
         <v>130816</v>
       </c>
       <c r="K845" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="846" spans="1:11">
@@ -40229,7 +40197,7 @@
         <v>3754</v>
       </c>
       <c r="G846" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="H846">
         <v>34</v>
@@ -40238,7 +40206,7 @@
         <v>130828</v>
       </c>
       <c r="K846" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="847" spans="1:11">
@@ -40270,7 +40238,7 @@
         <v>130843</v>
       </c>
       <c r="K847" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="848" spans="1:11">
@@ -40302,7 +40270,7 @@
         <v>130844</v>
       </c>
       <c r="K848" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="849" spans="1:11">
@@ -40325,7 +40293,7 @@
         <v>3754</v>
       </c>
       <c r="G849" t="s">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="H849">
         <v>35</v>
@@ -40366,7 +40334,7 @@
         <v>131086</v>
       </c>
       <c r="K850" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="851" spans="1:11">
@@ -40389,7 +40357,7 @@
         <v>3754</v>
       </c>
       <c r="G851" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H851">
         <v>33</v>
@@ -40398,7 +40366,7 @@
         <v>131160</v>
       </c>
       <c r="K851" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="852" spans="1:11">
@@ -40421,7 +40389,7 @@
         <v>3754</v>
       </c>
       <c r="G852" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H852">
         <v>33</v>
@@ -40430,7 +40398,7 @@
         <v>131161</v>
       </c>
       <c r="K852" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="853" spans="1:11">
@@ -40494,7 +40462,7 @@
         <v>131180</v>
       </c>
       <c r="K854" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="855" spans="1:11">
@@ -40526,7 +40494,7 @@
         <v>131213</v>
       </c>
       <c r="K855" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="856" spans="1:11">
@@ -40581,7 +40549,7 @@
         <v>3754</v>
       </c>
       <c r="G857" t="s">
-        <v>4066</v>
+        <v>4065</v>
       </c>
       <c r="H857">
         <v>17</v>
@@ -40590,7 +40558,7 @@
         <v>131286</v>
       </c>
       <c r="K857" t="s">
-        <v>4256</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="858" spans="1:11">
@@ -40613,7 +40581,7 @@
         <v>3754</v>
       </c>
       <c r="G858" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H858">
         <v>31</v>
@@ -40622,7 +40590,7 @@
         <v>131312</v>
       </c>
       <c r="K858" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="859" spans="1:11">
@@ -40645,7 +40613,7 @@
         <v>3754</v>
       </c>
       <c r="G859" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H859">
         <v>31</v>
@@ -40654,7 +40622,7 @@
         <v>131314</v>
       </c>
       <c r="K859" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="860" spans="1:11">
@@ -40686,7 +40654,7 @@
         <v>131374</v>
       </c>
       <c r="K860" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="861" spans="1:11">
@@ -40750,7 +40718,7 @@
         <v>131389</v>
       </c>
       <c r="K862" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="863" spans="1:11">
@@ -40782,7 +40750,7 @@
         <v>131390</v>
       </c>
       <c r="K863" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="864" spans="1:11">
@@ -40805,7 +40773,7 @@
         <v>3754</v>
       </c>
       <c r="G864" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="H864">
         <v>23</v>
@@ -40837,7 +40805,7 @@
         <v>3754</v>
       </c>
       <c r="G865" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
       <c r="H865">
         <v>22</v>
@@ -40878,7 +40846,7 @@
         <v>131562</v>
       </c>
       <c r="K866" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="867" spans="1:11">
@@ -40942,7 +40910,7 @@
         <v>131697</v>
       </c>
       <c r="K868" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="869" spans="1:11">
@@ -40965,7 +40933,7 @@
         <v>3754</v>
       </c>
       <c r="G869" t="s">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="H869">
         <v>35</v>
@@ -41029,7 +40997,7 @@
         <v>3754</v>
       </c>
       <c r="G871" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="H871">
         <v>33</v>
@@ -41038,7 +41006,7 @@
         <v>131810</v>
       </c>
       <c r="K871" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="872" spans="1:11">
@@ -41070,7 +41038,7 @@
         <v>131811</v>
       </c>
       <c r="K872" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="873" spans="1:11">
@@ -41093,7 +41061,7 @@
         <v>3754</v>
       </c>
       <c r="G873" t="s">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="H873">
         <v>10</v>
@@ -41102,7 +41070,7 @@
         <v>131870</v>
       </c>
       <c r="K873" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="874" spans="1:11">
@@ -41125,7 +41093,7 @@
         <v>3754</v>
       </c>
       <c r="G874" t="s">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="H874">
         <v>35</v>
@@ -41157,7 +41125,7 @@
         <v>3754</v>
       </c>
       <c r="G875" t="s">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="H875">
         <v>35</v>
@@ -41221,7 +41189,7 @@
         <v>3754</v>
       </c>
       <c r="G877" t="s">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="H877">
         <v>20</v>
@@ -41230,7 +41198,7 @@
         <v>131975</v>
       </c>
       <c r="K877" t="s">
-        <v>4257</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="878" spans="1:11">
@@ -41285,7 +41253,7 @@
         <v>3754</v>
       </c>
       <c r="G879" t="s">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="H879">
         <v>14</v>
@@ -41294,7 +41262,7 @@
         <v>132027</v>
       </c>
       <c r="K879" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="880" spans="1:11">
@@ -41358,7 +41326,7 @@
         <v>132029</v>
       </c>
       <c r="K881" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="882" spans="1:11">
@@ -41445,7 +41413,7 @@
         <v>3754</v>
       </c>
       <c r="G884" t="s">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="H884">
         <v>33</v>
@@ -41454,7 +41422,7 @@
         <v>132107</v>
       </c>
       <c r="K884" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="885" spans="1:11">
@@ -41477,7 +41445,7 @@
         <v>3754</v>
       </c>
       <c r="G885" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H885">
         <v>31</v>
@@ -41486,7 +41454,7 @@
         <v>132112</v>
       </c>
       <c r="K885" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="886" spans="1:11">
@@ -41509,7 +41477,7 @@
         <v>3754</v>
       </c>
       <c r="G886" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H886">
         <v>33</v>
@@ -41518,7 +41486,7 @@
         <v>132113</v>
       </c>
       <c r="K886" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="887" spans="1:11">
@@ -41550,7 +41518,7 @@
         <v>132125</v>
       </c>
       <c r="K887" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="888" spans="1:11">
@@ -41573,7 +41541,7 @@
         <v>3754</v>
       </c>
       <c r="G888" t="s">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="H888">
         <v>11</v>
@@ -41614,7 +41582,7 @@
         <v>132164</v>
       </c>
       <c r="K889" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="890" spans="1:11">
@@ -41637,7 +41605,7 @@
         <v>3754</v>
       </c>
       <c r="G890" t="s">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="H890">
         <v>35</v>
@@ -41669,7 +41637,7 @@
         <v>3754</v>
       </c>
       <c r="G891" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H891">
         <v>33</v>
@@ -41710,7 +41678,7 @@
         <v>132170</v>
       </c>
       <c r="K892" t="s">
-        <v>4259</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="893" spans="1:11">
@@ -41742,7 +41710,7 @@
         <v>132171</v>
       </c>
       <c r="K893" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="894" spans="1:11">
@@ -41765,7 +41733,7 @@
         <v>3754</v>
       </c>
       <c r="G894" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H894">
         <v>31</v>
@@ -41774,7 +41742,7 @@
         <v>132172</v>
       </c>
       <c r="K894" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="895" spans="1:11">
@@ -41861,7 +41829,7 @@
         <v>3754</v>
       </c>
       <c r="G897" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H897">
         <v>30</v>
@@ -41870,7 +41838,7 @@
         <v>132182</v>
       </c>
       <c r="K897" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="898" spans="1:11">
@@ -41893,7 +41861,7 @@
         <v>3754</v>
       </c>
       <c r="G898" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="H898">
         <v>14</v>
@@ -41902,7 +41870,7 @@
         <v>132183</v>
       </c>
       <c r="K898" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="899" spans="1:11">
@@ -41925,7 +41893,7 @@
         <v>3754</v>
       </c>
       <c r="G899" t="s">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="H899">
         <v>19</v>
@@ -41957,7 +41925,7 @@
         <v>3754</v>
       </c>
       <c r="G900" t="s">
-        <v>4054</v>
+        <v>4079</v>
       </c>
       <c r="H900">
         <v>19</v>
@@ -42172,7 +42140,7 @@
         <v>132270</v>
       </c>
       <c r="K907" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="908" spans="1:11">
@@ -42236,7 +42204,7 @@
         <v>132311</v>
       </c>
       <c r="K909" t="s">
-        <v>4260</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="910" spans="1:11">
@@ -42268,7 +42236,7 @@
         <v>132367</v>
       </c>
       <c r="K910" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="911" spans="1:11">
@@ -42300,7 +42268,7 @@
         <v>132424</v>
       </c>
       <c r="K911" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="912" spans="1:11">
@@ -42332,7 +42300,7 @@
         <v>132425</v>
       </c>
       <c r="K912" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="913" spans="1:11">
@@ -42355,7 +42323,7 @@
         <v>3754</v>
       </c>
       <c r="G913" t="s">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="H913">
         <v>19</v>
@@ -42396,7 +42364,7 @@
         <v>132446</v>
       </c>
       <c r="K914" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="915" spans="1:11">
@@ -42451,7 +42419,7 @@
         <v>3754</v>
       </c>
       <c r="G916" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H916">
         <v>31</v>
@@ -42460,7 +42428,7 @@
         <v>132676</v>
       </c>
       <c r="K916" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="917" spans="1:11">
@@ -42483,7 +42451,7 @@
         <v>3754</v>
       </c>
       <c r="G917" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H917">
         <v>33</v>
@@ -42547,7 +42515,7 @@
         <v>3754</v>
       </c>
       <c r="G919" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H919">
         <v>33</v>
@@ -42588,7 +42556,7 @@
         <v>132872</v>
       </c>
       <c r="K920" t="s">
-        <v>4259</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="921" spans="1:11">
@@ -42620,7 +42588,7 @@
         <v>133129</v>
       </c>
       <c r="K921" t="s">
-        <v>4261</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="922" spans="1:11">
@@ -42652,7 +42620,7 @@
         <v>133130</v>
       </c>
       <c r="K922" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="923" spans="1:11">
@@ -42716,7 +42684,7 @@
         <v>133362</v>
       </c>
       <c r="K924" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="925" spans="1:11">
@@ -42748,7 +42716,7 @@
         <v>133467</v>
       </c>
       <c r="K925" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="926" spans="1:11">
@@ -42780,7 +42748,7 @@
         <v>133468</v>
       </c>
       <c r="K926" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="927" spans="1:11">
@@ -42812,7 +42780,7 @@
         <v>133469</v>
       </c>
       <c r="K927" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="928" spans="1:11">
@@ -42844,7 +42812,7 @@
         <v>133470</v>
       </c>
       <c r="K928" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="929" spans="1:11">
@@ -42876,7 +42844,7 @@
         <v>133479</v>
       </c>
       <c r="K929" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="930" spans="1:11">
@@ -42908,7 +42876,7 @@
         <v>133544</v>
       </c>
       <c r="K930" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="931" spans="1:11">
@@ -42940,7 +42908,7 @@
         <v>133545</v>
       </c>
       <c r="K931" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="932" spans="1:11">
@@ -42972,7 +42940,7 @@
         <v>133546</v>
       </c>
       <c r="K932" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="933" spans="1:11">
@@ -43004,7 +42972,7 @@
         <v>133607</v>
       </c>
       <c r="K933" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="934" spans="1:11">
@@ -43036,7 +43004,7 @@
         <v>133738</v>
       </c>
       <c r="K934" t="s">
-        <v>4262</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="935" spans="1:11">
@@ -43114,7 +43082,7 @@
         <v>3754</v>
       </c>
       <c r="G937" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H937">
         <v>33</v>
@@ -43155,7 +43123,7 @@
         <v>133780</v>
       </c>
       <c r="K938" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="939" spans="1:11">
@@ -43210,7 +43178,7 @@
         <v>133915</v>
       </c>
       <c r="K940" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="941" spans="1:11">
@@ -43242,7 +43210,7 @@
         <v>133979</v>
       </c>
       <c r="K941" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="942" spans="1:11">
@@ -43297,7 +43265,7 @@
         <v>134012</v>
       </c>
       <c r="K943" t="s">
-        <v>4259</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="944" spans="1:11">
@@ -43416,7 +43384,7 @@
         <v>134091</v>
       </c>
       <c r="K947" t="s">
-        <v>4263</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="948" spans="1:11">
@@ -43512,7 +43480,7 @@
         <v>134209</v>
       </c>
       <c r="K950" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="951" spans="1:11">
@@ -43544,7 +43512,7 @@
         <v>134211</v>
       </c>
       <c r="K951" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="952" spans="1:11">
@@ -43608,7 +43576,7 @@
         <v>134218</v>
       </c>
       <c r="K953" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="954" spans="1:11">
@@ -43654,7 +43622,7 @@
         <v>3754</v>
       </c>
       <c r="G955" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="H955">
         <v>34</v>
@@ -43663,7 +43631,7 @@
         <v>134229</v>
       </c>
       <c r="K955" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="956" spans="1:11">
@@ -43686,7 +43654,7 @@
         <v>3754</v>
       </c>
       <c r="G956" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="H956">
         <v>10</v>
@@ -43695,7 +43663,7 @@
         <v>134231</v>
       </c>
       <c r="K956" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="957" spans="1:11">
@@ -43727,7 +43695,7 @@
         <v>134233</v>
       </c>
       <c r="K957" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="958" spans="1:11">
@@ -43791,7 +43759,7 @@
         <v>134330</v>
       </c>
       <c r="K959" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="960" spans="1:11">
@@ -43846,7 +43814,7 @@
         <v>3754</v>
       </c>
       <c r="G961" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="H961">
         <v>34</v>
@@ -43855,7 +43823,7 @@
         <v>134363</v>
       </c>
       <c r="K961" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="962" spans="1:11">
@@ -44079,7 +44047,7 @@
         <v>134679</v>
       </c>
       <c r="K968" t="s">
-        <v>4264</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="969" spans="1:11">
@@ -44143,7 +44111,7 @@
         <v>134681</v>
       </c>
       <c r="K970" t="s">
-        <v>4264</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="971" spans="1:11">
@@ -44389,14 +44357,8 @@
       <c r="F978" t="s">
         <v>3754</v>
       </c>
-      <c r="H978">
-        <v>19</v>
-      </c>
       <c r="J978">
         <v>134694</v>
-      </c>
-      <c r="K978" t="s">
-        <v>4088</v>
       </c>
     </row>
     <row r="979" spans="1:11">
@@ -44428,7 +44390,7 @@
         <v>134718</v>
       </c>
       <c r="K979" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="980" spans="1:11">
@@ -44748,7 +44710,7 @@
         <v>134731</v>
       </c>
       <c r="K989" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="990" spans="1:11">
@@ -44780,7 +44742,7 @@
         <v>134732</v>
       </c>
       <c r="K990" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="991" spans="1:11">
@@ -44803,7 +44765,7 @@
         <v>3754</v>
       </c>
       <c r="G991" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="H991">
         <v>33</v>
@@ -44812,7 +44774,7 @@
         <v>134733</v>
       </c>
       <c r="K991" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="992" spans="1:11">
@@ -44867,7 +44829,7 @@
         <v>3754</v>
       </c>
       <c r="G993" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H993">
         <v>30</v>
@@ -44876,7 +44838,7 @@
         <v>134735</v>
       </c>
       <c r="K993" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="994" spans="1:11">
@@ -44899,7 +44861,7 @@
         <v>3754</v>
       </c>
       <c r="G994" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H994">
         <v>30</v>
@@ -44908,7 +44870,7 @@
         <v>134736</v>
       </c>
       <c r="K994" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="995" spans="1:11">
@@ -45027,7 +44989,7 @@
         <v>3754</v>
       </c>
       <c r="G998" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H998">
         <v>30</v>
@@ -45036,7 +44998,7 @@
         <v>134742</v>
       </c>
       <c r="K998" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="999" spans="1:11">
@@ -45132,7 +45094,7 @@
         <v>134746</v>
       </c>
       <c r="K1001" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1002" spans="1:11">
@@ -45196,7 +45158,7 @@
         <v>134748</v>
       </c>
       <c r="K1003" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1004" spans="1:11">
@@ -45219,7 +45181,7 @@
         <v>3754</v>
       </c>
       <c r="G1004" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1004">
         <v>31</v>
@@ -45228,7 +45190,7 @@
         <v>134749</v>
       </c>
       <c r="K1004" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1005" spans="1:11">
@@ -45283,7 +45245,7 @@
         <v>134751</v>
       </c>
       <c r="K1006" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="1007" spans="1:11">
@@ -45315,7 +45277,7 @@
         <v>134752</v>
       </c>
       <c r="K1007" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="1008" spans="1:11">
@@ -45347,7 +45309,7 @@
         <v>134753</v>
       </c>
       <c r="K1008" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1009" spans="1:11">
@@ -45379,7 +45341,7 @@
         <v>134754</v>
       </c>
       <c r="K1009" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1010" spans="1:11">
@@ -45411,7 +45373,7 @@
         <v>134755</v>
       </c>
       <c r="K1010" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1011" spans="1:11">
@@ -45443,7 +45405,7 @@
         <v>134757</v>
       </c>
       <c r="K1011" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1012" spans="1:11">
@@ -45475,7 +45437,7 @@
         <v>134758</v>
       </c>
       <c r="K1012" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1013" spans="1:11">
@@ -45507,7 +45469,7 @@
         <v>134759</v>
       </c>
       <c r="K1013" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1014" spans="1:11">
@@ -45539,7 +45501,7 @@
         <v>134760</v>
       </c>
       <c r="K1014" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1015" spans="1:11">
@@ -45571,7 +45533,7 @@
         <v>134761</v>
       </c>
       <c r="K1015" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1016" spans="1:11">
@@ -45594,7 +45556,7 @@
         <v>3754</v>
       </c>
       <c r="G1016" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1016">
         <v>30</v>
@@ -45603,7 +45565,7 @@
         <v>134762</v>
       </c>
       <c r="K1016" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1017" spans="1:11">
@@ -45626,7 +45588,7 @@
         <v>3754</v>
       </c>
       <c r="G1017" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1017">
         <v>31</v>
@@ -45635,7 +45597,7 @@
         <v>134763</v>
       </c>
       <c r="K1017" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1018" spans="1:11">
@@ -45667,7 +45629,7 @@
         <v>134764</v>
       </c>
       <c r="K1018" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1019" spans="1:11">
@@ -45699,7 +45661,7 @@
         <v>134765</v>
       </c>
       <c r="K1019" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1020" spans="1:11">
@@ -45722,7 +45684,7 @@
         <v>3754</v>
       </c>
       <c r="G1020" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1020">
         <v>31</v>
@@ -45731,7 +45693,7 @@
         <v>134766</v>
       </c>
       <c r="K1020" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1021" spans="1:11">
@@ -45795,7 +45757,7 @@
         <v>134768</v>
       </c>
       <c r="K1022" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1023" spans="1:11">
@@ -45827,7 +45789,7 @@
         <v>134769</v>
       </c>
       <c r="K1023" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1024" spans="1:11">
@@ -45859,7 +45821,7 @@
         <v>134770</v>
       </c>
       <c r="K1024" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1025" spans="1:11">
@@ -45882,7 +45844,7 @@
         <v>3754</v>
       </c>
       <c r="G1025" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="H1025">
         <v>19</v>
@@ -45891,7 +45853,7 @@
         <v>134771</v>
       </c>
       <c r="K1025" t="s">
-        <v>4265</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="1026" spans="1:11">
@@ -45914,7 +45876,7 @@
         <v>3754</v>
       </c>
       <c r="G1026" t="s">
-        <v>4054</v>
+        <v>4079</v>
       </c>
       <c r="H1026">
         <v>19</v>
@@ -45955,7 +45917,7 @@
         <v>134773</v>
       </c>
       <c r="K1027" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1028" spans="1:11">
@@ -45987,7 +45949,7 @@
         <v>134774</v>
       </c>
       <c r="K1028" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1029" spans="1:11">
@@ -46019,7 +45981,7 @@
         <v>134775</v>
       </c>
       <c r="K1029" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1030" spans="1:11">
@@ -46051,7 +46013,7 @@
         <v>134776</v>
       </c>
       <c r="K1030" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1031" spans="1:11">
@@ -46179,7 +46141,7 @@
         <v>134789</v>
       </c>
       <c r="K1034" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1035" spans="1:11">
@@ -46211,7 +46173,7 @@
         <v>134791</v>
       </c>
       <c r="K1035" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1036" spans="1:11">
@@ -46243,7 +46205,7 @@
         <v>134792</v>
       </c>
       <c r="K1036" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1037" spans="1:11">
@@ -46330,7 +46292,7 @@
         <v>134824</v>
       </c>
       <c r="K1039" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1040" spans="1:11">
@@ -46458,7 +46420,7 @@
         <v>134828</v>
       </c>
       <c r="K1043" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1044" spans="1:11">
@@ -46522,7 +46484,7 @@
         <v>134830</v>
       </c>
       <c r="K1045" t="s">
-        <v>4267</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="1046" spans="1:11">
@@ -46554,7 +46516,7 @@
         <v>134831</v>
       </c>
       <c r="K1046" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1047" spans="1:11">
@@ -46647,7 +46609,7 @@
         <v>134836</v>
       </c>
       <c r="K1049" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1050" spans="1:11">
@@ -46711,7 +46673,7 @@
         <v>134838</v>
       </c>
       <c r="K1051" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1052" spans="1:11">
@@ -46807,7 +46769,7 @@
         <v>134842</v>
       </c>
       <c r="K1054" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1055" spans="1:11">
@@ -46871,7 +46833,7 @@
         <v>134844</v>
       </c>
       <c r="K1056" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1057" spans="1:11">
@@ -46903,7 +46865,7 @@
         <v>134845</v>
       </c>
       <c r="K1057" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1058" spans="1:11">
@@ -47031,7 +46993,7 @@
         <v>134860</v>
       </c>
       <c r="K1061" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1062" spans="1:11">
@@ -47077,7 +47039,7 @@
         <v>3754</v>
       </c>
       <c r="G1063" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1063">
         <v>33</v>
@@ -47118,7 +47080,7 @@
         <v>134865</v>
       </c>
       <c r="K1064" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1065" spans="1:11">
@@ -47150,7 +47112,7 @@
         <v>134866</v>
       </c>
       <c r="K1065" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="1066" spans="1:11">
@@ -47251,7 +47213,7 @@
         <v>3754</v>
       </c>
       <c r="G1069" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="H1069">
         <v>23</v>
@@ -47260,7 +47222,7 @@
         <v>134872</v>
       </c>
       <c r="K1069" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1070" spans="1:11">
@@ -47315,7 +47277,7 @@
         <v>3754</v>
       </c>
       <c r="G1071" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1071">
         <v>31</v>
@@ -47370,7 +47332,7 @@
         <v>3754</v>
       </c>
       <c r="G1073" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1073">
         <v>31</v>
@@ -47486,7 +47448,7 @@
         <v>134885</v>
       </c>
       <c r="K1077" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1078" spans="1:11">
@@ -47582,7 +47544,7 @@
         <v>134893</v>
       </c>
       <c r="K1080" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1081" spans="1:11">
@@ -47614,7 +47576,7 @@
         <v>134894</v>
       </c>
       <c r="K1081" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1082" spans="1:11">
@@ -47637,7 +47599,7 @@
         <v>3754</v>
       </c>
       <c r="G1082" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1082">
         <v>31</v>
@@ -47646,7 +47608,7 @@
         <v>134896</v>
       </c>
       <c r="K1082" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1083" spans="1:11">
@@ -47669,7 +47631,7 @@
         <v>3754</v>
       </c>
       <c r="G1083" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1083">
         <v>31</v>
@@ -47678,7 +47640,7 @@
         <v>134897</v>
       </c>
       <c r="K1083" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1084" spans="1:11">
@@ -47701,7 +47663,7 @@
         <v>3754</v>
       </c>
       <c r="G1084" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1084">
         <v>31</v>
@@ -47710,7 +47672,7 @@
         <v>134899</v>
       </c>
       <c r="K1084" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1085" spans="1:11">
@@ -47733,7 +47695,7 @@
         <v>3754</v>
       </c>
       <c r="G1085" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1085">
         <v>31</v>
@@ -47742,7 +47704,7 @@
         <v>134900</v>
       </c>
       <c r="K1085" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1086" spans="1:11">
@@ -47765,7 +47727,7 @@
         <v>3754</v>
       </c>
       <c r="G1086" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1086">
         <v>31</v>
@@ -47774,7 +47736,7 @@
         <v>134902</v>
       </c>
       <c r="K1086" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1087" spans="1:11">
@@ -47806,7 +47768,7 @@
         <v>134904</v>
       </c>
       <c r="K1087" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1088" spans="1:11">
@@ -47829,7 +47791,7 @@
         <v>3754</v>
       </c>
       <c r="G1088" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1088">
         <v>31</v>
@@ -47838,7 +47800,7 @@
         <v>134905</v>
       </c>
       <c r="K1088" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1089" spans="1:11">
@@ -47870,7 +47832,7 @@
         <v>134907</v>
       </c>
       <c r="K1089" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1090" spans="1:11">
@@ -47902,7 +47864,7 @@
         <v>134932</v>
       </c>
       <c r="K1090" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1091" spans="1:11">
@@ -47934,7 +47896,7 @@
         <v>134933</v>
       </c>
       <c r="K1091" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1092" spans="1:11">
@@ -47966,7 +47928,7 @@
         <v>134935</v>
       </c>
       <c r="K1092" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1093" spans="1:11">
@@ -47998,7 +47960,7 @@
         <v>134936</v>
       </c>
       <c r="K1093" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1094" spans="1:11">
@@ -48021,7 +47983,7 @@
         <v>3754</v>
       </c>
       <c r="G1094" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1094">
         <v>31</v>
@@ -48030,7 +47992,7 @@
         <v>134938</v>
       </c>
       <c r="K1094" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1095" spans="1:11">
@@ -48053,7 +48015,7 @@
         <v>3754</v>
       </c>
       <c r="G1095" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1095">
         <v>30</v>
@@ -48062,7 +48024,7 @@
         <v>134939</v>
       </c>
       <c r="K1095" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1096" spans="1:11">
@@ -48085,7 +48047,7 @@
         <v>3754</v>
       </c>
       <c r="G1096" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1096">
         <v>30</v>
@@ -48094,7 +48056,7 @@
         <v>134940</v>
       </c>
       <c r="K1096" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1097" spans="1:11">
@@ -48222,7 +48184,7 @@
         <v>135014</v>
       </c>
       <c r="K1100" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1101" spans="1:11">
@@ -48300,7 +48262,7 @@
         <v>3754</v>
       </c>
       <c r="G1103" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1103">
         <v>33</v>
@@ -48309,7 +48271,7 @@
         <v>135020</v>
       </c>
       <c r="K1103" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1104" spans="1:11">
@@ -48332,7 +48294,7 @@
         <v>3754</v>
       </c>
       <c r="G1104" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1104">
         <v>33</v>
@@ -48341,7 +48303,7 @@
         <v>135021</v>
       </c>
       <c r="K1104" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1105" spans="1:11">
@@ -48463,7 +48425,7 @@
         <v>135049</v>
       </c>
       <c r="K1108" t="s">
-        <v>4260</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="1109" spans="1:11">
@@ -48495,7 +48457,7 @@
         <v>135050</v>
       </c>
       <c r="K1109" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1110" spans="1:11">
@@ -48527,7 +48489,7 @@
         <v>135051</v>
       </c>
       <c r="K1110" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1111" spans="1:11">
@@ -48550,7 +48512,7 @@
         <v>3754</v>
       </c>
       <c r="G1111" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1111">
         <v>33</v>
@@ -48559,7 +48521,7 @@
         <v>135053</v>
       </c>
       <c r="K1111" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1112" spans="1:11">
@@ -48582,7 +48544,7 @@
         <v>3754</v>
       </c>
       <c r="G1112" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1112">
         <v>33</v>
@@ -48591,7 +48553,7 @@
         <v>135054</v>
       </c>
       <c r="K1112" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1113" spans="1:11">
@@ -48614,7 +48576,7 @@
         <v>3754</v>
       </c>
       <c r="G1113" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1113">
         <v>33</v>
@@ -48623,7 +48585,7 @@
         <v>135055</v>
       </c>
       <c r="K1113" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1114" spans="1:11">
@@ -48655,7 +48617,7 @@
         <v>135056</v>
       </c>
       <c r="K1114" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1115" spans="1:11">
@@ -48687,7 +48649,7 @@
         <v>135057</v>
       </c>
       <c r="K1115" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1116" spans="1:11">
@@ -48719,7 +48681,7 @@
         <v>135058</v>
       </c>
       <c r="K1116" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1117" spans="1:11">
@@ -48751,7 +48713,7 @@
         <v>135059</v>
       </c>
       <c r="K1117" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1118" spans="1:11">
@@ -48783,7 +48745,7 @@
         <v>135060</v>
       </c>
       <c r="K1118" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1119" spans="1:11">
@@ -48815,7 +48777,7 @@
         <v>135061</v>
       </c>
       <c r="K1119" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1120" spans="1:11">
@@ -48847,7 +48809,7 @@
         <v>135062</v>
       </c>
       <c r="K1120" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1121" spans="1:11">
@@ -48879,7 +48841,7 @@
         <v>135063</v>
       </c>
       <c r="K1121" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1122" spans="1:11">
@@ -48911,7 +48873,7 @@
         <v>135064</v>
       </c>
       <c r="K1122" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1123" spans="1:11">
@@ -48943,7 +48905,7 @@
         <v>135065</v>
       </c>
       <c r="K1123" t="s">
-        <v>4260</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="1124" spans="1:11">
@@ -48975,7 +48937,7 @@
         <v>135066</v>
       </c>
       <c r="K1124" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1125" spans="1:11">
@@ -49007,7 +48969,7 @@
         <v>135067</v>
       </c>
       <c r="K1125" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1126" spans="1:11">
@@ -49039,7 +49001,7 @@
         <v>135068</v>
       </c>
       <c r="K1126" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1127" spans="1:11">
@@ -49071,7 +49033,7 @@
         <v>135076</v>
       </c>
       <c r="K1127" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1128" spans="1:11">
@@ -49094,7 +49056,7 @@
         <v>3754</v>
       </c>
       <c r="G1128" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1128">
         <v>33</v>
@@ -49103,7 +49065,7 @@
         <v>135077</v>
       </c>
       <c r="K1128" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1129" spans="1:11">
@@ -49263,7 +49225,7 @@
         <v>135092</v>
       </c>
       <c r="K1133" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1134" spans="1:11">
@@ -49295,7 +49257,7 @@
         <v>135093</v>
       </c>
       <c r="K1134" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1135" spans="1:11">
@@ -49327,7 +49289,7 @@
         <v>135095</v>
       </c>
       <c r="K1135" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1136" spans="1:11">
@@ -49359,7 +49321,7 @@
         <v>135096</v>
       </c>
       <c r="K1136" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1137" spans="1:11">
@@ -49391,7 +49353,7 @@
         <v>135097</v>
       </c>
       <c r="K1137" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1138" spans="1:11">
@@ -49423,7 +49385,7 @@
         <v>135098</v>
       </c>
       <c r="K1138" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1139" spans="1:11">
@@ -49574,7 +49536,7 @@
         <v>135103</v>
       </c>
       <c r="K1143" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1144" spans="1:11">
@@ -49606,7 +49568,7 @@
         <v>135108</v>
       </c>
       <c r="K1144" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="1145" spans="1:11">
@@ -49670,7 +49632,7 @@
         <v>135110</v>
       </c>
       <c r="K1146" t="s">
-        <v>4269</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1147" spans="1:11">
@@ -49734,7 +49696,7 @@
         <v>135113</v>
       </c>
       <c r="K1148" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1149" spans="1:11">
@@ -49766,7 +49728,7 @@
         <v>135117</v>
       </c>
       <c r="K1149" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1150" spans="1:11">
@@ -49798,7 +49760,7 @@
         <v>135118</v>
       </c>
       <c r="K1150" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1151" spans="1:11">
@@ -49830,7 +49792,7 @@
         <v>135119</v>
       </c>
       <c r="K1151" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1152" spans="1:11">
@@ -49926,7 +49888,7 @@
         <v>135125</v>
       </c>
       <c r="K1154" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1155" spans="1:11">
@@ -49958,7 +49920,7 @@
         <v>135126</v>
       </c>
       <c r="K1155" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1156" spans="1:11">
@@ -50004,7 +49966,7 @@
         <v>3754</v>
       </c>
       <c r="G1157" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1157">
         <v>31</v>
@@ -50013,7 +49975,7 @@
         <v>135129</v>
       </c>
       <c r="K1157" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1158" spans="1:11">
@@ -50036,7 +49998,7 @@
         <v>3754</v>
       </c>
       <c r="G1158" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1158">
         <v>31</v>
@@ -50045,7 +50007,7 @@
         <v>135130</v>
       </c>
       <c r="K1158" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1159" spans="1:11">
@@ -50068,7 +50030,7 @@
         <v>3754</v>
       </c>
       <c r="G1159" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1159">
         <v>31</v>
@@ -50077,7 +50039,7 @@
         <v>135131</v>
       </c>
       <c r="K1159" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1160" spans="1:11">
@@ -50100,7 +50062,7 @@
         <v>3754</v>
       </c>
       <c r="G1160" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1160">
         <v>31</v>
@@ -50109,7 +50071,7 @@
         <v>135132</v>
       </c>
       <c r="K1160" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1161" spans="1:11">
@@ -50132,7 +50094,7 @@
         <v>3754</v>
       </c>
       <c r="G1161" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1161">
         <v>31</v>
@@ -50141,7 +50103,7 @@
         <v>135133</v>
       </c>
       <c r="K1161" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1162" spans="1:11">
@@ -50187,7 +50149,7 @@
         <v>3754</v>
       </c>
       <c r="G1163" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1163">
         <v>31</v>
@@ -50196,7 +50158,7 @@
         <v>135178</v>
       </c>
       <c r="K1163" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1164" spans="1:11">
@@ -50219,7 +50181,7 @@
         <v>3754</v>
       </c>
       <c r="G1164" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1164">
         <v>31</v>
@@ -50228,7 +50190,7 @@
         <v>135180</v>
       </c>
       <c r="K1164" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1165" spans="1:11">
@@ -50324,7 +50286,7 @@
         <v>135262</v>
       </c>
       <c r="K1167" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1168" spans="1:11">
@@ -50356,7 +50318,7 @@
         <v>135266</v>
       </c>
       <c r="K1168" t="s">
-        <v>4270</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="1169" spans="1:11">
@@ -50388,7 +50350,7 @@
         <v>135267</v>
       </c>
       <c r="K1169" t="s">
-        <v>4271</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="1170" spans="1:11">
@@ -50411,7 +50373,7 @@
         <v>3754</v>
       </c>
       <c r="G1170" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1170">
         <v>30</v>
@@ -50420,7 +50382,7 @@
         <v>135268</v>
       </c>
       <c r="K1170" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1171" spans="1:11">
@@ -50484,7 +50446,7 @@
         <v>135335</v>
       </c>
       <c r="K1172" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1173" spans="1:11">
@@ -50644,7 +50606,7 @@
         <v>135343</v>
       </c>
       <c r="K1177" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1178" spans="1:11">
@@ -50795,7 +50757,7 @@
         <v>3754</v>
       </c>
       <c r="G1182" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1182">
         <v>31</v>
@@ -50804,7 +50766,7 @@
         <v>135426</v>
       </c>
       <c r="K1182" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1183" spans="1:11">
@@ -50827,7 +50789,7 @@
         <v>3754</v>
       </c>
       <c r="G1183" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1183">
         <v>31</v>
@@ -50836,7 +50798,7 @@
         <v>135427</v>
       </c>
       <c r="K1183" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1184" spans="1:11">
@@ -50859,7 +50821,7 @@
         <v>3754</v>
       </c>
       <c r="G1184" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1184">
         <v>31</v>
@@ -50868,7 +50830,7 @@
         <v>135429</v>
       </c>
       <c r="K1184" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1185" spans="1:11">
@@ -50891,7 +50853,7 @@
         <v>3754</v>
       </c>
       <c r="G1185" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1185">
         <v>31</v>
@@ -50900,7 +50862,7 @@
         <v>135430</v>
       </c>
       <c r="K1185" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1186" spans="1:11">
@@ -50932,7 +50894,7 @@
         <v>135431</v>
       </c>
       <c r="K1186" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1187" spans="1:11">
@@ -50955,7 +50917,7 @@
         <v>3754</v>
       </c>
       <c r="G1187" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1187">
         <v>31</v>
@@ -50964,7 +50926,7 @@
         <v>135432</v>
       </c>
       <c r="K1187" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1188" spans="1:11">
@@ -50987,7 +50949,7 @@
         <v>3754</v>
       </c>
       <c r="G1188" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1188">
         <v>31</v>
@@ -50996,7 +50958,7 @@
         <v>135433</v>
       </c>
       <c r="K1188" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1189" spans="1:11">
@@ -51019,7 +50981,7 @@
         <v>3754</v>
       </c>
       <c r="G1189" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1189">
         <v>31</v>
@@ -51028,7 +50990,7 @@
         <v>135435</v>
       </c>
       <c r="K1189" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1190" spans="1:11">
@@ -51060,7 +51022,7 @@
         <v>135436</v>
       </c>
       <c r="K1190" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1191" spans="1:11">
@@ -51156,7 +51118,7 @@
         <v>135439</v>
       </c>
       <c r="K1193" t="s">
-        <v>4265</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="1194" spans="1:11">
@@ -51188,7 +51150,7 @@
         <v>135440</v>
       </c>
       <c r="K1194" t="s">
-        <v>4272</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="1195" spans="1:11">
@@ -51444,7 +51406,7 @@
         <v>135452</v>
       </c>
       <c r="K1202" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1203" spans="1:11">
@@ -51499,7 +51461,7 @@
         <v>3754</v>
       </c>
       <c r="G1204" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1204">
         <v>33</v>
@@ -51508,7 +51470,7 @@
         <v>135475</v>
       </c>
       <c r="K1204" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1205" spans="1:11">
@@ -51540,7 +51502,7 @@
         <v>135584</v>
       </c>
       <c r="K1205" t="s">
-        <v>4273</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="1206" spans="1:11">
@@ -51595,7 +51557,7 @@
         <v>135586</v>
       </c>
       <c r="K1207" t="s">
-        <v>4273</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="1208" spans="1:11">
@@ -51627,7 +51589,7 @@
         <v>135589</v>
       </c>
       <c r="K1208" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1209" spans="1:11">
@@ -51691,7 +51653,7 @@
         <v>135593</v>
       </c>
       <c r="K1210" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1211" spans="1:11">
@@ -51723,7 +51685,7 @@
         <v>135594</v>
       </c>
       <c r="K1211" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1212" spans="1:11">
@@ -51755,7 +51717,7 @@
         <v>135595</v>
       </c>
       <c r="K1212" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1213" spans="1:11">
@@ -51810,7 +51772,7 @@
         <v>3754</v>
       </c>
       <c r="G1214" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1214">
         <v>31</v>
@@ -51819,7 +51781,7 @@
         <v>135598</v>
       </c>
       <c r="K1214" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1215" spans="1:11">
@@ -51842,7 +51804,7 @@
         <v>3754</v>
       </c>
       <c r="G1215" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1215">
         <v>31</v>
@@ -51851,7 +51813,7 @@
         <v>135601</v>
       </c>
       <c r="K1215" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1216" spans="1:11">
@@ -51874,7 +51836,7 @@
         <v>3754</v>
       </c>
       <c r="G1216" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1216">
         <v>31</v>
@@ -51883,7 +51845,7 @@
         <v>135610</v>
       </c>
       <c r="K1216" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1217" spans="1:11">
@@ -51915,7 +51877,7 @@
         <v>135622</v>
       </c>
       <c r="K1217" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1218" spans="1:11">
@@ -51970,7 +51932,7 @@
         <v>3754</v>
       </c>
       <c r="G1219" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="H1219">
         <v>19</v>
@@ -51979,7 +51941,7 @@
         <v>135672</v>
       </c>
       <c r="K1219" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="1220" spans="1:11">
@@ -52066,7 +52028,7 @@
         <v>3754</v>
       </c>
       <c r="G1222" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="H1222">
         <v>19</v>
@@ -52075,7 +52037,7 @@
         <v>135676</v>
       </c>
       <c r="K1222" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="1223" spans="1:11">
@@ -52098,7 +52060,7 @@
         <v>3754</v>
       </c>
       <c r="G1223" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="H1223">
         <v>33</v>
@@ -52107,7 +52069,7 @@
         <v>135677</v>
       </c>
       <c r="K1223" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1224" spans="1:11">
@@ -52171,7 +52133,7 @@
         <v>135685</v>
       </c>
       <c r="K1225" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1226" spans="1:11">
@@ -52235,7 +52197,7 @@
         <v>135687</v>
       </c>
       <c r="K1227" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1228" spans="1:11">
@@ -52395,7 +52357,7 @@
         <v>135720</v>
       </c>
       <c r="K1232" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1233" spans="1:11">
@@ -52427,7 +52389,7 @@
         <v>135721</v>
       </c>
       <c r="K1233" t="s">
-        <v>4274</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="1234" spans="1:11">
@@ -52459,7 +52421,7 @@
         <v>135799</v>
       </c>
       <c r="K1234" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1235" spans="1:11">
@@ -52491,7 +52453,7 @@
         <v>135801</v>
       </c>
       <c r="K1235" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1236" spans="1:11">
@@ -52555,7 +52517,7 @@
         <v>135803</v>
       </c>
       <c r="K1237" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1238" spans="1:11">
@@ -52587,7 +52549,7 @@
         <v>135805</v>
       </c>
       <c r="K1238" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1239" spans="1:11">
@@ -52808,7 +52770,7 @@
         <v>135887</v>
       </c>
       <c r="K1248" t="s">
-        <v>4275</v>
+        <v>4274</v>
       </c>
     </row>
     <row r="1249" spans="1:11">
@@ -52848,7 +52810,7 @@
         <v>3754</v>
       </c>
       <c r="G1250" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1250">
         <v>33</v>
@@ -52877,7 +52839,7 @@
         <v>3754</v>
       </c>
       <c r="G1251" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1251">
         <v>33</v>
@@ -52935,7 +52897,7 @@
         <v>3754</v>
       </c>
       <c r="G1253" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="H1253">
         <v>33</v>
@@ -52944,7 +52906,7 @@
         <v>135952</v>
       </c>
       <c r="K1253" t="s">
-        <v>4276</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="1254" spans="1:11">
@@ -53022,7 +52984,7 @@
         <v>3754</v>
       </c>
       <c r="G1256" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1256">
         <v>30</v>
@@ -53031,7 +52993,7 @@
         <v>221714</v>
       </c>
       <c r="K1256" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1257" spans="1:11">
@@ -53095,7 +53057,7 @@
         <v>221760</v>
       </c>
       <c r="K1258" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1259" spans="1:11">
@@ -53118,7 +53080,7 @@
         <v>3754</v>
       </c>
       <c r="G1259" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="H1259">
         <v>14</v>
@@ -53127,7 +53089,7 @@
         <v>221766</v>
       </c>
       <c r="K1259" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1260" spans="1:11">
@@ -53191,7 +53153,7 @@
         <v>221850</v>
       </c>
       <c r="K1261" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="1262" spans="1:11">
@@ -53223,7 +53185,7 @@
         <v>221867</v>
       </c>
       <c r="K1262" t="s">
-        <v>4243</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="1263" spans="1:11">
@@ -53287,7 +53249,7 @@
         <v>222179</v>
       </c>
       <c r="K1264" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1265" spans="1:11">
@@ -53351,7 +53313,7 @@
         <v>222211</v>
       </c>
       <c r="K1266" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1267" spans="1:11">
@@ -53383,7 +53345,7 @@
         <v>222235</v>
       </c>
       <c r="K1267" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1268" spans="1:11">
@@ -53415,7 +53377,7 @@
         <v>222249</v>
       </c>
       <c r="K1268" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1269" spans="1:11">
@@ -53479,7 +53441,7 @@
         <v>222320</v>
       </c>
       <c r="K1270" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1271" spans="1:11">
@@ -53543,7 +53505,7 @@
         <v>222462</v>
       </c>
       <c r="K1272" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="1273" spans="1:11">
@@ -53575,7 +53537,7 @@
         <v>222731</v>
       </c>
       <c r="K1273" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1274" spans="1:11">
@@ -53607,7 +53569,7 @@
         <v>223136</v>
       </c>
       <c r="K1274" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1275" spans="1:11">
@@ -53639,7 +53601,7 @@
         <v>223181</v>
       </c>
       <c r="K1275" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1276" spans="1:11">
@@ -53671,7 +53633,7 @@
         <v>223217</v>
       </c>
       <c r="K1276" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1277" spans="1:11">
@@ -53703,7 +53665,7 @@
         <v>223259</v>
       </c>
       <c r="K1277" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1278" spans="1:11">
@@ -53735,7 +53697,7 @@
         <v>223268</v>
       </c>
       <c r="K1278" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1279" spans="1:11">
@@ -53767,7 +53729,7 @@
         <v>223326</v>
       </c>
       <c r="K1279" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1280" spans="1:11">
@@ -53799,7 +53761,7 @@
         <v>223333</v>
       </c>
       <c r="K1280" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1281" spans="1:11">
@@ -53831,7 +53793,7 @@
         <v>223446</v>
       </c>
       <c r="K1281" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1282" spans="1:11">
@@ -53895,7 +53857,7 @@
         <v>223582</v>
       </c>
       <c r="K1283" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1284" spans="1:11">
@@ -53927,7 +53889,7 @@
         <v>223603</v>
       </c>
       <c r="K1284" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1285" spans="1:11">
@@ -53959,7 +53921,7 @@
         <v>223719</v>
       </c>
       <c r="K1285" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1286" spans="1:11">
@@ -53982,7 +53944,7 @@
         <v>3754</v>
       </c>
       <c r="G1286" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="H1286">
         <v>14</v>
@@ -53991,7 +53953,7 @@
         <v>223779</v>
       </c>
       <c r="K1286" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1287" spans="1:11">
@@ -54055,7 +54017,7 @@
         <v>223925</v>
       </c>
       <c r="K1288" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1289" spans="1:11">
@@ -54087,7 +54049,7 @@
         <v>223939</v>
       </c>
       <c r="K1289" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="1290" spans="1:11">
@@ -54119,7 +54081,7 @@
         <v>223977</v>
       </c>
       <c r="K1290" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1291" spans="1:11">
@@ -54151,7 +54113,7 @@
         <v>224038</v>
       </c>
       <c r="K1291" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1292" spans="1:11">
@@ -54183,7 +54145,7 @@
         <v>224071</v>
       </c>
       <c r="K1292" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1293" spans="1:11">
@@ -54215,7 +54177,7 @@
         <v>224368</v>
       </c>
       <c r="K1293" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1294" spans="1:11">
@@ -54247,7 +54209,7 @@
         <v>224383</v>
       </c>
       <c r="K1294" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="1295" spans="1:11">
@@ -54270,7 +54232,7 @@
         <v>3754</v>
       </c>
       <c r="G1295" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1295">
         <v>30</v>
@@ -54279,7 +54241,7 @@
         <v>224398</v>
       </c>
       <c r="K1295" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1296" spans="1:11">
@@ -54311,7 +54273,7 @@
         <v>224508</v>
       </c>
       <c r="K1296" t="s">
-        <v>4277</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="1297" spans="1:11">
@@ -54343,7 +54305,7 @@
         <v>224516</v>
       </c>
       <c r="K1297" t="s">
-        <v>4277</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="1298" spans="1:11">
@@ -54366,7 +54328,7 @@
         <v>3754</v>
       </c>
       <c r="G1298" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="H1298">
         <v>33</v>
@@ -54407,7 +54369,7 @@
         <v>224551</v>
       </c>
       <c r="K1299" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1300" spans="1:11">
@@ -54471,7 +54433,7 @@
         <v>224648</v>
       </c>
       <c r="K1301" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1302" spans="1:11">
@@ -54494,7 +54456,7 @@
         <v>3754</v>
       </c>
       <c r="G1302" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="H1302">
         <v>22</v>
@@ -54526,7 +54488,7 @@
         <v>3754</v>
       </c>
       <c r="G1303" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="H1303">
         <v>22</v>
@@ -54558,7 +54520,7 @@
         <v>3754</v>
       </c>
       <c r="G1304" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="H1304">
         <v>22</v>
@@ -54599,7 +54561,7 @@
         <v>224721</v>
       </c>
       <c r="K1305" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1306" spans="1:11">
@@ -54631,7 +54593,7 @@
         <v>224733</v>
       </c>
       <c r="K1306" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1307" spans="1:11">
@@ -54663,7 +54625,7 @@
         <v>224735</v>
       </c>
       <c r="K1307" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1308" spans="1:11">
@@ -54695,7 +54657,7 @@
         <v>224738</v>
       </c>
       <c r="K1308" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1309" spans="1:11">
@@ -54727,7 +54689,7 @@
         <v>224787</v>
       </c>
       <c r="K1309" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="1310" spans="1:11">
@@ -54759,7 +54721,7 @@
         <v>224820</v>
       </c>
       <c r="K1310" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1311" spans="1:11">
@@ -54791,7 +54753,7 @@
         <v>224882</v>
       </c>
       <c r="K1311" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1312" spans="1:11">
@@ -54814,7 +54776,7 @@
         <v>3754</v>
       </c>
       <c r="G1312" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="H1312">
         <v>34</v>
@@ -54823,7 +54785,7 @@
         <v>224918</v>
       </c>
       <c r="K1312" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1313" spans="1:11">
@@ -54846,7 +54808,7 @@
         <v>3754</v>
       </c>
       <c r="G1313" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="H1313">
         <v>34</v>
@@ -54855,7 +54817,7 @@
         <v>224927</v>
       </c>
       <c r="K1313" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1314" spans="1:11">
@@ -54919,7 +54881,7 @@
         <v>224961</v>
       </c>
       <c r="K1315" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="1316" spans="1:11">
@@ -54951,7 +54913,7 @@
         <v>225093</v>
       </c>
       <c r="K1316" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1317" spans="1:11">
@@ -54983,7 +54945,7 @@
         <v>225097</v>
       </c>
       <c r="K1317" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1318" spans="1:11">
@@ -55015,7 +54977,7 @@
         <v>225123</v>
       </c>
       <c r="K1318" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1319" spans="1:11">
@@ -55047,7 +55009,7 @@
         <v>225127</v>
       </c>
       <c r="K1319" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1320" spans="1:11">
@@ -55079,7 +55041,7 @@
         <v>225179</v>
       </c>
       <c r="K1320" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1321" spans="1:11">
@@ -55271,7 +55233,7 @@
         <v>225937</v>
       </c>
       <c r="K1326" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1327" spans="1:11">
@@ -55303,7 +55265,7 @@
         <v>225938</v>
       </c>
       <c r="K1327" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="1328" spans="1:11">
@@ -55399,7 +55361,7 @@
         <v>226098</v>
       </c>
       <c r="K1330" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1331" spans="1:11">
@@ -55431,7 +55393,7 @@
         <v>226118</v>
       </c>
       <c r="K1331" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="1332" spans="1:11">
@@ -55463,7 +55425,7 @@
         <v>226129</v>
       </c>
       <c r="K1332" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="1333" spans="1:11">
@@ -55550,7 +55512,7 @@
         <v>3754</v>
       </c>
       <c r="G1335" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="H1335">
         <v>34</v>
@@ -55559,7 +55521,7 @@
         <v>226186</v>
       </c>
       <c r="K1335" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1336" spans="1:11">
@@ -55655,7 +55617,7 @@
         <v>226395</v>
       </c>
       <c r="K1338" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1339" spans="1:11">
@@ -55687,7 +55649,7 @@
         <v>226414</v>
       </c>
       <c r="K1339" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1340" spans="1:11">
@@ -55710,7 +55672,7 @@
         <v>3754</v>
       </c>
       <c r="G1340" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="H1340">
         <v>19</v>
@@ -55751,7 +55713,7 @@
         <v>226611</v>
       </c>
       <c r="K1341" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1342" spans="1:11">
@@ -55847,7 +55809,7 @@
         <v>227181</v>
       </c>
       <c r="K1344" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1345" spans="1:11">
@@ -55879,7 +55841,7 @@
         <v>227182</v>
       </c>
       <c r="K1345" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1346" spans="1:11">
@@ -55911,7 +55873,7 @@
         <v>227305</v>
       </c>
       <c r="K1346" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1347" spans="1:11">
@@ -55943,7 +55905,7 @@
         <v>227317</v>
       </c>
       <c r="K1347" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1348" spans="1:11">
@@ -55975,7 +55937,7 @@
         <v>227330</v>
       </c>
       <c r="K1348" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1349" spans="1:11">
@@ -56007,7 +55969,7 @@
         <v>227361</v>
       </c>
       <c r="K1349" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1350" spans="1:11">
@@ -56039,7 +56001,7 @@
         <v>227375</v>
       </c>
       <c r="K1350" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1351" spans="1:11">
@@ -56071,7 +56033,7 @@
         <v>227427</v>
       </c>
       <c r="K1351" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1352" spans="1:11">
@@ -56094,7 +56056,7 @@
         <v>3754</v>
       </c>
       <c r="G1352" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="H1352">
         <v>14</v>
@@ -56103,7 +56065,7 @@
         <v>227498</v>
       </c>
       <c r="K1352" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1353" spans="1:11">
@@ -56167,7 +56129,7 @@
         <v>227565</v>
       </c>
       <c r="K1354" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1355" spans="1:11">
@@ -56199,7 +56161,7 @@
         <v>227566</v>
       </c>
       <c r="K1355" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1356" spans="1:11">
@@ -56231,7 +56193,7 @@
         <v>227580</v>
       </c>
       <c r="K1356" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1357" spans="1:11">
@@ -56263,7 +56225,7 @@
         <v>227614</v>
       </c>
       <c r="K1357" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1358" spans="1:11">
@@ -56295,7 +56257,7 @@
         <v>227624</v>
       </c>
       <c r="K1358" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1359" spans="1:11">
@@ -56327,7 +56289,7 @@
         <v>227633</v>
       </c>
       <c r="K1359" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1360" spans="1:11">
@@ -56359,7 +56321,7 @@
         <v>227684</v>
       </c>
       <c r="K1360" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1361" spans="1:11">
@@ -56391,7 +56353,7 @@
         <v>227720</v>
       </c>
       <c r="K1361" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1362" spans="1:11">
@@ -56423,7 +56385,7 @@
         <v>227749</v>
       </c>
       <c r="K1362" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1363" spans="1:11">
@@ -56487,7 +56449,7 @@
         <v>227788</v>
       </c>
       <c r="K1364" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1365" spans="1:11">
@@ -56519,7 +56481,7 @@
         <v>227803</v>
       </c>
       <c r="K1365" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="1366" spans="1:11">
@@ -56775,7 +56737,7 @@
         <v>228123</v>
       </c>
       <c r="K1373" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1374" spans="1:11">
@@ -56807,7 +56769,7 @@
         <v>228125</v>
       </c>
       <c r="K1374" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1375" spans="1:11">
@@ -56839,7 +56801,7 @@
         <v>228133</v>
       </c>
       <c r="K1375" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1376" spans="1:11">
@@ -56935,7 +56897,7 @@
         <v>228155</v>
       </c>
       <c r="K1378" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="1379" spans="1:11">
@@ -56967,7 +56929,7 @@
         <v>228156</v>
       </c>
       <c r="K1379" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="1380" spans="1:11">
@@ -56999,7 +56961,7 @@
         <v>228173</v>
       </c>
       <c r="K1380" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="1381" spans="1:11">
@@ -57031,7 +56993,7 @@
         <v>228307</v>
       </c>
       <c r="K1381" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1382" spans="1:11">
@@ -57063,7 +57025,7 @@
         <v>228308</v>
       </c>
       <c r="K1382" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1383" spans="1:11">
@@ -57287,7 +57249,7 @@
         <v>228505</v>
       </c>
       <c r="K1389" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1390" spans="1:11">
@@ -57319,7 +57281,7 @@
         <v>228517</v>
       </c>
       <c r="K1390" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1391" spans="1:11">
@@ -57351,7 +57313,7 @@
         <v>228519</v>
       </c>
       <c r="K1391" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1392" spans="1:11">
@@ -57383,7 +57345,7 @@
         <v>228553</v>
       </c>
       <c r="K1392" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1393" spans="1:11">
@@ -57415,7 +57377,7 @@
         <v>228582</v>
       </c>
       <c r="K1393" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1394" spans="1:11">
@@ -57447,7 +57409,7 @@
         <v>228586</v>
       </c>
       <c r="K1394" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1395" spans="1:11">
@@ -57479,7 +57441,7 @@
         <v>228591</v>
       </c>
       <c r="K1395" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1396" spans="1:11">
@@ -57511,7 +57473,7 @@
         <v>228592</v>
       </c>
       <c r="K1396" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1397" spans="1:11">
@@ -57543,7 +57505,7 @@
         <v>228643</v>
       </c>
       <c r="K1397" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1398" spans="1:11">
@@ -57575,7 +57537,7 @@
         <v>228644</v>
       </c>
       <c r="K1398" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1399" spans="1:11">
@@ -57607,7 +57569,7 @@
         <v>228647</v>
       </c>
       <c r="K1399" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1400" spans="1:11">
@@ -57639,7 +57601,7 @@
         <v>228704</v>
       </c>
       <c r="K1400" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1401" spans="1:11">
@@ -57671,7 +57633,7 @@
         <v>228759</v>
       </c>
       <c r="K1401" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1402" spans="1:11">
@@ -57703,7 +57665,7 @@
         <v>228763</v>
       </c>
       <c r="K1402" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1403" spans="1:11">
@@ -57735,7 +57697,7 @@
         <v>228844</v>
       </c>
       <c r="K1403" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1404" spans="1:11">
@@ -57767,7 +57729,7 @@
         <v>228845</v>
       </c>
       <c r="K1404" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1405" spans="1:11">
@@ -57959,7 +57921,7 @@
         <v>229009</v>
       </c>
       <c r="K1410" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1411" spans="1:11">
@@ -57991,7 +57953,7 @@
         <v>229063</v>
       </c>
       <c r="K1411" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1412" spans="1:11">
@@ -58014,7 +57976,7 @@
         <v>3754</v>
       </c>
       <c r="G1412" t="s">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="H1412">
         <v>21</v>
@@ -58215,7 +58177,7 @@
         <v>229123</v>
       </c>
       <c r="K1418" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1419" spans="1:11">
@@ -58247,7 +58209,7 @@
         <v>229141</v>
       </c>
       <c r="K1419" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1420" spans="1:11">
@@ -58279,7 +58241,7 @@
         <v>229181</v>
       </c>
       <c r="K1420" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="1421" spans="1:11">
@@ -58526,7 +58488,7 @@
         <v>3754</v>
       </c>
       <c r="G1428" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1428">
         <v>31</v>
@@ -58535,7 +58497,7 @@
         <v>229323</v>
       </c>
       <c r="K1428" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1429" spans="1:11">
@@ -58567,7 +58529,7 @@
         <v>229343</v>
       </c>
       <c r="K1429" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1430" spans="1:11">
@@ -58599,7 +58561,7 @@
         <v>229349</v>
       </c>
       <c r="K1430" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1431" spans="1:11">
@@ -58631,7 +58593,7 @@
         <v>229351</v>
       </c>
       <c r="K1431" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1432" spans="1:11">
@@ -58663,7 +58625,7 @@
         <v>229369</v>
       </c>
       <c r="K1432" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1433" spans="1:11">
@@ -58695,7 +58657,7 @@
         <v>229370</v>
       </c>
       <c r="K1433" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1434" spans="1:11">
@@ -58727,7 +58689,7 @@
         <v>229387</v>
       </c>
       <c r="K1434" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1435" spans="1:11">
@@ -58759,7 +58721,7 @@
         <v>229403</v>
       </c>
       <c r="K1435" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1436" spans="1:11">
@@ -58791,7 +58753,7 @@
         <v>229406</v>
       </c>
       <c r="K1436" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1437" spans="1:11">
@@ -58823,7 +58785,7 @@
         <v>229429</v>
       </c>
       <c r="K1437" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1438" spans="1:11">
@@ -58855,7 +58817,7 @@
         <v>229434</v>
       </c>
       <c r="K1438" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1439" spans="1:11">
@@ -58887,7 +58849,7 @@
         <v>229506</v>
       </c>
       <c r="K1439" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1440" spans="1:11">
@@ -58919,7 +58881,7 @@
         <v>229515</v>
       </c>
       <c r="K1440" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1441" spans="1:11">
@@ -58951,7 +58913,7 @@
         <v>229560</v>
       </c>
       <c r="K1441" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1442" spans="1:11">
@@ -58983,7 +58945,7 @@
         <v>229568</v>
       </c>
       <c r="K1442" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1443" spans="1:11">
@@ -59015,7 +58977,7 @@
         <v>229576</v>
       </c>
       <c r="K1443" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1444" spans="1:11">
@@ -59047,7 +59009,7 @@
         <v>229578</v>
       </c>
       <c r="K1444" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1445" spans="1:11">
@@ -59079,7 +59041,7 @@
         <v>229579</v>
       </c>
       <c r="K1445" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1446" spans="1:11">
@@ -59111,7 +59073,7 @@
         <v>229585</v>
       </c>
       <c r="K1446" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1447" spans="1:11">
@@ -59143,7 +59105,7 @@
         <v>229588</v>
       </c>
       <c r="K1447" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1448" spans="1:11">
@@ -59175,7 +59137,7 @@
         <v>229589</v>
       </c>
       <c r="K1448" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1449" spans="1:11">
@@ -59207,7 +59169,7 @@
         <v>229597</v>
       </c>
       <c r="K1449" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1450" spans="1:11">
@@ -59239,7 +59201,7 @@
         <v>229618</v>
       </c>
       <c r="K1450" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1451" spans="1:11">
@@ -59271,7 +59233,7 @@
         <v>229619</v>
       </c>
       <c r="K1451" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1452" spans="1:11">
@@ -59303,7 +59265,7 @@
         <v>229624</v>
       </c>
       <c r="K1452" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1453" spans="1:11">
@@ -59335,7 +59297,7 @@
         <v>229639</v>
       </c>
       <c r="K1453" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1454" spans="1:11">
@@ -59367,7 +59329,7 @@
         <v>229645</v>
       </c>
       <c r="K1454" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1455" spans="1:11">
@@ -59399,7 +59361,7 @@
         <v>229648</v>
       </c>
       <c r="K1455" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1456" spans="1:11">
@@ -59495,7 +59457,7 @@
         <v>229711</v>
       </c>
       <c r="K1458" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1459" spans="1:11">
@@ -59605,7 +59567,7 @@
         <v>229743</v>
       </c>
       <c r="K1462" t="s">
-        <v>4278</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="1463" spans="1:11">
@@ -59683,7 +59645,7 @@
         <v>229786</v>
       </c>
       <c r="K1465" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1466" spans="1:11">
@@ -59715,7 +59677,7 @@
         <v>229787</v>
       </c>
       <c r="K1466" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1467" spans="1:11">
@@ -59880,7 +59842,7 @@
         <v>229914</v>
       </c>
       <c r="K1472" t="s">
-        <v>4279</v>
+        <v>4278</v>
       </c>
     </row>
     <row r="1473" spans="1:11">
@@ -59912,7 +59874,7 @@
         <v>229916</v>
       </c>
       <c r="K1473" t="s">
-        <v>4279</v>
+        <v>4278</v>
       </c>
     </row>
     <row r="1474" spans="1:11">
@@ -60040,7 +60002,7 @@
         <v>230010</v>
       </c>
       <c r="K1477" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1478" spans="1:11">
@@ -60296,7 +60258,7 @@
         <v>230073</v>
       </c>
       <c r="K1485" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1486" spans="1:11">
@@ -60328,7 +60290,7 @@
         <v>230076</v>
       </c>
       <c r="K1486" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1487" spans="1:11">
@@ -60360,7 +60322,7 @@
         <v>230087</v>
       </c>
       <c r="K1487" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1488" spans="1:11">
@@ -60392,7 +60354,7 @@
         <v>230088</v>
       </c>
       <c r="K1488" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1489" spans="1:11">
@@ -60424,7 +60386,7 @@
         <v>230089</v>
       </c>
       <c r="K1489" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1490" spans="1:11">
@@ -60456,7 +60418,7 @@
         <v>230091</v>
       </c>
       <c r="K1490" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1491" spans="1:11">
@@ -60488,7 +60450,7 @@
         <v>230100</v>
       </c>
       <c r="K1491" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1492" spans="1:11">
@@ -60520,7 +60482,7 @@
         <v>230112</v>
       </c>
       <c r="K1492" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1493" spans="1:11">
@@ -60552,7 +60514,7 @@
         <v>230117</v>
       </c>
       <c r="K1493" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1494" spans="1:11">
@@ -60584,7 +60546,7 @@
         <v>230125</v>
       </c>
       <c r="K1494" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1495" spans="1:11">
@@ -60616,7 +60578,7 @@
         <v>230135</v>
       </c>
       <c r="K1495" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1496" spans="1:11">
@@ -60648,7 +60610,7 @@
         <v>230168</v>
       </c>
       <c r="K1496" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1497" spans="1:11">
@@ -60680,7 +60642,7 @@
         <v>230169</v>
       </c>
       <c r="K1497" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1498" spans="1:11">
@@ -60712,7 +60674,7 @@
         <v>230171</v>
       </c>
       <c r="K1498" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1499" spans="1:11">
@@ -60744,7 +60706,7 @@
         <v>230205</v>
       </c>
       <c r="K1499" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1500" spans="1:11">
@@ -60776,7 +60738,7 @@
         <v>230227</v>
       </c>
       <c r="K1500" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1501" spans="1:11">
@@ -60808,7 +60770,7 @@
         <v>230290</v>
       </c>
       <c r="K1501" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1502" spans="1:11">
@@ -60863,7 +60825,7 @@
         <v>230310</v>
       </c>
       <c r="K1503" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1504" spans="1:11">
@@ -60895,7 +60857,7 @@
         <v>230339</v>
       </c>
       <c r="K1504" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1505" spans="1:11">
@@ -60927,7 +60889,7 @@
         <v>230349</v>
       </c>
       <c r="K1505" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1506" spans="1:11">
@@ -60959,7 +60921,7 @@
         <v>230351</v>
       </c>
       <c r="K1506" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1507" spans="1:11">
@@ -60991,7 +60953,7 @@
         <v>230353</v>
       </c>
       <c r="K1507" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1508" spans="1:11">
@@ -61023,7 +60985,7 @@
         <v>230354</v>
       </c>
       <c r="K1508" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1509" spans="1:11">
@@ -61055,7 +61017,7 @@
         <v>230431</v>
       </c>
       <c r="K1509" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1510" spans="1:11">
@@ -61471,7 +61433,7 @@
         <v>230633</v>
       </c>
       <c r="K1522" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1523" spans="1:11">
@@ -61503,7 +61465,7 @@
         <v>230636</v>
       </c>
       <c r="K1523" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1524" spans="1:11">
@@ -61535,7 +61497,7 @@
         <v>230672</v>
       </c>
       <c r="K1524" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1525" spans="1:11">
@@ -61567,7 +61529,7 @@
         <v>230677</v>
       </c>
       <c r="K1525" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1526" spans="1:11">
@@ -61599,7 +61561,7 @@
         <v>230710</v>
       </c>
       <c r="K1526" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1527" spans="1:11">
@@ -61631,7 +61593,7 @@
         <v>230717</v>
       </c>
       <c r="K1527" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1528" spans="1:11">
@@ -61663,7 +61625,7 @@
         <v>230751</v>
       </c>
       <c r="K1528" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1529" spans="1:11">
@@ -61695,7 +61657,7 @@
         <v>230753</v>
       </c>
       <c r="K1529" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="1530" spans="1:11">
@@ -61727,7 +61689,7 @@
         <v>230889</v>
       </c>
       <c r="K1530" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1531" spans="1:11">
@@ -61759,7 +61721,7 @@
         <v>230918</v>
       </c>
       <c r="K1531" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1532" spans="1:11">
@@ -61791,7 +61753,7 @@
         <v>230919</v>
       </c>
       <c r="K1532" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1533" spans="1:11">
@@ -61823,7 +61785,7 @@
         <v>230926</v>
       </c>
       <c r="K1533" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1534" spans="1:11">
@@ -61887,7 +61849,7 @@
         <v>230930</v>
       </c>
       <c r="K1535" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1536" spans="1:11">
@@ -61919,7 +61881,7 @@
         <v>230938</v>
       </c>
       <c r="K1536" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1537" spans="1:11">
@@ -61951,7 +61913,7 @@
         <v>230941</v>
       </c>
       <c r="K1537" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1538" spans="1:11">
@@ -61983,7 +61945,7 @@
         <v>230949</v>
       </c>
       <c r="K1538" t="s">
-        <v>4280</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="1539" spans="1:11">
@@ -62015,7 +61977,7 @@
         <v>231004</v>
       </c>
       <c r="K1539" t="s">
-        <v>4280</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="1540" spans="1:11">
@@ -62047,7 +62009,7 @@
         <v>231048</v>
       </c>
       <c r="K1540" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1541" spans="1:11">
@@ -62079,7 +62041,7 @@
         <v>231051</v>
       </c>
       <c r="K1541" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1542" spans="1:11">
@@ -62111,7 +62073,7 @@
         <v>231053</v>
       </c>
       <c r="K1542" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1543" spans="1:11">
@@ -62143,7 +62105,7 @@
         <v>231054</v>
       </c>
       <c r="K1543" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1544" spans="1:11">
@@ -62175,7 +62137,7 @@
         <v>231077</v>
       </c>
       <c r="K1544" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1545" spans="1:11">
@@ -62207,7 +62169,7 @@
         <v>231091</v>
       </c>
       <c r="K1545" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1546" spans="1:11">
@@ -62239,7 +62201,7 @@
         <v>231094</v>
       </c>
       <c r="K1546" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1547" spans="1:11">
@@ -62271,7 +62233,7 @@
         <v>231131</v>
       </c>
       <c r="K1547" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1548" spans="1:11">
@@ -62367,7 +62329,7 @@
         <v>231237</v>
       </c>
       <c r="K1550" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1551" spans="1:11">
@@ -62399,7 +62361,7 @@
         <v>231240</v>
       </c>
       <c r="K1551" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1552" spans="1:11">
@@ -62431,7 +62393,7 @@
         <v>231242</v>
       </c>
       <c r="K1552" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1553" spans="1:11">
@@ -62463,7 +62425,7 @@
         <v>231246</v>
       </c>
       <c r="K1553" t="s">
-        <v>4281</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="1554" spans="1:11">
@@ -62550,7 +62512,7 @@
         <v>3754</v>
       </c>
       <c r="G1556" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1556">
         <v>31</v>
@@ -62559,7 +62521,7 @@
         <v>231321</v>
       </c>
       <c r="K1556" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1557" spans="1:11">
@@ -62591,7 +62553,7 @@
         <v>231343</v>
       </c>
       <c r="K1557" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1558" spans="1:11">
@@ -62623,7 +62585,7 @@
         <v>231376</v>
       </c>
       <c r="K1558" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1559" spans="1:11">
@@ -62655,7 +62617,7 @@
         <v>231377</v>
       </c>
       <c r="K1559" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1560" spans="1:11">
@@ -62687,7 +62649,7 @@
         <v>231400</v>
       </c>
       <c r="K1560" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1561" spans="1:11">
@@ -62719,7 +62681,7 @@
         <v>231404</v>
       </c>
       <c r="K1561" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1562" spans="1:11">
@@ -62751,7 +62713,7 @@
         <v>231415</v>
       </c>
       <c r="K1562" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1563" spans="1:11">
@@ -62783,7 +62745,7 @@
         <v>231427</v>
       </c>
       <c r="K1563" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1564" spans="1:11">
@@ -62815,7 +62777,7 @@
         <v>231446</v>
       </c>
       <c r="K1564" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1565" spans="1:11">
@@ -62847,7 +62809,7 @@
         <v>231447</v>
       </c>
       <c r="K1565" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1566" spans="1:11">
@@ -62879,7 +62841,7 @@
         <v>231455</v>
       </c>
       <c r="K1566" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1567" spans="1:11">
@@ -62911,7 +62873,7 @@
         <v>231483</v>
       </c>
       <c r="K1567" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1568" spans="1:11">
@@ -62943,7 +62905,7 @@
         <v>231487</v>
       </c>
       <c r="K1568" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1569" spans="1:11">
@@ -62975,7 +62937,7 @@
         <v>231575</v>
       </c>
       <c r="K1569" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1570" spans="1:11">
@@ -63007,7 +62969,7 @@
         <v>231576</v>
       </c>
       <c r="K1570" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1571" spans="1:11">
@@ -63039,7 +63001,7 @@
         <v>231577</v>
       </c>
       <c r="K1571" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1572" spans="1:11">
@@ -63071,7 +63033,7 @@
         <v>231597</v>
       </c>
       <c r="K1572" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1573" spans="1:11">
@@ -63103,7 +63065,7 @@
         <v>231598</v>
       </c>
       <c r="K1573" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1574" spans="1:11">
@@ -63135,7 +63097,7 @@
         <v>231599</v>
       </c>
       <c r="K1574" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1575" spans="1:11">
@@ -63167,7 +63129,7 @@
         <v>231616</v>
       </c>
       <c r="K1575" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1576" spans="1:11">
@@ -63199,7 +63161,7 @@
         <v>231622</v>
       </c>
       <c r="K1576" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1577" spans="1:11">
@@ -63231,7 +63193,7 @@
         <v>231638</v>
       </c>
       <c r="K1577" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1578" spans="1:11">
@@ -63263,7 +63225,7 @@
         <v>231646</v>
       </c>
       <c r="K1578" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1579" spans="1:11">
@@ -63295,7 +63257,7 @@
         <v>231647</v>
       </c>
       <c r="K1579" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1580" spans="1:11">
@@ -63327,7 +63289,7 @@
         <v>231679</v>
       </c>
       <c r="K1580" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1581" spans="1:11">
@@ -63359,7 +63321,7 @@
         <v>231687</v>
       </c>
       <c r="K1581" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1582" spans="1:11">
@@ -63391,7 +63353,7 @@
         <v>231699</v>
       </c>
       <c r="K1582" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1583" spans="1:11">
@@ -63423,7 +63385,7 @@
         <v>231740</v>
       </c>
       <c r="K1583" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1584" spans="1:11">
@@ -63455,7 +63417,7 @@
         <v>231764</v>
       </c>
       <c r="K1584" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1585" spans="1:11">
@@ -63487,7 +63449,7 @@
         <v>231805</v>
       </c>
       <c r="K1585" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1586" spans="1:11">
@@ -63519,7 +63481,7 @@
         <v>231847</v>
       </c>
       <c r="K1586" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1587" spans="1:11">
@@ -63551,7 +63513,7 @@
         <v>231848</v>
       </c>
       <c r="K1587" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1588" spans="1:11">
@@ -63775,7 +63737,7 @@
         <v>231868</v>
       </c>
       <c r="K1594" t="s">
-        <v>4282</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="1595" spans="1:11">
@@ -63839,7 +63801,7 @@
         <v>231871</v>
       </c>
       <c r="K1596" t="s">
-        <v>4283</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="1597" spans="1:11">
@@ -63903,7 +63865,7 @@
         <v>231873</v>
       </c>
       <c r="K1598" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1599" spans="1:11">
@@ -63935,7 +63897,7 @@
         <v>231874</v>
       </c>
       <c r="K1599" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1600" spans="1:11">
@@ -64063,7 +64025,7 @@
         <v>231878</v>
       </c>
       <c r="K1603" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1604" spans="1:11">
@@ -64095,7 +64057,7 @@
         <v>231879</v>
       </c>
       <c r="K1604" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1605" spans="1:11">
@@ -64127,7 +64089,7 @@
         <v>231880</v>
       </c>
       <c r="K1605" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1606" spans="1:11">
@@ -64191,7 +64153,7 @@
         <v>231894</v>
       </c>
       <c r="K1607" t="s">
-        <v>4284</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="1608" spans="1:11">
@@ -64255,7 +64217,7 @@
         <v>231896</v>
       </c>
       <c r="K1609" t="s">
-        <v>4285</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="1610" spans="1:11">
@@ -64287,7 +64249,7 @@
         <v>231897</v>
       </c>
       <c r="K1610" t="s">
-        <v>4286</v>
+        <v>4285</v>
       </c>
     </row>
     <row r="1611" spans="1:11">
@@ -64351,7 +64313,7 @@
         <v>231902</v>
       </c>
       <c r="K1612" t="s">
-        <v>4287</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="1613" spans="1:11">
@@ -64447,7 +64409,7 @@
         <v>231905</v>
       </c>
       <c r="K1615" t="s">
-        <v>4288</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="1616" spans="1:11">
@@ -64575,7 +64537,7 @@
         <v>231940</v>
       </c>
       <c r="K1619" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1620" spans="1:11">
@@ -64607,7 +64569,7 @@
         <v>231941</v>
       </c>
       <c r="K1620" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1621" spans="1:11">
@@ -64639,7 +64601,7 @@
         <v>231943</v>
       </c>
       <c r="K1621" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1622" spans="1:11">
@@ -64671,7 +64633,7 @@
         <v>231965</v>
       </c>
       <c r="K1622" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1623" spans="1:11">
@@ -64703,7 +64665,7 @@
         <v>231966</v>
       </c>
       <c r="K1623" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1624" spans="1:11">
@@ -65023,7 +64985,7 @@
         <v>231994</v>
       </c>
       <c r="K1633" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1634" spans="1:11">
@@ -65183,7 +65145,7 @@
         <v>231999</v>
       </c>
       <c r="K1638" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1639" spans="1:11">
@@ -65215,7 +65177,7 @@
         <v>232000</v>
       </c>
       <c r="K1639" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1640" spans="1:11">
@@ -65311,7 +65273,7 @@
         <v>232008</v>
       </c>
       <c r="K1642" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1643" spans="1:11">
@@ -65444,7 +65406,7 @@
         <v>232050</v>
       </c>
       <c r="K1647" t="s">
-        <v>4290</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1648" spans="1:11">
@@ -65540,7 +65502,7 @@
         <v>232054</v>
       </c>
       <c r="K1650" t="s">
-        <v>4290</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1651" spans="1:11">
@@ -65636,7 +65598,7 @@
         <v>232058</v>
       </c>
       <c r="K1653" t="s">
-        <v>4291</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="1654" spans="1:11">
@@ -65755,7 +65717,7 @@
         <v>232087</v>
       </c>
       <c r="K1657" t="s">
-        <v>4292</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="1658" spans="1:11">
@@ -65979,7 +65941,7 @@
         <v>232095</v>
       </c>
       <c r="K1664" t="s">
-        <v>4293</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="1665" spans="1:11">
@@ -66107,7 +66069,7 @@
         <v>232099</v>
       </c>
       <c r="K1668" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="1669" spans="1:11">
@@ -66162,7 +66124,7 @@
         <v>3754</v>
       </c>
       <c r="G1670" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1670">
         <v>30</v>
@@ -66194,7 +66156,7 @@
         <v>3754</v>
       </c>
       <c r="G1671" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="H1671">
         <v>30</v>
@@ -66235,7 +66197,7 @@
         <v>232107</v>
       </c>
       <c r="K1672" t="s">
-        <v>4294</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="1673" spans="1:11">
@@ -66459,7 +66421,7 @@
         <v>232117</v>
       </c>
       <c r="K1679" t="s">
-        <v>4295</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="1680" spans="1:11">
@@ -66555,7 +66517,7 @@
         <v>232134</v>
       </c>
       <c r="K1682" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="1683" spans="1:11">
@@ -66619,7 +66581,7 @@
         <v>232136</v>
       </c>
       <c r="K1684" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1685" spans="1:11">
@@ -66651,7 +66613,7 @@
         <v>232137</v>
       </c>
       <c r="K1685" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1686" spans="1:11">
@@ -66683,7 +66645,7 @@
         <v>232138</v>
       </c>
       <c r="K1686" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1687" spans="1:11">
@@ -66715,7 +66677,7 @@
         <v>232143</v>
       </c>
       <c r="K1687" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1688" spans="1:11">
@@ -66802,7 +66764,7 @@
         <v>3754</v>
       </c>
       <c r="G1690" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="H1690">
         <v>33</v>
@@ -66843,7 +66805,7 @@
         <v>232178</v>
       </c>
       <c r="K1691" t="s">
-        <v>4294</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="1692" spans="1:11">
@@ -67003,7 +66965,7 @@
         <v>232184</v>
       </c>
       <c r="K1696" t="s">
-        <v>4294</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="1697" spans="1:11">
@@ -67058,7 +67020,7 @@
         <v>3754</v>
       </c>
       <c r="G1698" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="H1698">
         <v>33</v>
@@ -67131,7 +67093,7 @@
         <v>232188</v>
       </c>
       <c r="K1700" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="1701" spans="1:11">
@@ -67218,7 +67180,7 @@
         <v>3754</v>
       </c>
       <c r="G1703" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="H1703">
         <v>40</v>
@@ -69202,7 +69164,7 @@
         <v>3754</v>
       </c>
       <c r="G1765" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="H1765">
         <v>31</v>
@@ -69275,7 +69237,7 @@
         <v>232503</v>
       </c>
       <c r="K1767" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1768" spans="1:11">
@@ -69339,7 +69301,7 @@
         <v>232505</v>
       </c>
       <c r="K1769" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1770" spans="1:11">
@@ -69371,7 +69333,7 @@
         <v>232507</v>
       </c>
       <c r="K1770" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1771" spans="1:11">
@@ -69755,7 +69717,7 @@
         <v>232570</v>
       </c>
       <c r="K1782" t="s">
-        <v>4296</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="1783" spans="1:11">
@@ -71419,7 +71381,7 @@
         <v>230437</v>
       </c>
       <c r="K1852" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
   </sheetData>

--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHARTESH\OneDrive\Desktop\updated project\SHARED SUPPORT SERVICE APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF2F6AD-A37A-4FAF-B63B-9940EE65EF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237F0F96-3FC6-47C2-9240-DDD75065B125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60805,7 +60805,7 @@
         <v>18</v>
       </c>
       <c r="J1500">
-        <v>230205</v>
+        <v>230227</v>
       </c>
       <c r="K1500" t="s">
         <v>4234</v>
